--- a/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
+++ b/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
@@ -1,21 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d752cb73b61fc091/Desktop/linuxlabs/projectredstone/docs/project-management/02_Business_Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52D93188-6EC9-4891-AC7C-0483AAB4F32A}"/>
+  <xr:revisionPtr revIDLastSave="262" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{309A0387-D55D-4B4E-A611-398DC9D6328D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="2" activeTab="4" xr2:uid="{BD0B86D2-9AC1-421E-A95D-1B17A25780EE}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="RTM" sheetId="2" r:id="rId2"/>
     <sheet name="Legend &amp; Reference" sheetId="3" r:id="rId3"/>
+    <sheet name="Architecture Domains" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1241" uniqueCount="389">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="504">
   <si>
     <t>Northwind Outdoor Ltd. | RTM Summary</t>
   </si>
@@ -403,9 +406,6 @@
     <t>BR-016</t>
   </si>
   <si>
-    <t>Application Resilience — Business-critical applications shall minimise single points of failure and support improved service resilience where justified by business requirements.</t>
-  </si>
-  <si>
     <t>Agreed critical services meet defined resilience requirements and expected failure scenarios are addressed.</t>
   </si>
   <si>
@@ -1202,13 +1202,378 @@
   </si>
   <si>
     <t>RHCSA Objective</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Architecture Domain</t>
+  </si>
+  <si>
+    <t>What we'll design at HLD level</t>
+  </si>
+  <si>
+    <t>Example capabilities inside it</t>
+  </si>
+  <si>
+    <t>AD-01</t>
+  </si>
+  <si>
+    <t>Network Architecture</t>
+  </si>
+  <si>
+    <t>How systems/users connect and how networks are logically separated</t>
+  </si>
+  <si>
+    <t>VLANs, routing, firewall boundaries, Internet access, remote connectivity</t>
+  </si>
+  <si>
+    <t>AD-02</t>
+  </si>
+  <si>
+    <t>Compute &amp; Platform Architecture</t>
+  </si>
+  <si>
+    <t>Where workloads run</t>
+  </si>
+  <si>
+    <t>Proxmox/virtualisation, Linux VMs, server roles, sandbox/production separation</t>
+  </si>
+  <si>
+    <t>AD-03</t>
+  </si>
+  <si>
+    <t>Identity &amp; Access Architecture</t>
+  </si>
+  <si>
+    <t>How people/systems authenticate and receive access</t>
+  </si>
+  <si>
+    <t>Users, groups, authentication, sudo/admin access, joiners/leavers</t>
+  </si>
+  <si>
+    <t>AD-04</t>
+  </si>
+  <si>
+    <t>Core Infrastructure Services</t>
+  </si>
+  <si>
+    <t>Fundamental services other systems depend upon</t>
+  </si>
+  <si>
+    <t>DNS, DHCP, NTP/time synchronisation</t>
+  </si>
+  <si>
+    <t>AD-05</t>
+  </si>
+  <si>
+    <t>Application &amp; Business Services</t>
+  </si>
+  <si>
+    <t>Services directly consumed by Northwind users/business processes</t>
+  </si>
+  <si>
+    <t>File sharing, printing, internal applications/web services</t>
+  </si>
+  <si>
+    <t>AD-06</t>
+  </si>
+  <si>
+    <t>Storage Architecture</t>
+  </si>
+  <si>
+    <t>How persistent data is stored and expanded</t>
+  </si>
+  <si>
+    <t>Filesystems, logical storage, capacity, growth</t>
+  </si>
+  <si>
+    <t>AD-07</t>
+  </si>
+  <si>
+    <t>Backup &amp; Recovery Architecture</t>
+  </si>
+  <si>
+    <t>How data/services are protected and recovered</t>
+  </si>
+  <si>
+    <t>Backups, retention, restore testing, RPO/RTO</t>
+  </si>
+  <si>
+    <t>AD-08</t>
+  </si>
+  <si>
+    <t>Security Architecture</t>
+  </si>
+  <si>
+    <t>Security principles and trust boundaries across the environment</t>
+  </si>
+  <si>
+    <t>Segmentation, least privilege, firewalling, SELinux, hardening</t>
+  </si>
+  <si>
+    <t>AD-09</t>
+  </si>
+  <si>
+    <t>Observability Architecture</t>
+  </si>
+  <si>
+    <t>How we know what the environment is doing</t>
+  </si>
+  <si>
+    <t>Monitoring, logging, alerting, capacity metrics</t>
+  </si>
+  <si>
+    <t>AD-10</t>
+  </si>
+  <si>
+    <t>Management &amp; Operations Architecture</t>
+  </si>
+  <si>
+    <t>How IT operates and maintains the environment</t>
+  </si>
+  <si>
+    <t>SSH/admin access, patching, software management, maintenance, operational procedures</t>
+  </si>
+  <si>
+    <t>AD-11</t>
+  </si>
+  <si>
+    <t>Integration Architecture</t>
+  </si>
+  <si>
+    <t>How Northwind systems interact with external/existing platforms</t>
+  </si>
+  <si>
+    <t>Microsoft 365, external services, future integrations</t>
+  </si>
+  <si>
+    <t>AD-12</t>
+  </si>
+  <si>
+    <t>Resilience &amp; Availability Architecture</t>
+  </si>
+  <si>
+    <t>How the architecture responds to failures</t>
+  </si>
+  <si>
+    <t>Redundancy, failure domains, HA decisions, service dependencies</t>
+  </si>
+  <si>
+    <t>Primary AD</t>
+  </si>
+  <si>
+    <t>Secondary Ads</t>
+  </si>
+  <si>
+    <t>AD-07, AD-06, AD-09</t>
+  </si>
+  <si>
+    <t>AD-01, AD-08, AD-10</t>
+  </si>
+  <si>
+    <t>Key ADs</t>
+  </si>
+  <si>
+    <t>AD-04,AD-08,AD-09,AD-10</t>
+  </si>
+  <si>
+    <t>AD-01, AD-02,AD-05</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Domain</t>
+  </si>
+  <si>
+    <t>Primary</t>
+  </si>
+  <si>
+    <t>Key Supporting</t>
+  </si>
+  <si>
+    <t>Secondary</t>
+  </si>
+  <si>
+    <t>AD-05 Application &amp; Business Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AD-03, AD-05, AD-08, </t>
+  </si>
+  <si>
+    <t>AD-11, AD-02, AD-09</t>
+  </si>
+  <si>
+    <t>AD-03 Identity &amp; Access Architecture</t>
+  </si>
+  <si>
+    <t>AD-08 Security Architecture</t>
+  </si>
+  <si>
+    <t>AD-03, AD-05, AD-08</t>
+  </si>
+  <si>
+    <t>Why it relates</t>
+  </si>
+  <si>
+    <t>AD-09 Observability Architecture</t>
+  </si>
+  <si>
+    <t>AD-08, AD-05, AD-10</t>
+  </si>
+  <si>
+    <t>AD-02, AD-11, AD-09</t>
+  </si>
+  <si>
+    <t>AD-06, AD-03, AD-08, AD-07</t>
+  </si>
+  <si>
+    <t>AD-01, AD-09, AD-10, AD-12, AD-02</t>
+  </si>
+  <si>
+    <t>AD-10, AD-03, AD-08</t>
+  </si>
+  <si>
+    <t>AD-06, AD-09, AD-07</t>
+  </si>
+  <si>
+    <t>AD-10 Management &amp; Operations Architecture</t>
+  </si>
+  <si>
+    <t>AD-10, AD-05, AD-03</t>
+  </si>
+  <si>
+    <t>AD-03, AD-09, AD-05</t>
+  </si>
+  <si>
+    <t>AD-10, AD-06, AD-11, AD-02</t>
+  </si>
+  <si>
+    <t>AD-02 Compute &amp; Platform Architecture</t>
+  </si>
+  <si>
+    <t>AD-01 Network Architecture</t>
+  </si>
+  <si>
+    <t>AD-04 Core Infrastructure Services</t>
+  </si>
+  <si>
+    <t>AD-12 Resilience &amp; Availability Architecture</t>
+  </si>
+  <si>
+    <t>AD-10, AD-08, AD-07</t>
+  </si>
+  <si>
+    <t>AD-02, AD-05, AD-06, AD-01, AD-04, AD-03, AD-12</t>
+  </si>
+  <si>
+    <t>AD-09, AD-10, AD-03</t>
+  </si>
+  <si>
+    <t>AD-02, AD-01, AD-05, AD-04</t>
+  </si>
+  <si>
+    <t>AD-12, AD-06, AD-10</t>
+  </si>
+  <si>
+    <t>AD-09, AD-08, AD-02, AD-05, AD-01</t>
+  </si>
+  <si>
+    <t>AD-10, AD-12, AD-02</t>
+  </si>
+  <si>
+    <t>AD-06, AD-09, AD-08, AD-05</t>
+  </si>
+  <si>
+    <t>AD-07, AD-10, AD-02</t>
+  </si>
+  <si>
+    <t>AD-05, AD-06, AD-04, AD-03, AD-01, AD-09, AD-08</t>
+  </si>
+  <si>
+    <t>AD-05, AD-02, AD-01</t>
+  </si>
+  <si>
+    <t>AD-06, AD-04, AD-09, AD-10, AD-08, AD-07</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Application Resilience — Business-critical applications shall minimise single points of failure and support improved service resilience </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>where justified by business requirements</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Carlito"/>
+      </rPr>
+      <t>.</t>
+    </r>
+  </si>
+  <si>
+    <t>AD-08, AD-03, AD-01</t>
+  </si>
+  <si>
+    <t>AD-02, AD-09, AD-04, AD-12</t>
+  </si>
+  <si>
+    <t>AD-08, AD-03, AD-05</t>
+  </si>
+  <si>
+    <t>AD-09, AD-10, AD-11, AD-12, AD-04</t>
+  </si>
+  <si>
+    <t>AD-01, AD-03, AD-09</t>
+  </si>
+  <si>
+    <t>AD-10, AD-05, AD-02, AD-11, AD-12</t>
+  </si>
+  <si>
+    <t>Logical separation of systems/services is fundamentally a network architecture capability. The network design determines the segmentation model, boundaries and permitted connectivity between segments.</t>
+  </si>
+  <si>
+    <t>Improved security is an explicit outcome. Segmentation should limit unnecessary access and reduce the ability of a compromised system to reach unrelated infrastructure.</t>
+  </si>
+  <si>
+    <t>Operational resilience is also explicit. Segmentation can contain failures, reduce blast radius and separate systems with different operational/security characteristics.</t>
+  </si>
+  <si>
+    <t>Workloads must be placed into appropriate logical network/security zones. The compute architecture therefore needs to support the segmentation model.</t>
+  </si>
+  <si>
+    <t>Service placement and legitimate application communication requirements determine which segments need to communicate.</t>
+  </si>
+  <si>
+    <t>Administrative access across segments, changes to segmentation policy and troubleshooting require controlled operational processes.</t>
+  </si>
+  <si>
+    <t>Cross-segment traffic, denied connections and segment health may need logging/monitoring.</t>
+  </si>
+  <si>
+    <t>Certain access decisions may involve user/admin roles, particularly management access, although segmentation itself is primarily network-based.</t>
+  </si>
+  <si>
+    <t>Shared DNS, DHCP, NTP and similar services may need to operate across multiple segments and therefore influence permitted network flows.</t>
+  </si>
+  <si>
+    <t>AD-08, AD-12, AD-02</t>
+  </si>
+  <si>
+    <t>AD-05, AD-10, AD-09, AD-03, AD-04</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -1268,6 +1633,16 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -1621,7 +1996,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1737,6 +2112,18 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1752,14 +2139,21 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="6">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1776,20 +2170,105 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFDCE6F1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFDCE6F1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFDCE6F1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFDCE6F1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFDCE6F1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFDCE6F1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFDCE6F1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFDCE6F1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFDCE6F1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFDCE6F1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFDCE6F1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFDCE6F1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2008,9 +2487,13 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="RTMTable" displayName="RTMTable" ref="B4:T60" totalsRowShown="0">
-  <tableColumns count="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="RTMTable" displayName="RTMTable" ref="B4:W60" totalsRowShown="0">
+  <tableColumns count="22">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Requirement ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Requirement / Title"/>
@@ -2022,6 +2505,9 @@
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="BRD"/>
     <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="SOW"/>
     <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Sprint"/>
+    <tableColumn id="20" xr3:uid="{D1E0B300-86BD-45A9-B3EB-8951F17E8029}" name="Primary AD" dataDxfId="5"/>
+    <tableColumn id="22" xr3:uid="{701B3B8E-55FF-4520-83AD-295760593E66}" name="Key ADs" dataDxfId="4"/>
+    <tableColumn id="21" xr3:uid="{1638868F-A11C-40F1-8FB2-2AB197E42B79}" name="Secondary Ads" dataDxfId="3"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="HLD"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="LLD"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="ADR"/>
@@ -2245,32 +2731,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
     </row>
     <row r="2" spans="1:10" ht="21" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
     </row>
     <row r="4" spans="1:10" ht="15">
       <c r="A4" s="21" t="s">
@@ -2440,7 +2926,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="32">
-        <f>COUNTIF(RTM!$R$5:$R$60,A16)</f>
+        <f>COUNTIF(RTM!$U$5:$U$60,A16)</f>
         <v>56</v>
       </c>
     </row>
@@ -2456,7 +2942,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:T60"/>
+  <dimension ref="A1:W60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="2" width="15" customWidth="1"/>
@@ -2468,62 +2954,70 @@
     <col min="8" max="8" width="11" customWidth="1"/>
     <col min="9" max="9" width="12" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="16" width="17" customWidth="1"/>
-    <col min="17" max="17" width="42" customWidth="1"/>
-    <col min="18" max="18" width="22" customWidth="1"/>
-    <col min="19" max="19" width="26" customWidth="1"/>
-    <col min="20" max="20" width="54" customWidth="1"/>
+    <col min="11" max="13" width="17" customWidth="1"/>
+    <col min="14" max="14" width="15.25" bestFit="1" customWidth="1"/>
+    <col min="15" max="19" width="17" customWidth="1"/>
+    <col min="20" max="20" width="42" customWidth="1"/>
+    <col min="21" max="21" width="22" customWidth="1"/>
+    <col min="22" max="22" width="26" customWidth="1"/>
+    <col min="23" max="23" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="27.95" customHeight="1">
-      <c r="B1" s="39" t="s">
+    <row r="1" spans="1:23" ht="27.95" customHeight="1">
+      <c r="B1" s="43" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
-      <c r="K1" s="39"/>
-      <c r="L1" s="39"/>
-      <c r="M1" s="39"/>
-      <c r="N1" s="39"/>
-      <c r="O1" s="39"/>
-      <c r="P1" s="39"/>
-      <c r="Q1" s="39"/>
-      <c r="R1" s="39"/>
-      <c r="S1" s="39"/>
-      <c r="T1" s="39"/>
-    </row>
-    <row r="2" spans="1:20" ht="21" customHeight="1">
-      <c r="B2" s="40" t="s">
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
+      <c r="M1" s="43"/>
+      <c r="N1" s="43"/>
+      <c r="O1" s="43"/>
+      <c r="P1" s="43"/>
+      <c r="Q1" s="43"/>
+      <c r="R1" s="43"/>
+      <c r="S1" s="43"/>
+      <c r="T1" s="43"/>
+      <c r="U1" s="43"/>
+      <c r="V1" s="43"/>
+      <c r="W1" s="43"/>
+    </row>
+    <row r="2" spans="1:23" ht="21" customHeight="1">
+      <c r="B2" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-    </row>
-    <row r="4" spans="1:20" ht="33" customHeight="1">
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
+      <c r="M2" s="44"/>
+      <c r="N2" s="44"/>
+      <c r="O2" s="44"/>
+      <c r="P2" s="44"/>
+      <c r="Q2" s="44"/>
+      <c r="R2" s="44"/>
+      <c r="S2" s="44"/>
+      <c r="T2" s="44"/>
+      <c r="U2" s="44"/>
+      <c r="V2" s="44"/>
+      <c r="W2" s="44"/>
+    </row>
+    <row r="4" spans="1:23" ht="33" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>34</v>
@@ -2559,32 +3053,41 @@
         <v>44</v>
       </c>
       <c r="M4" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="N4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="O4" s="1" t="s">
+      <c r="R4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="S4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Q4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="R4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A5" s="44" t="s">
+    <row r="5" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A5" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B5" s="8" t="s">
@@ -2612,7 +3115,7 @@
         <v>56</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="K5" s="2" t="s">
         <v>57</v>
@@ -2621,32 +3124,41 @@
         <v>57</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>57</v>
+        <v>436</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>57</v>
+        <v>442</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>57</v>
+        <v>443</v>
       </c>
       <c r="P5" s="2" t="s">
         <v>57</v>
       </c>
       <c r="Q5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="T5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="U5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="V5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="T5" s="3" t="s">
+      <c r="W5" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A6" s="44" t="s">
+    <row r="6" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A6" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="9" t="s">
@@ -2674,7 +3186,7 @@
         <v>56</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>57</v>
@@ -2683,32 +3195,41 @@
         <v>57</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>57</v>
+        <v>400</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>446</v>
       </c>
       <c r="P6" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="R6" s="4" t="s">
+      <c r="U6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S6" s="4" t="s">
+      <c r="V6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T6" s="5" t="s">
+      <c r="W6" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A7" s="44" t="s">
+    <row r="7" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A7" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B7" s="9" t="s">
@@ -2736,7 +3257,7 @@
         <v>56</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>57</v>
@@ -2745,32 +3266,41 @@
         <v>57</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>57</v>
+        <v>453</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>57</v>
+        <v>454</v>
       </c>
       <c r="P7" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T7" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="R7" s="4" t="s">
+      <c r="U7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S7" s="4" t="s">
+      <c r="V7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T7" s="5" t="s">
+      <c r="W7" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A8" s="44" t="s">
+    <row r="8" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A8" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B8" s="9" t="s">
@@ -2798,7 +3328,7 @@
         <v>56</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>57</v>
@@ -2807,32 +3337,41 @@
         <v>57</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>57</v>
+        <v>457</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>57</v>
+        <v>454</v>
       </c>
       <c r="P8" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="R8" s="4" t="s">
+      <c r="U8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S8" s="4" t="s">
+      <c r="V8" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T8" s="5" t="s">
+      <c r="W8" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A9" s="44" t="s">
+    <row r="9" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A9" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B9" s="9" t="s">
@@ -2860,7 +3399,7 @@
         <v>56</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>57</v>
@@ -2869,32 +3408,41 @@
         <v>57</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>57</v>
+        <v>400</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>57</v>
+        <v>460</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>57</v>
+        <v>461</v>
       </c>
       <c r="P9" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T9" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="R9" s="4" t="s">
+      <c r="U9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S9" s="4" t="s">
+      <c r="V9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T9" s="5" t="s">
+      <c r="W9" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A10" s="44" t="s">
+    <row r="10" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A10" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B10" s="9" t="s">
@@ -2922,7 +3470,7 @@
         <v>56</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>57</v>
@@ -2931,32 +3479,41 @@
         <v>57</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>57</v>
+        <v>408</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>57</v>
+        <v>462</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>57</v>
+        <v>463</v>
       </c>
       <c r="P10" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T10" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="R10" s="4" t="s">
+      <c r="U10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S10" s="4" t="s">
+      <c r="V10" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T10" s="5" t="s">
+      <c r="W10" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A11" s="44" t="s">
+    <row r="11" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A11" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B11" s="9" t="s">
@@ -2984,7 +3541,7 @@
         <v>56</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>57</v>
@@ -2993,32 +3550,41 @@
         <v>57</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>57</v>
+        <v>408</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>57</v>
+        <v>464</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>57</v>
+        <v>465</v>
       </c>
       <c r="P11" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T11" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="R11" s="4" t="s">
+      <c r="U11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S11" s="4" t="s">
+      <c r="V11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T11" s="5" t="s">
+      <c r="W11" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A12" s="44" t="s">
+    <row r="12" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A12" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B12" s="9" t="s">
@@ -3046,7 +3612,7 @@
         <v>56</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>57</v>
@@ -3055,32 +3621,41 @@
         <v>57</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>57</v>
+        <v>420</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>57</v>
+        <v>467</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>57</v>
+        <v>465</v>
       </c>
       <c r="P12" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T12" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="R12" s="4" t="s">
+      <c r="U12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S12" s="4" t="s">
+      <c r="V12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T12" s="5" t="s">
+      <c r="W12" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A13" s="44" t="s">
+    <row r="13" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A13" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B13" s="9" t="s">
@@ -3108,7 +3683,7 @@
         <v>56</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>57</v>
@@ -3117,32 +3692,41 @@
         <v>57</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>57</v>
+        <v>420</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>57</v>
+        <v>468</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>57</v>
+        <v>469</v>
       </c>
       <c r="P13" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T13" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="R13" s="4" t="s">
+      <c r="U13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S13" s="4" t="s">
+      <c r="V13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T13" s="5" t="s">
+      <c r="W13" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A14" s="44" t="s">
+    <row r="14" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A14" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B14" s="9" t="s">
@@ -3170,7 +3754,7 @@
         <v>56</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>57</v>
@@ -3179,32 +3763,41 @@
         <v>57</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>57</v>
+        <v>424</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>57</v>
+        <v>416</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>57</v>
+        <v>432</v>
       </c>
       <c r="P14" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T14" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="R14" s="4" t="s">
+      <c r="U14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S14" s="4" t="s">
+      <c r="V14" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T14" s="5" t="s">
+      <c r="W14" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A15" s="44" t="s">
+    <row r="15" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A15" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B15" s="9" t="s">
@@ -3232,7 +3825,7 @@
         <v>56</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>57</v>
@@ -3241,32 +3834,41 @@
         <v>57</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>57</v>
+        <v>424</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>57</v>
+        <v>474</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>57</v>
+        <v>475</v>
       </c>
       <c r="P15" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T15" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="R15" s="4" t="s">
+      <c r="U15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S15" s="4" t="s">
+      <c r="V15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T15" s="5" t="s">
+      <c r="W15" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A16" s="44" t="s">
+    <row r="16" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A16" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B16" s="9" t="s">
@@ -3294,7 +3896,7 @@
         <v>56</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>57</v>
@@ -3303,32 +3905,41 @@
         <v>57</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>57</v>
+        <v>420</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>57</v>
+        <v>476</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>57</v>
+        <v>477</v>
       </c>
       <c r="P16" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T16" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="R16" s="4" t="s">
+      <c r="U16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S16" s="4" t="s">
+      <c r="V16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T16" s="5" t="s">
+      <c r="W16" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="17" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A17" s="44" t="s">
+    <row r="17" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A17" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B17" s="9" t="s">
@@ -3356,7 +3967,7 @@
         <v>56</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>57</v>
@@ -3365,32 +3976,41 @@
         <v>57</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>57</v>
+        <v>416</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>57</v>
+        <v>478</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>57</v>
+        <v>479</v>
       </c>
       <c r="P17" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T17" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="R17" s="4" t="s">
+      <c r="U17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S17" s="4" t="s">
+      <c r="V17" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T17" s="5" t="s">
+      <c r="W17" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A18" s="44" t="s">
+    <row r="18" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A18" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B18" s="9" t="s">
@@ -3418,7 +4038,7 @@
         <v>56</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>57</v>
@@ -3427,32 +4047,41 @@
         <v>57</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>57</v>
+        <v>416</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>57</v>
+        <v>480</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>57</v>
+        <v>481</v>
       </c>
       <c r="P18" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T18" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="R18" s="4" t="s">
+      <c r="U18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S18" s="4" t="s">
+      <c r="V18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T18" s="5" t="s">
+      <c r="W18" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A19" s="44" t="s">
+    <row r="19" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A19" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B19" s="9" t="s">
@@ -3480,7 +4109,7 @@
         <v>56</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>57</v>
@@ -3489,32 +4118,41 @@
         <v>57</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>57</v>
+        <v>436</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>57</v>
+        <v>482</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>57</v>
+        <v>483</v>
       </c>
       <c r="P19" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T19" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="R19" s="4" t="s">
+      <c r="U19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="S19" s="4" t="s">
+      <c r="V19" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="T19" s="5" t="s">
+      <c r="W19" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A20" s="44" t="s">
+    <row r="20" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A20" s="39" t="s">
         <v>57</v>
       </c>
       <c r="B20" s="9" t="s">
@@ -3524,7 +4162,7 @@
         <v>23</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>122</v>
+        <v>486</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>24</v>
@@ -3542,7 +4180,7 @@
         <v>56</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>57</v>
@@ -3551,42 +4189,51 @@
         <v>57</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>57</v>
+        <v>436</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>57</v>
+        <v>484</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>57</v>
+        <v>485</v>
       </c>
       <c r="P20" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T20" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="U20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V20" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W20" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="R20" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S20" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T20" s="5" t="s">
+    </row>
+    <row r="21" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A21" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B21" s="9" t="s">
         <v>124</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A21" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B21" s="9" t="s">
-        <v>125</v>
       </c>
       <c r="C21" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>24</v>
@@ -3604,7 +4251,7 @@
         <v>56</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>57</v>
@@ -3613,42 +4260,51 @@
         <v>57</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>57</v>
+        <v>487</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>57</v>
+        <v>488</v>
       </c>
       <c r="P21" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q21" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R21" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S21" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T21" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="U21" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V21" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W21" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="R21" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S21" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T21" s="5" t="s">
+    </row>
+    <row r="22" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A22" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B22" s="9" t="s">
         <v>128</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A22" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>129</v>
       </c>
       <c r="C22" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>24</v>
@@ -3666,7 +4322,7 @@
         <v>56</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>57</v>
@@ -3675,42 +4331,51 @@
         <v>57</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>57</v>
+        <v>392</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>57</v>
+        <v>489</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>57</v>
+        <v>490</v>
       </c>
       <c r="P22" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q22" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R22" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S22" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T22" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="U22" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V22" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W22" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="R22" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S22" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T22" s="5" t="s">
+    </row>
+    <row r="23" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A23" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="9" t="s">
         <v>132</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A23" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>133</v>
       </c>
       <c r="C23" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>24</v>
@@ -3728,7 +4393,7 @@
         <v>56</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>57</v>
@@ -3737,42 +4402,51 @@
         <v>57</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>57</v>
+        <v>420</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>57</v>
+        <v>491</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>57</v>
+        <v>492</v>
       </c>
       <c r="P23" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q23" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R23" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S23" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T23" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="U23" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V23" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W23" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="R23" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S23" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T23" s="5" t="s">
+    </row>
+    <row r="24" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A24" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B24" s="9" t="s">
         <v>136</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A24" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>137</v>
       </c>
       <c r="C24" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>27</v>
@@ -3790,7 +4464,7 @@
         <v>56</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>57</v>
@@ -3799,42 +4473,51 @@
         <v>57</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>57</v>
+        <v>392</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>57</v>
+        <v>502</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>57</v>
+        <v>503</v>
       </c>
       <c r="P24" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T24" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="U24" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V24" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W24" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="R24" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S24" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T24" s="5" t="s">
+    </row>
+    <row r="25" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A25" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="9" t="s">
         <v>140</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A25" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>141</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>24</v>
@@ -3852,7 +4535,7 @@
         <v>56</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>57</v>
@@ -3860,43 +4543,46 @@
       <c r="L25" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M25" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N25" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O25" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M25" s="4"/>
+      <c r="N25" s="4"/>
+      <c r="O25" s="4"/>
       <c r="P25" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q25" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R25" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S25" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T25" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="U25" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V25" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W25" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="R25" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S25" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T25" s="5" t="s">
+    </row>
+    <row r="26" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A26" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="9" t="s">
         <v>144</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A26" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="9" t="s">
-        <v>145</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>24</v>
@@ -3914,7 +4600,7 @@
         <v>56</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>57</v>
@@ -3922,43 +4608,46 @@
       <c r="L26" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O26" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M26" s="4"/>
+      <c r="N26" s="4"/>
+      <c r="O26" s="4"/>
       <c r="P26" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T26" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="U26" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V26" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W26" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="R26" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S26" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T26" s="5" t="s">
+    </row>
+    <row r="27" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A27" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="9" t="s">
         <v>148</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A27" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="9" t="s">
-        <v>149</v>
       </c>
       <c r="C27" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>27</v>
@@ -3976,7 +4665,7 @@
         <v>56</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>57</v>
@@ -3984,43 +4673,46 @@
       <c r="L27" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M27" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N27" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O27" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M27" s="4"/>
+      <c r="N27" s="4"/>
+      <c r="O27" s="4"/>
       <c r="P27" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T27" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="U27" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V27" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W27" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="R27" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S27" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T27" s="5" t="s">
+    </row>
+    <row r="28" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A28" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B28" s="9" t="s">
         <v>152</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A28" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B28" s="9" t="s">
-        <v>153</v>
       </c>
       <c r="C28" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>24</v>
@@ -4038,7 +4730,7 @@
         <v>56</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>57</v>
@@ -4046,43 +4738,46 @@
       <c r="L28" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O28" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M28" s="4"/>
+      <c r="N28" s="4"/>
+      <c r="O28" s="4"/>
       <c r="P28" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T28" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="U28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V28" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W28" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="R28" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S28" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T28" s="5" t="s">
+    </row>
+    <row r="29" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A29" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" s="9" t="s">
         <v>156</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A29" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B29" s="9" t="s">
-        <v>157</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>24</v>
@@ -4100,7 +4795,7 @@
         <v>56</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>57</v>
@@ -4108,43 +4803,46 @@
       <c r="L29" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O29" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M29" s="4"/>
+      <c r="N29" s="4"/>
+      <c r="O29" s="4"/>
       <c r="P29" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T29" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="U29" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V29" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W29" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="R29" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S29" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T29" s="5" t="s">
+    </row>
+    <row r="30" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A30" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B30" s="9" t="s">
         <v>160</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A30" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>161</v>
       </c>
       <c r="C30" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>27</v>
@@ -4162,7 +4860,7 @@
         <v>56</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>57</v>
@@ -4170,43 +4868,46 @@
       <c r="L30" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M30" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N30" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O30" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M30" s="4"/>
+      <c r="N30" s="4"/>
+      <c r="O30" s="4"/>
       <c r="P30" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T30" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="U30" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V30" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W30" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="R30" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S30" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T30" s="5" t="s">
+    </row>
+    <row r="31" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A31" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B31" s="9" t="s">
         <v>164</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A31" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="C31" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>29</v>
@@ -4224,7 +4925,7 @@
         <v>56</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>57</v>
@@ -4232,43 +4933,46 @@
       <c r="L31" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M31" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N31" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O31" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M31" s="4"/>
+      <c r="N31" s="4"/>
+      <c r="O31" s="4"/>
       <c r="P31" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q31" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R31" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S31" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T31" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="U31" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V31" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W31" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="R31" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S31" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T31" s="5" t="s">
+    </row>
+    <row r="32" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A32" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="9" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A32" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>169</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>27</v>
@@ -4286,7 +4990,7 @@
         <v>56</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>57</v>
@@ -4294,43 +4998,46 @@
       <c r="L32" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M32" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N32" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O32" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M32" s="4"/>
+      <c r="N32" s="4"/>
+      <c r="O32" s="4"/>
       <c r="P32" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T32" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="U32" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V32" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W32" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="R32" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S32" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T32" s="5" t="s">
+    </row>
+    <row r="33" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A33" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="9" t="s">
         <v>172</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A33" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>173</v>
       </c>
       <c r="C33" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>24</v>
@@ -4348,7 +5055,7 @@
         <v>56</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>57</v>
@@ -4356,43 +5063,46 @@
       <c r="L33" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M33" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N33" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O33" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M33" s="4"/>
+      <c r="N33" s="4"/>
+      <c r="O33" s="4"/>
       <c r="P33" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q33" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R33" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S33" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T33" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="U33" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V33" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W33" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="R33" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S33" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T33" s="5" t="s">
+    </row>
+    <row r="34" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A34" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="9" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A34" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>177</v>
       </c>
       <c r="C34" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>24</v>
@@ -4410,7 +5120,7 @@
         <v>56</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>57</v>
@@ -4418,43 +5128,46 @@
       <c r="L34" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M34" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N34" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O34" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M34" s="4"/>
+      <c r="N34" s="4"/>
+      <c r="O34" s="4"/>
       <c r="P34" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q34" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R34" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S34" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T34" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="U34" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V34" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W34" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="R34" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S34" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T34" s="5" t="s">
+    </row>
+    <row r="35" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A35" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="9" t="s">
         <v>180</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A35" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>181</v>
       </c>
       <c r="C35" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>27</v>
@@ -4472,7 +5185,7 @@
         <v>56</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>57</v>
@@ -4480,43 +5193,46 @@
       <c r="L35" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M35" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N35" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O35" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M35" s="4"/>
+      <c r="N35" s="4"/>
+      <c r="O35" s="4"/>
       <c r="P35" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q35" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R35" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S35" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T35" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="U35" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V35" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W35" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="R35" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S35" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T35" s="5" t="s">
+    </row>
+    <row r="36" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A36" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="9" t="s">
         <v>184</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A36" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" s="9" t="s">
-        <v>185</v>
       </c>
       <c r="C36" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>27</v>
@@ -4534,7 +5250,7 @@
         <v>56</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>57</v>
@@ -4542,43 +5258,46 @@
       <c r="L36" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M36" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N36" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O36" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M36" s="4"/>
+      <c r="N36" s="4"/>
+      <c r="O36" s="4"/>
       <c r="P36" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q36" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R36" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S36" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T36" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="U36" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V36" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W36" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="R36" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S36" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T36" s="5" t="s">
+    </row>
+    <row r="37" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A37" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="9" t="s">
         <v>188</v>
-      </c>
-    </row>
-    <row r="37" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A37" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" s="9" t="s">
-        <v>189</v>
       </c>
       <c r="C37" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>27</v>
@@ -4596,7 +5315,7 @@
         <v>56</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>57</v>
@@ -4604,43 +5323,46 @@
       <c r="L37" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M37" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N37" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O37" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M37" s="4"/>
+      <c r="N37" s="4"/>
+      <c r="O37" s="4"/>
       <c r="P37" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q37" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R37" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S37" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T37" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="U37" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V37" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W37" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="R37" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S37" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T37" s="5" t="s">
+    </row>
+    <row r="38" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A38" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="9" t="s">
         <v>192</v>
-      </c>
-    </row>
-    <row r="38" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A38" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="9" t="s">
-        <v>193</v>
       </c>
       <c r="C38" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>27</v>
@@ -4658,7 +5380,7 @@
         <v>56</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>57</v>
@@ -4666,43 +5388,46 @@
       <c r="L38" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M38" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N38" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O38" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M38" s="4"/>
+      <c r="N38" s="4"/>
+      <c r="O38" s="4"/>
       <c r="P38" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q38" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R38" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S38" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T38" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="U38" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V38" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W38" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="R38" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S38" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T38" s="5" t="s">
+    </row>
+    <row r="39" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A39" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="9" t="s">
         <v>196</v>
-      </c>
-    </row>
-    <row r="39" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A39" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="9" t="s">
-        <v>197</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>24</v>
@@ -4720,7 +5445,7 @@
         <v>56</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>57</v>
@@ -4728,43 +5453,46 @@
       <c r="L39" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M39" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N39" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O39" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M39" s="4"/>
+      <c r="N39" s="4"/>
+      <c r="O39" s="4"/>
       <c r="P39" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q39" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R39" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S39" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T39" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="U39" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V39" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W39" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="R39" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S39" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T39" s="5" t="s">
+    </row>
+    <row r="40" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A40" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="9" t="s">
         <v>200</v>
-      </c>
-    </row>
-    <row r="40" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A40" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>201</v>
       </c>
       <c r="C40" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>24</v>
@@ -4782,7 +5510,7 @@
         <v>56</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>57</v>
@@ -4790,43 +5518,46 @@
       <c r="L40" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M40" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N40" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O40" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M40" s="4"/>
+      <c r="N40" s="4"/>
+      <c r="O40" s="4"/>
       <c r="P40" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q40" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R40" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S40" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T40" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="U40" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V40" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W40" s="5" t="s">
         <v>203</v>
       </c>
-      <c r="R40" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S40" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T40" s="5" t="s">
+    </row>
+    <row r="41" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A41" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" s="9" t="s">
         <v>204</v>
-      </c>
-    </row>
-    <row r="41" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A41" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B41" s="9" t="s">
-        <v>205</v>
       </c>
       <c r="C41" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>27</v>
@@ -4844,7 +5575,7 @@
         <v>56</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>57</v>
@@ -4852,43 +5583,46 @@
       <c r="L41" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M41" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N41" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O41" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M41" s="4"/>
+      <c r="N41" s="4"/>
+      <c r="O41" s="4"/>
       <c r="P41" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q41" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R41" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S41" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T41" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="U41" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V41" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W41" s="5" t="s">
         <v>207</v>
       </c>
-      <c r="R41" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S41" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T41" s="5" t="s">
+    </row>
+    <row r="42" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A42" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="9" t="s">
         <v>208</v>
-      </c>
-    </row>
-    <row r="42" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A42" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42" s="9" t="s">
-        <v>209</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>23</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>24</v>
@@ -4906,7 +5640,7 @@
         <v>56</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>57</v>
@@ -4914,43 +5648,46 @@
       <c r="L42" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M42" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N42" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O42" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M42" s="4"/>
+      <c r="N42" s="4"/>
+      <c r="O42" s="4"/>
       <c r="P42" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q42" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R42" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S42" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T42" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="U42" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V42" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W42" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="R42" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S42" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T42" s="5" t="s">
+    </row>
+    <row r="43" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A43" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="9" t="s">
         <v>212</v>
-      </c>
-    </row>
-    <row r="43" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A43" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B43" s="9" t="s">
-        <v>213</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>24</v>
@@ -4968,7 +5705,7 @@
         <v>56</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>57</v>
@@ -4976,43 +5713,46 @@
       <c r="L43" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M43" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N43" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O43" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M43" s="4"/>
+      <c r="N43" s="4"/>
+      <c r="O43" s="4"/>
       <c r="P43" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q43" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R43" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S43" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T43" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="U43" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V43" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W43" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="R43" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S43" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T43" s="5" t="s">
+    </row>
+    <row r="44" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A44" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="9" t="s">
         <v>216</v>
-      </c>
-    </row>
-    <row r="44" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A44" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B44" s="9" t="s">
-        <v>217</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>24</v>
@@ -5030,7 +5770,7 @@
         <v>56</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>57</v>
@@ -5038,43 +5778,46 @@
       <c r="L44" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M44" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N44" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O44" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M44" s="4"/>
+      <c r="N44" s="4"/>
+      <c r="O44" s="4"/>
       <c r="P44" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T44" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="U44" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V44" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W44" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="R44" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S44" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T44" s="5" t="s">
+    </row>
+    <row r="45" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A45" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" s="9" t="s">
         <v>220</v>
-      </c>
-    </row>
-    <row r="45" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A45" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B45" s="9" t="s">
-        <v>221</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>24</v>
@@ -5092,7 +5835,7 @@
         <v>56</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>57</v>
@@ -5100,43 +5843,46 @@
       <c r="L45" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M45" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N45" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O45" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M45" s="4"/>
+      <c r="N45" s="4"/>
+      <c r="O45" s="4"/>
       <c r="P45" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q45" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R45" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S45" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T45" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="U45" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V45" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W45" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="R45" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S45" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T45" s="5" t="s">
+    </row>
+    <row r="46" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A46" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="9" t="s">
         <v>224</v>
-      </c>
-    </row>
-    <row r="46" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A46" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B46" s="9" t="s">
-        <v>225</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>27</v>
@@ -5154,7 +5900,7 @@
         <v>56</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>57</v>
@@ -5162,43 +5908,46 @@
       <c r="L46" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M46" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N46" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O46" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M46" s="4"/>
+      <c r="N46" s="4"/>
+      <c r="O46" s="4"/>
       <c r="P46" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q46" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R46" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S46" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T46" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="U46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V46" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W46" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="R46" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S46" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T46" s="5" t="s">
+    </row>
+    <row r="47" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A47" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" s="9" t="s">
         <v>228</v>
-      </c>
-    </row>
-    <row r="47" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A47" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="9" t="s">
-        <v>229</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>24</v>
@@ -5216,7 +5965,7 @@
         <v>56</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>57</v>
@@ -5224,43 +5973,46 @@
       <c r="L47" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M47" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N47" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O47" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M47" s="4"/>
+      <c r="N47" s="4"/>
+      <c r="O47" s="4"/>
       <c r="P47" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q47" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R47" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S47" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T47" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="U47" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V47" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W47" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="R47" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S47" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T47" s="5" t="s">
+    </row>
+    <row r="48" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A48" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="9" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="48" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A48" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B48" s="9" t="s">
-        <v>233</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>24</v>
@@ -5278,7 +6030,7 @@
         <v>56</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>57</v>
@@ -5286,43 +6038,46 @@
       <c r="L48" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M48" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N48" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O48" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
       <c r="P48" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q48" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R48" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S48" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T48" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="U48" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V48" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W48" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="R48" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S48" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T48" s="5" t="s">
+    </row>
+    <row r="49" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A49" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="9" t="s">
         <v>236</v>
-      </c>
-    </row>
-    <row r="49" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A49" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="C49" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>24</v>
@@ -5340,7 +6095,7 @@
         <v>56</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>57</v>
@@ -5348,43 +6103,46 @@
       <c r="L49" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M49" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N49" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O49" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
       <c r="P49" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T49" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="U49" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V49" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W49" s="5" t="s">
         <v>239</v>
       </c>
-      <c r="R49" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S49" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T49" s="5" t="s">
+    </row>
+    <row r="50" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A50" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="9" t="s">
         <v>240</v>
-      </c>
-    </row>
-    <row r="50" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A50" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="9" t="s">
-        <v>241</v>
       </c>
       <c r="C50" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>24</v>
@@ -5402,7 +6160,7 @@
         <v>56</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>57</v>
@@ -5410,43 +6168,46 @@
       <c r="L50" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M50" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N50" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O50" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
       <c r="P50" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q50" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R50" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S50" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T50" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="U50" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V50" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W50" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="R50" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S50" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T50" s="5" t="s">
+    </row>
+    <row r="51" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A51" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="9" t="s">
         <v>244</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A51" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="9" t="s">
-        <v>245</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>24</v>
@@ -5464,7 +6225,7 @@
         <v>56</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>57</v>
@@ -5472,43 +6233,46 @@
       <c r="L51" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M51" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N51" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O51" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
       <c r="P51" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q51" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R51" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S51" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T51" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="U51" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V51" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W51" s="5" t="s">
         <v>247</v>
       </c>
-      <c r="R51" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S51" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T51" s="5" t="s">
+    </row>
+    <row r="52" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A52" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="9" t="s">
         <v>248</v>
-      </c>
-    </row>
-    <row r="52" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A52" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B52" s="9" t="s">
-        <v>249</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>24</v>
@@ -5526,7 +6290,7 @@
         <v>56</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>57</v>
@@ -5534,43 +6298,46 @@
       <c r="L52" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M52" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N52" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O52" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
       <c r="P52" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q52" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R52" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S52" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T52" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="U52" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V52" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W52" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="R52" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S52" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T52" s="5" t="s">
+    </row>
+    <row r="53" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A53" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="9" t="s">
         <v>252</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A53" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B53" s="9" t="s">
-        <v>253</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>27</v>
@@ -5588,7 +6355,7 @@
         <v>56</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>57</v>
@@ -5596,43 +6363,46 @@
       <c r="L53" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M53" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N53" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O53" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M53" s="4"/>
+      <c r="N53" s="4"/>
+      <c r="O53" s="4"/>
       <c r="P53" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q53" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R53" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S53" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T53" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="U53" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V53" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W53" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="R53" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S53" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T53" s="5" t="s">
+    </row>
+    <row r="54" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A54" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54" s="9" t="s">
         <v>256</v>
-      </c>
-    </row>
-    <row r="54" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A54" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B54" s="9" t="s">
-        <v>257</v>
       </c>
       <c r="C54" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>24</v>
@@ -5650,7 +6420,7 @@
         <v>56</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>57</v>
@@ -5658,43 +6428,46 @@
       <c r="L54" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M54" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N54" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O54" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M54" s="4"/>
+      <c r="N54" s="4"/>
+      <c r="O54" s="4"/>
       <c r="P54" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q54" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R54" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S54" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T54" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="U54" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V54" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W54" s="5" t="s">
         <v>259</v>
       </c>
-      <c r="R54" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S54" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T54" s="5" t="s">
+    </row>
+    <row r="55" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A55" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="9" t="s">
         <v>260</v>
-      </c>
-    </row>
-    <row r="55" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A55" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B55" s="9" t="s">
-        <v>261</v>
       </c>
       <c r="C55" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>24</v>
@@ -5712,7 +6485,7 @@
         <v>56</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>57</v>
@@ -5720,43 +6493,46 @@
       <c r="L55" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M55" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N55" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O55" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M55" s="4"/>
+      <c r="N55" s="4"/>
+      <c r="O55" s="4"/>
       <c r="P55" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q55" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R55" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S55" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T55" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="U55" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V55" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W55" s="5" t="s">
         <v>263</v>
       </c>
-      <c r="R55" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S55" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T55" s="5" t="s">
+    </row>
+    <row r="56" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A56" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="9" t="s">
         <v>264</v>
-      </c>
-    </row>
-    <row r="56" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A56" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B56" s="9" t="s">
-        <v>265</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>24</v>
@@ -5774,7 +6550,7 @@
         <v>56</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>57</v>
@@ -5782,43 +6558,46 @@
       <c r="L56" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M56" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N56" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O56" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M56" s="4"/>
+      <c r="N56" s="4"/>
+      <c r="O56" s="4"/>
       <c r="P56" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q56" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R56" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S56" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T56" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="U56" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V56" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W56" s="5" t="s">
         <v>267</v>
       </c>
-      <c r="R56" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S56" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T56" s="5" t="s">
+    </row>
+    <row r="57" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A57" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="9" t="s">
         <v>268</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A57" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B57" s="9" t="s">
-        <v>269</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>27</v>
@@ -5836,7 +6615,7 @@
         <v>56</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>57</v>
@@ -5844,43 +6623,46 @@
       <c r="L57" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M57" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N57" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O57" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M57" s="4"/>
+      <c r="N57" s="4"/>
+      <c r="O57" s="4"/>
       <c r="P57" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q57" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R57" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S57" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T57" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="U57" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V57" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W57" s="5" t="s">
         <v>271</v>
       </c>
-      <c r="R57" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S57" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T57" s="5" t="s">
+    </row>
+    <row r="58" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A58" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="9" t="s">
         <v>272</v>
-      </c>
-    </row>
-    <row r="58" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A58" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="9" t="s">
-        <v>273</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>24</v>
@@ -5898,7 +6680,7 @@
         <v>56</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>57</v>
@@ -5906,43 +6688,46 @@
       <c r="L58" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M58" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N58" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O58" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M58" s="4"/>
+      <c r="N58" s="4"/>
+      <c r="O58" s="4"/>
       <c r="P58" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q58" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R58" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S58" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T58" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="U58" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V58" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W58" s="5" t="s">
         <v>275</v>
       </c>
-      <c r="R58" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S58" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T58" s="5" t="s">
+    </row>
+    <row r="59" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A59" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="9" t="s">
         <v>276</v>
-      </c>
-    </row>
-    <row r="59" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A59" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B59" s="9" t="s">
-        <v>277</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>26</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>24</v>
@@ -5960,7 +6745,7 @@
         <v>56</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>57</v>
@@ -5968,43 +6753,46 @@
       <c r="L59" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M59" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="N59" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="O59" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="M59" s="4"/>
+      <c r="N59" s="4"/>
+      <c r="O59" s="4"/>
       <c r="P59" s="4" t="s">
         <v>57</v>
       </c>
       <c r="Q59" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="R59" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="S59" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="T59" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="U59" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="V59" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="W59" s="5" t="s">
         <v>279</v>
       </c>
-      <c r="R59" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="S59" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="T59" s="5" t="s">
+    </row>
+    <row r="60" spans="1:23" ht="51.95" customHeight="1">
+      <c r="A60" s="39" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60" s="10" t="s">
         <v>280</v>
-      </c>
-    </row>
-    <row r="60" spans="1:20" ht="51.95" customHeight="1">
-      <c r="A60" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="B60" s="10" t="s">
-        <v>281</v>
       </c>
       <c r="C60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>24</v>
@@ -6022,7 +6810,7 @@
         <v>56</v>
       </c>
       <c r="J60" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="K60" s="6" t="s">
         <v>57</v>
@@ -6030,48 +6818,51 @@
       <c r="L60" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="M60" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="N60" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="O60" s="6" t="s">
-        <v>57</v>
-      </c>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+      <c r="O60" s="6"/>
       <c r="P60" s="6" t="s">
         <v>57</v>
       </c>
       <c r="Q60" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="R60" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="S60" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="T60" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="U60" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="V60" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="W60" s="7" t="s">
         <v>283</v>
-      </c>
-      <c r="R60" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="S60" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="T60" s="7" t="s">
-        <v>284</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:T1"/>
-    <mergeCell ref="B2:T2"/>
+    <mergeCell ref="B1:W1"/>
+    <mergeCell ref="B2:W2"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:T60">
-    <cfRule type="expression" dxfId="3" priority="3">
+  <conditionalFormatting sqref="A5:A60">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>$E5="Must"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R5:R60">
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="Pending"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A5:A60">
-    <cfRule type="expression" dxfId="0" priority="1">
+  <conditionalFormatting sqref="B5:W60">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>$E5="Must"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="U5:U60">
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Pending"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" sqref="B5:B60" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -6097,33 +6888,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+    </row>
+    <row r="2" spans="1:4" ht="21" customHeight="1">
+      <c r="A2" s="44" t="s">
         <v>285</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-    </row>
-    <row r="2" spans="1:4" ht="21" customHeight="1">
-      <c r="A2" s="40" t="s">
-        <v>286</v>
-      </c>
-      <c r="B2" s="40"/>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
     </row>
     <row r="4" spans="1:4" ht="15">
       <c r="A4" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="B4" s="11" t="s">
         <v>287</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="C4" s="11" t="s">
         <v>288</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D4" s="11" t="s">
         <v>289</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="38.1" customHeight="1">
@@ -6131,13 +6922,13 @@
         <v>39</v>
       </c>
       <c r="B5" s="12" t="s">
+        <v>290</v>
+      </c>
+      <c r="C5" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="D5" s="13" t="s">
         <v>292</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="38.1" customHeight="1">
@@ -6145,13 +6936,13 @@
         <v>40</v>
       </c>
       <c r="B6" s="14" t="s">
+        <v>293</v>
+      </c>
+      <c r="C6" s="14" t="s">
         <v>294</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="D6" s="15" t="s">
         <v>295</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="38.1" customHeight="1">
@@ -6159,13 +6950,13 @@
         <v>41</v>
       </c>
       <c r="B7" s="14" t="s">
+        <v>296</v>
+      </c>
+      <c r="C7" s="14" t="s">
         <v>297</v>
       </c>
-      <c r="C7" s="14" t="s">
+      <c r="D7" s="15" t="s">
         <v>298</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="38.1" customHeight="1">
@@ -6173,13 +6964,13 @@
         <v>42</v>
       </c>
       <c r="B8" s="14" t="s">
+        <v>299</v>
+      </c>
+      <c r="C8" s="14" t="s">
         <v>300</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="D8" s="15" t="s">
         <v>301</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="38.1" customHeight="1">
@@ -6187,13 +6978,13 @@
         <v>43</v>
       </c>
       <c r="B9" s="14" t="s">
+        <v>302</v>
+      </c>
+      <c r="C9" s="14" t="s">
         <v>303</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="D9" s="15" t="s">
         <v>304</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="38.1" customHeight="1">
@@ -6204,10 +6995,10 @@
         <v>44</v>
       </c>
       <c r="C10" s="14" t="s">
+        <v>305</v>
+      </c>
+      <c r="D10" s="15" t="s">
         <v>306</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="38.1" customHeight="1">
@@ -6215,13 +7006,13 @@
         <v>45</v>
       </c>
       <c r="B11" s="14" t="s">
+        <v>307</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>308</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="D11" s="15" t="s">
         <v>309</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="38.1" customHeight="1">
@@ -6229,13 +7020,13 @@
         <v>46</v>
       </c>
       <c r="B12" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>311</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="D12" s="15" t="s">
         <v>312</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="38.1" customHeight="1">
@@ -6243,13 +7034,13 @@
         <v>47</v>
       </c>
       <c r="B13" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>314</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="D13" s="15" t="s">
         <v>315</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="38.1" customHeight="1">
@@ -6257,13 +7048,13 @@
         <v>48</v>
       </c>
       <c r="B14" s="14" t="s">
+        <v>316</v>
+      </c>
+      <c r="C14" s="14" t="s">
         <v>317</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="D14" s="15" t="s">
         <v>318</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>319</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="38.1" customHeight="1">
@@ -6271,13 +7062,13 @@
         <v>50</v>
       </c>
       <c r="B15" s="14" t="s">
+        <v>319</v>
+      </c>
+      <c r="C15" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="D15" s="15" t="s">
         <v>321</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="38.1" customHeight="1">
@@ -6285,13 +7076,13 @@
         <v>51</v>
       </c>
       <c r="B16" s="14" t="s">
+        <v>322</v>
+      </c>
+      <c r="C16" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="D16" s="15" t="s">
         <v>324</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="38.1" customHeight="1">
@@ -6299,13 +7090,13 @@
         <v>37</v>
       </c>
       <c r="B17" s="14" t="s">
+        <v>325</v>
+      </c>
+      <c r="C17" s="14" t="s">
         <v>326</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="D17" s="15" t="s">
         <v>327</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="38.1" customHeight="1">
@@ -6313,22 +7104,22 @@
         <v>38</v>
       </c>
       <c r="B18" s="16" t="s">
+        <v>328</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>329</v>
       </c>
-      <c r="C18" s="16" t="s">
+      <c r="D18" s="17" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="42" customHeight="1">
+      <c r="A20" s="45" t="s">
         <v>330</v>
       </c>
-      <c r="D18" s="17" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="42" customHeight="1">
-      <c r="A20" s="41" t="s">
-        <v>331</v>
-      </c>
-      <c r="B20" s="42"/>
-      <c r="C20" s="42"/>
-      <c r="D20" s="43"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -6338,4 +7129,328 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B7B1DBE-C4F7-4329-8F3C-A2139FB742EE}">
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="55.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="30.625" customWidth="1"/>
+    <col min="3" max="3" width="53.5" customWidth="1"/>
+    <col min="4" max="4" width="51" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15">
+      <c r="A1" s="40" t="s">
+        <v>388</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>389</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>390</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="28.5">
+      <c r="A2" s="42" t="s">
+        <v>392</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>393</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>394</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="28.5">
+      <c r="A3" s="42" t="s">
+        <v>396</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>397</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>398</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="28.5">
+      <c r="A4" s="42" t="s">
+        <v>400</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>401</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>402</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15">
+      <c r="A5" s="42" t="s">
+        <v>404</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>405</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>406</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="28.5">
+      <c r="A6" s="42" t="s">
+        <v>408</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>409</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>410</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15">
+      <c r="A7" s="42" t="s">
+        <v>412</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>413</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>414</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15">
+      <c r="A8" s="42" t="s">
+        <v>416</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>417</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>418</v>
+      </c>
+      <c r="D8" s="41" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="28.5">
+      <c r="A9" s="42" t="s">
+        <v>420</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>421</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>422</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15">
+      <c r="A10" s="42" t="s">
+        <v>424</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>425</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>426</v>
+      </c>
+      <c r="D10" s="41" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="30">
+      <c r="A11" s="42" t="s">
+        <v>428</v>
+      </c>
+      <c r="B11" s="42" t="s">
+        <v>429</v>
+      </c>
+      <c r="C11" s="41" t="s">
+        <v>430</v>
+      </c>
+      <c r="D11" s="41" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="28.5">
+      <c r="A12" s="42" t="s">
+        <v>432</v>
+      </c>
+      <c r="B12" s="42" t="s">
+        <v>433</v>
+      </c>
+      <c r="C12" s="41" t="s">
+        <v>434</v>
+      </c>
+      <c r="D12" s="41" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="30">
+      <c r="A13" s="42" t="s">
+        <v>436</v>
+      </c>
+      <c r="B13" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="C13" s="41" t="s">
+        <v>438</v>
+      </c>
+      <c r="D13" s="41" t="s">
+        <v>439</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE6F4BC9-6BA0-49D2-B9EC-3326267B383F}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultColWidth="27.125" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="67.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="15">
+      <c r="A1" s="40" t="s">
+        <v>447</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>448</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="57">
+      <c r="A2" s="42" t="s">
+        <v>449</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>471</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="42.75">
+      <c r="A3" s="42" t="s">
+        <v>450</v>
+      </c>
+      <c r="B3" s="42" t="s">
+        <v>456</v>
+      </c>
+      <c r="C3" s="41" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="42.75">
+      <c r="A4" s="42" t="s">
+        <v>450</v>
+      </c>
+      <c r="B4" s="42" t="s">
+        <v>473</v>
+      </c>
+      <c r="C4" s="41" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="42.75">
+      <c r="A5" s="42" t="s">
+        <v>450</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>470</v>
+      </c>
+      <c r="C5" s="41" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="30">
+      <c r="A6" s="42" t="s">
+        <v>451</v>
+      </c>
+      <c r="B6" s="42" t="s">
+        <v>452</v>
+      </c>
+      <c r="C6" s="41" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="30">
+      <c r="A7" s="42" t="s">
+        <v>451</v>
+      </c>
+      <c r="B7" s="42" t="s">
+        <v>466</v>
+      </c>
+      <c r="C7" s="41" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30">
+      <c r="A8" s="42" t="s">
+        <v>451</v>
+      </c>
+      <c r="B8" s="42" t="s">
+        <v>459</v>
+      </c>
+      <c r="C8" s="41" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="42.75">
+      <c r="A9" s="42" t="s">
+        <v>451</v>
+      </c>
+      <c r="B9" s="42" t="s">
+        <v>455</v>
+      </c>
+      <c r="C9" s="41" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="42.75">
+      <c r="A10" s="42" t="s">
+        <v>451</v>
+      </c>
+      <c r="B10" s="42" t="s">
+        <v>472</v>
+      </c>
+      <c r="C10" s="41" t="s">
+        <v>501</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
+++ b/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
@@ -8,17 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d752cb73b61fc091/Desktop/linuxlabs/projectredstone/docs/project-management/02_Business_Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="262" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{309A0387-D55D-4B4E-A611-398DC9D6328D}"/>
+  <xr:revisionPtr revIDLastSave="472" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5783A1C2-7965-49AB-ABD3-D35792B2B3D4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" firstSheet="2" activeTab="4" xr2:uid="{BD0B86D2-9AC1-421E-A95D-1B17A25780EE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="RTM" sheetId="2" r:id="rId2"/>
     <sheet name="Legend &amp; Reference" sheetId="3" r:id="rId3"/>
     <sheet name="Architecture Domains" sheetId="4" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1386" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="550">
   <si>
     <t>Northwind Outdoor Ltd. | RTM Summary</t>
   </si>
@@ -1381,45 +1379,15 @@
     <t>AD-01, AD-02,AD-05</t>
   </si>
   <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>Domain</t>
-  </si>
-  <si>
-    <t>Primary</t>
-  </si>
-  <si>
-    <t>Key Supporting</t>
-  </si>
-  <si>
-    <t>Secondary</t>
-  </si>
-  <si>
-    <t>AD-05 Application &amp; Business Services</t>
-  </si>
-  <si>
     <t xml:space="preserve">AD-03, AD-05, AD-08, </t>
   </si>
   <si>
     <t>AD-11, AD-02, AD-09</t>
   </si>
   <si>
-    <t>AD-03 Identity &amp; Access Architecture</t>
-  </si>
-  <si>
-    <t>AD-08 Security Architecture</t>
-  </si>
-  <si>
     <t>AD-03, AD-05, AD-08</t>
   </si>
   <si>
-    <t>Why it relates</t>
-  </si>
-  <si>
-    <t>AD-09 Observability Architecture</t>
-  </si>
-  <si>
     <t>AD-08, AD-05, AD-10</t>
   </si>
   <si>
@@ -1438,9 +1406,6 @@
     <t>AD-06, AD-09, AD-07</t>
   </si>
   <si>
-    <t>AD-10 Management &amp; Operations Architecture</t>
-  </si>
-  <si>
     <t>AD-10, AD-05, AD-03</t>
   </si>
   <si>
@@ -1448,18 +1413,6 @@
   </si>
   <si>
     <t>AD-10, AD-06, AD-11, AD-02</t>
-  </si>
-  <si>
-    <t>AD-02 Compute &amp; Platform Architecture</t>
-  </si>
-  <si>
-    <t>AD-01 Network Architecture</t>
-  </si>
-  <si>
-    <t>AD-04 Core Infrastructure Services</t>
-  </si>
-  <si>
-    <t>AD-12 Resilience &amp; Availability Architecture</t>
   </si>
   <si>
     <t>AD-10, AD-08, AD-07</t>
@@ -1536,37 +1489,220 @@
     <t>AD-10, AD-05, AD-02, AD-11, AD-12</t>
   </si>
   <si>
-    <t>Logical separation of systems/services is fundamentally a network architecture capability. The network design determines the segmentation model, boundaries and permitted connectivity between segments.</t>
-  </si>
-  <si>
-    <t>Improved security is an explicit outcome. Segmentation should limit unnecessary access and reduce the ability of a compromised system to reach unrelated infrastructure.</t>
-  </si>
-  <si>
-    <t>Operational resilience is also explicit. Segmentation can contain failures, reduce blast radius and separate systems with different operational/security characteristics.</t>
-  </si>
-  <si>
-    <t>Workloads must be placed into appropriate logical network/security zones. The compute architecture therefore needs to support the segmentation model.</t>
-  </si>
-  <si>
-    <t>Service placement and legitimate application communication requirements determine which segments need to communicate.</t>
-  </si>
-  <si>
-    <t>Administrative access across segments, changes to segmentation policy and troubleshooting require controlled operational processes.</t>
-  </si>
-  <si>
-    <t>Cross-segment traffic, denied connections and segment health may need logging/monitoring.</t>
-  </si>
-  <si>
-    <t>Certain access decisions may involve user/admin roles, particularly management access, although segmentation itself is primarily network-based.</t>
-  </si>
-  <si>
-    <t>Shared DNS, DHCP, NTP and similar services may need to operate across multiple segments and therefore influence permitted network flows.</t>
-  </si>
-  <si>
     <t>AD-08, AD-12, AD-02</t>
   </si>
   <si>
     <t>AD-05, AD-10, AD-09, AD-03, AD-04</t>
+  </si>
+  <si>
+    <t>AD-05, AD-03, AD-01</t>
+  </si>
+  <si>
+    <t>AD-08, AD-10, AD-02, AD-09, AD-12</t>
+  </si>
+  <si>
+    <t>AD-12, AD-05, AD-06</t>
+  </si>
+  <si>
+    <t>AD-01, AD-04, AD-08, AD-10, AD-09, AD-07</t>
+  </si>
+  <si>
+    <t>AD-06, AD-01, AD-05</t>
+  </si>
+  <si>
+    <t>AD-03, AD-04, AD-09, AD-10, AD-08, AD-07, AD-12</t>
+  </si>
+  <si>
+    <t>AD-02, AD-08, AD-04</t>
+  </si>
+  <si>
+    <t>AD-01, AD-03, AD-05, AD-06, AD-09, AD-07, AD-12</t>
+  </si>
+  <si>
+    <t>AD-12, AD-07, AD-05</t>
+  </si>
+  <si>
+    <t>AD-02, AD-01, AD-03, AD-04, AD-06, AD-08, AD-09, AD-11</t>
+  </si>
+  <si>
+    <t>AD-10, AD-08, AD-06</t>
+  </si>
+  <si>
+    <t>AD-02, AD-05, AD-01, AD-07, AD-12, AD-03</t>
+  </si>
+  <si>
+    <t>AD-03, AD-08, AD-09</t>
+  </si>
+  <si>
+    <t>AD-05, AD-02, AD-11</t>
+  </si>
+  <si>
+    <t>AD-01, AD-03, AD-10</t>
+  </si>
+  <si>
+    <t>AD-02, AD-08, AD-09, AD-12</t>
+  </si>
+  <si>
+    <t>AD-02, AD-08, AD-09</t>
+  </si>
+  <si>
+    <t>AD-01, AD-05, AD-11</t>
+  </si>
+  <si>
+    <t>AD-08, AD-02, AD-12</t>
+  </si>
+  <si>
+    <t>AD-05, AD-09, AD-07, AD-11</t>
+  </si>
+  <si>
+    <t>AD-02, AD-08, AD-05</t>
+  </si>
+  <si>
+    <t>AD-09, AD-12, AD-11</t>
+  </si>
+  <si>
+    <t>AD-02, AD-03, AD-08</t>
+  </si>
+  <si>
+    <t>AD-05, AD-06, AD-09, AD-07, AD-04, AD-01</t>
+  </si>
+  <si>
+    <t>AD-07, AD-05, AD-06, AD-04, AD-12</t>
+  </si>
+  <si>
+    <t>AD-09, AD-02, AD-06</t>
+  </si>
+  <si>
+    <t>AD-01, AD-05, AD-07, AD-12, AD-04</t>
+  </si>
+  <si>
+    <t>AD-03, AD-09, AD-08</t>
+  </si>
+  <si>
+    <t>AD-10, AD-02, AD-01, AD-05</t>
+  </si>
+  <si>
+    <t>AD-03, AD-02, AD-10</t>
+  </si>
+  <si>
+    <t>AD-01, AD-05, AD-06, AD-09</t>
+  </si>
+  <si>
+    <t>AD-03, AD-08, AD-10</t>
+  </si>
+  <si>
+    <t>AD-05, AD-04, AD-02, AD-09, AD-12</t>
+  </si>
+  <si>
+    <t>AD-09, AD-02, AD-08</t>
+  </si>
+  <si>
+    <t>AD-01, AD-05, AD-03, AD-04, AD-06, AD-07, AD-12, AD-11</t>
+  </si>
+  <si>
+    <t>AD-07 Backup &amp; Recovery, AD-02 Compute &amp; Platform, AD-09 Observability</t>
+  </si>
+  <si>
+    <t>AD-01, AD-04, AD-05, AD-06, AD-10</t>
+  </si>
+  <si>
+    <t>AD-02 Compute &amp; Platform, AD-10 Management &amp; Operations, AD-09 Observability</t>
+  </si>
+  <si>
+    <t>AD-01, AD-04, AD-05, AD-06, AD-07, AD-08</t>
+  </si>
+  <si>
+    <t>AD-06 Storage, AD-09 Observability, AD-01 Network</t>
+  </si>
+  <si>
+    <t>AD-05, AD-10, AD-12</t>
+  </si>
+  <si>
+    <t>AD-06 Storage, AD-01 Network, AD-10 Management &amp; Operations</t>
+  </si>
+  <si>
+    <t>AD-03, AD-04, AD-05, AD-09, AD-12</t>
+  </si>
+  <si>
+    <t>AD-03 Identity &amp; Access, AD-01 Network, AD-10 Management &amp; Operations</t>
+  </si>
+  <si>
+    <t>AD-02, AD-05, AD-06, AD-09, AD-11</t>
+  </si>
+  <si>
+    <t>AD-08 Security, AD-10 Management &amp; Operations, AD-03 Identity &amp; Access</t>
+  </si>
+  <si>
+    <t>AD-02, AD-05, AD-11</t>
+  </si>
+  <si>
+    <t>AD-03 Identity &amp; Access, AD-07 Backup &amp; Recovery, AD-06 Storage</t>
+  </si>
+  <si>
+    <t>AD-05, AD-09, AD-10, AD-11</t>
+  </si>
+  <si>
+    <t>AD-02 Compute &amp; Platform, AD-24-equivalent standardisation via BR-024 / AD-08 Security, AD-09 Observability</t>
+  </si>
+  <si>
+    <t>AD-01, AD-04, AD-05, AD-06, AD-07</t>
+  </si>
+  <si>
+    <t>AD-12 Resilience &amp; Availability, AD-10 Management &amp; Operations, AD-02 Compute &amp; Platform</t>
+  </si>
+  <si>
+    <t>AD-05, AD-06, AD-09, AD-04, AD-03</t>
+  </si>
+  <si>
+    <t>AD-09 Observability, AD-02 Compute &amp; Platform, AD-12 Resilience &amp; Availability</t>
+  </si>
+  <si>
+    <t>AD-05, AD-07, AD-08, AD-03, AD-04</t>
+  </si>
+  <si>
+    <t>AD-02 Compute &amp; Platform, AD-03 Identity &amp; Access, AD-08 Security</t>
+  </si>
+  <si>
+    <t>AD-04, AD-05, AD-09, AD-01</t>
+  </si>
+  <si>
+    <t>AD-05 Application &amp; Business Services, AD-03 Identity &amp; Access, AD-01 Network</t>
+  </si>
+  <si>
+    <t>AD-02, AD-08, AD-10, AD-04</t>
+  </si>
+  <si>
+    <t>AD-10 Management &amp; Operations, AD-09 Observability, AD-03 Identity &amp; Access</t>
+  </si>
+  <si>
+    <t>AD-05, AD-06, AD-07, AD-11</t>
+  </si>
+  <si>
+    <t>AD-10 Management &amp; Operations, AD-08 Security, AD-02 Compute &amp; Platform</t>
+  </si>
+  <si>
+    <t>AD-01, AD-04, AD-05, AD-06, AD-07, AD-12</t>
+  </si>
+  <si>
+    <t>AD-01 Network, AD-10 Management &amp; Operations, AD-11 Integration</t>
+  </si>
+  <si>
+    <t>AD-03, AD-04, AD-05, AD-06, AD-08, AD-09, AD-12</t>
+  </si>
+  <si>
+    <t>AD-02 Compute &amp; Platform, AD-08 Security, AD-09 Observability</t>
+  </si>
+  <si>
+    <t>AD-01, AD-03, AD-04, AD-05, AD-06, AD-07</t>
+  </si>
+  <si>
+    <t>AD-07 Backup &amp; Recovery, AD-10 Management &amp; Operations, AD-02 Compute &amp; Platform</t>
+  </si>
+  <si>
+    <t>AD-05, AD-06, AD-09, AD-08</t>
+  </si>
+  <si>
+    <t>AD-03 Identity &amp; Access, AD-09 Observability, AD-08 Security</t>
   </si>
 </sst>
 </file>
@@ -2945,21 +3081,24 @@
   <dimension ref="A1:W60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="1" max="1" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
-    <col min="7" max="7" width="12" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="11" customWidth="1"/>
-    <col min="9" max="9" width="12" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="18" customWidth="1"/>
-    <col min="11" max="13" width="17" customWidth="1"/>
-    <col min="14" max="14" width="15.25" bestFit="1" customWidth="1"/>
-    <col min="15" max="19" width="17" customWidth="1"/>
+    <col min="5" max="5" width="6.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="3.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.25" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="16" max="19" width="11.5" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="42" customWidth="1"/>
-    <col min="21" max="21" width="22" customWidth="1"/>
-    <col min="22" max="22" width="26" customWidth="1"/>
+    <col min="21" max="21" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="25" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="54" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3269,10 +3408,10 @@
         <v>428</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="P7" s="4" t="s">
         <v>57</v>
@@ -3340,10 +3479,10 @@
         <v>428</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="P8" s="4" t="s">
         <v>57</v>
@@ -3411,10 +3550,10 @@
         <v>400</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="P9" s="4" t="s">
         <v>57</v>
@@ -3482,10 +3621,10 @@
         <v>408</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="P10" s="4" t="s">
         <v>57</v>
@@ -3553,10 +3692,10 @@
         <v>408</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="P11" s="4" t="s">
         <v>57</v>
@@ -3624,10 +3763,10 @@
         <v>420</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="P12" s="4" t="s">
         <v>57</v>
@@ -3695,10 +3834,10 @@
         <v>420</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="P13" s="4" t="s">
         <v>57</v>
@@ -3837,10 +3976,10 @@
         <v>424</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="P15" s="4" t="s">
         <v>57</v>
@@ -3908,10 +4047,10 @@
         <v>420</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>477</v>
+        <v>462</v>
       </c>
       <c r="P16" s="4" t="s">
         <v>57</v>
@@ -3979,10 +4118,10 @@
         <v>416</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>478</v>
+        <v>463</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>479</v>
+        <v>464</v>
       </c>
       <c r="P17" s="4" t="s">
         <v>57</v>
@@ -4050,10 +4189,10 @@
         <v>416</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>480</v>
+        <v>465</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>481</v>
+        <v>466</v>
       </c>
       <c r="P18" s="4" t="s">
         <v>57</v>
@@ -4121,10 +4260,10 @@
         <v>436</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>483</v>
+        <v>468</v>
       </c>
       <c r="P19" s="4" t="s">
         <v>57</v>
@@ -4162,7 +4301,7 @@
         <v>23</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>486</v>
+        <v>471</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>24</v>
@@ -4192,10 +4331,10 @@
         <v>436</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>485</v>
+        <v>470</v>
       </c>
       <c r="P20" s="4" t="s">
         <v>57</v>
@@ -4263,10 +4402,10 @@
         <v>428</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>487</v>
+        <v>472</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>488</v>
+        <v>473</v>
       </c>
       <c r="P21" s="4" t="s">
         <v>57</v>
@@ -4334,10 +4473,10 @@
         <v>392</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>489</v>
+        <v>474</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>490</v>
+        <v>475</v>
       </c>
       <c r="P22" s="4" t="s">
         <v>57</v>
@@ -4405,10 +4544,10 @@
         <v>420</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>491</v>
+        <v>476</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>492</v>
+        <v>477</v>
       </c>
       <c r="P23" s="4" t="s">
         <v>57</v>
@@ -4476,10 +4615,10 @@
         <v>392</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>502</v>
+        <v>478</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>503</v>
+        <v>479</v>
       </c>
       <c r="P24" s="4" t="s">
         <v>57</v>
@@ -4543,9 +4682,15 @@
       <c r="L25" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M25" s="4"/>
-      <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
+      <c r="M25" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="N25" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="O25" s="4" t="s">
+        <v>481</v>
+      </c>
       <c r="P25" s="4" t="s">
         <v>57</v>
       </c>
@@ -4608,9 +4753,15 @@
       <c r="L26" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M26" s="4"/>
-      <c r="N26" s="4"/>
-      <c r="O26" s="4"/>
+      <c r="M26" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="N26" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="O26" s="4" t="s">
+        <v>483</v>
+      </c>
       <c r="P26" s="4" t="s">
         <v>57</v>
       </c>
@@ -4673,9 +4824,15 @@
       <c r="L27" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M27" s="4"/>
-      <c r="N27" s="4"/>
-      <c r="O27" s="4"/>
+      <c r="M27" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="N27" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="O27" s="4" t="s">
+        <v>485</v>
+      </c>
       <c r="P27" s="4" t="s">
         <v>57</v>
       </c>
@@ -4738,9 +4895,15 @@
       <c r="L28" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M28" s="4"/>
-      <c r="N28" s="4"/>
-      <c r="O28" s="4"/>
+      <c r="M28" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N28" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="O28" s="4" t="s">
+        <v>487</v>
+      </c>
       <c r="P28" s="4" t="s">
         <v>57</v>
       </c>
@@ -4803,9 +4966,15 @@
       <c r="L29" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M29" s="4"/>
-      <c r="N29" s="4"/>
-      <c r="O29" s="4"/>
+      <c r="M29" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N29" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="O29" s="4" t="s">
+        <v>489</v>
+      </c>
       <c r="P29" s="4" t="s">
         <v>57</v>
       </c>
@@ -4868,9 +5037,15 @@
       <c r="L30" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M30" s="4"/>
-      <c r="N30" s="4"/>
-      <c r="O30" s="4"/>
+      <c r="M30" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="N30" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="O30" s="4" t="s">
+        <v>491</v>
+      </c>
       <c r="P30" s="4" t="s">
         <v>57</v>
       </c>
@@ -4933,9 +5108,15 @@
       <c r="L31" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
+      <c r="M31" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N31" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="O31" s="4" t="s">
+        <v>493</v>
+      </c>
       <c r="P31" s="4" t="s">
         <v>57</v>
       </c>
@@ -4998,9 +5179,15 @@
       <c r="L32" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
+      <c r="M32" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="N32" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="O32" s="4" t="s">
+        <v>495</v>
+      </c>
       <c r="P32" s="4" t="s">
         <v>57</v>
       </c>
@@ -5063,9 +5250,15 @@
       <c r="L33" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
+      <c r="M33" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N33" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="O33" s="4" t="s">
+        <v>497</v>
+      </c>
       <c r="P33" s="4" t="s">
         <v>57</v>
       </c>
@@ -5128,9 +5321,15 @@
       <c r="L34" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
+      <c r="M34" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N34" s="4" t="s">
+        <v>498</v>
+      </c>
+      <c r="O34" s="4" t="s">
+        <v>499</v>
+      </c>
       <c r="P34" s="4" t="s">
         <v>57</v>
       </c>
@@ -5193,9 +5392,15 @@
       <c r="L35" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
+      <c r="M35" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N35" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="O35" s="4" t="s">
+        <v>501</v>
+      </c>
       <c r="P35" s="4" t="s">
         <v>57</v>
       </c>
@@ -5258,9 +5463,15 @@
       <c r="L36" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
+      <c r="M36" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N36" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="O36" s="4" t="s">
+        <v>503</v>
+      </c>
       <c r="P36" s="4" t="s">
         <v>57</v>
       </c>
@@ -5323,9 +5534,15 @@
       <c r="L37" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M37" s="4"/>
-      <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
+      <c r="M37" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N37" s="4" t="s">
+        <v>496</v>
+      </c>
+      <c r="O37" s="4" t="s">
+        <v>504</v>
+      </c>
       <c r="P37" s="4" t="s">
         <v>57</v>
       </c>
@@ -5388,9 +5605,15 @@
       <c r="L38" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M38" s="4"/>
-      <c r="N38" s="4"/>
-      <c r="O38" s="4"/>
+      <c r="M38" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N38" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="O38" s="4" t="s">
+        <v>506</v>
+      </c>
       <c r="P38" s="4" t="s">
         <v>57</v>
       </c>
@@ -5453,9 +5676,15 @@
       <c r="L39" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M39" s="4"/>
-      <c r="N39" s="4"/>
-      <c r="O39" s="4"/>
+      <c r="M39" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="N39" s="4" t="s">
+        <v>507</v>
+      </c>
+      <c r="O39" s="4" t="s">
+        <v>508</v>
+      </c>
       <c r="P39" s="4" t="s">
         <v>57</v>
       </c>
@@ -5518,9 +5747,15 @@
       <c r="L40" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M40" s="4"/>
-      <c r="N40" s="4"/>
-      <c r="O40" s="4"/>
+      <c r="M40" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="N40" s="4" t="s">
+        <v>509</v>
+      </c>
+      <c r="O40" s="4" t="s">
+        <v>510</v>
+      </c>
       <c r="P40" s="4" t="s">
         <v>57</v>
       </c>
@@ -5583,9 +5818,15 @@
       <c r="L41" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M41" s="4"/>
-      <c r="N41" s="4"/>
-      <c r="O41" s="4"/>
+      <c r="M41" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="N41" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="O41" s="4" t="s">
+        <v>512</v>
+      </c>
       <c r="P41" s="4" t="s">
         <v>57</v>
       </c>
@@ -5648,9 +5889,15 @@
       <c r="L42" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M42" s="4"/>
-      <c r="N42" s="4"/>
-      <c r="O42" s="4"/>
+      <c r="M42" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N42" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="O42" s="4" t="s">
+        <v>514</v>
+      </c>
       <c r="P42" s="4" t="s">
         <v>57</v>
       </c>
@@ -5713,9 +5960,15 @@
       <c r="L43" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M43" s="4"/>
-      <c r="N43" s="4"/>
-      <c r="O43" s="4"/>
+      <c r="M43" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="N43" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="O43" s="4" t="s">
+        <v>516</v>
+      </c>
       <c r="P43" s="4" t="s">
         <v>57</v>
       </c>
@@ -5778,9 +6031,15 @@
       <c r="L44" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M44" s="4"/>
-      <c r="N44" s="4"/>
-      <c r="O44" s="4"/>
+      <c r="M44" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="N44" s="4" t="s">
+        <v>517</v>
+      </c>
+      <c r="O44" s="4" t="s">
+        <v>518</v>
+      </c>
       <c r="P44" s="4" t="s">
         <v>57</v>
       </c>
@@ -5843,9 +6102,15 @@
       <c r="L45" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M45" s="4"/>
-      <c r="N45" s="4"/>
-      <c r="O45" s="4"/>
+      <c r="M45" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="N45" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="O45" s="4" t="s">
+        <v>520</v>
+      </c>
       <c r="P45" s="4" t="s">
         <v>57</v>
       </c>
@@ -5908,9 +6173,15 @@
       <c r="L46" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M46" s="4"/>
-      <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
+      <c r="M46" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="N46" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="O46" s="4" t="s">
+        <v>522</v>
+      </c>
       <c r="P46" s="4" t="s">
         <v>57</v>
       </c>
@@ -5973,9 +6244,15 @@
       <c r="L47" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M47" s="4"/>
-      <c r="N47" s="4"/>
-      <c r="O47" s="4"/>
+      <c r="M47" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="N47" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="O47" s="4" t="s">
+        <v>524</v>
+      </c>
       <c r="P47" s="4" t="s">
         <v>57</v>
       </c>
@@ -6038,9 +6315,15 @@
       <c r="L48" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M48" s="4"/>
-      <c r="N48" s="4"/>
-      <c r="O48" s="4"/>
+      <c r="M48" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="N48" s="4" t="s">
+        <v>525</v>
+      </c>
+      <c r="O48" s="4" t="s">
+        <v>526</v>
+      </c>
       <c r="P48" s="4" t="s">
         <v>57</v>
       </c>
@@ -6103,9 +6386,15 @@
       <c r="L49" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M49" s="4"/>
-      <c r="N49" s="4"/>
-      <c r="O49" s="4"/>
+      <c r="M49" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="N49" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="O49" s="4" t="s">
+        <v>528</v>
+      </c>
       <c r="P49" s="4" t="s">
         <v>57</v>
       </c>
@@ -6168,9 +6457,15 @@
       <c r="L50" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M50" s="4"/>
-      <c r="N50" s="4"/>
-      <c r="O50" s="4"/>
+      <c r="M50" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N50" s="4" t="s">
+        <v>529</v>
+      </c>
+      <c r="O50" s="4" t="s">
+        <v>530</v>
+      </c>
       <c r="P50" s="4" t="s">
         <v>57</v>
       </c>
@@ -6233,9 +6528,15 @@
       <c r="L51" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M51" s="4"/>
-      <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
+      <c r="M51" s="4" t="s">
+        <v>416</v>
+      </c>
+      <c r="N51" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="O51" s="4" t="s">
+        <v>532</v>
+      </c>
       <c r="P51" s="4" t="s">
         <v>57</v>
       </c>
@@ -6298,9 +6599,15 @@
       <c r="L52" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M52" s="4"/>
-      <c r="N52" s="4"/>
-      <c r="O52" s="4"/>
+      <c r="M52" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N52" s="4" t="s">
+        <v>533</v>
+      </c>
+      <c r="O52" s="4" t="s">
+        <v>534</v>
+      </c>
       <c r="P52" s="4" t="s">
         <v>57</v>
       </c>
@@ -6363,9 +6670,15 @@
       <c r="L53" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M53" s="4"/>
-      <c r="N53" s="4"/>
-      <c r="O53" s="4"/>
+      <c r="M53" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N53" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="O53" s="4" t="s">
+        <v>536</v>
+      </c>
       <c r="P53" s="4" t="s">
         <v>57</v>
       </c>
@@ -6428,9 +6741,15 @@
       <c r="L54" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M54" s="4"/>
-      <c r="N54" s="4"/>
-      <c r="O54" s="4"/>
+      <c r="M54" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="N54" s="4" t="s">
+        <v>537</v>
+      </c>
+      <c r="O54" s="4" t="s">
+        <v>538</v>
+      </c>
       <c r="P54" s="4" t="s">
         <v>57</v>
       </c>
@@ -6493,9 +6812,15 @@
       <c r="L55" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M55" s="4"/>
-      <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
+      <c r="M55" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="N55" s="4" t="s">
+        <v>539</v>
+      </c>
+      <c r="O55" s="4" t="s">
+        <v>540</v>
+      </c>
       <c r="P55" s="4" t="s">
         <v>57</v>
       </c>
@@ -6558,9 +6883,15 @@
       <c r="L56" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M56" s="4"/>
-      <c r="N56" s="4"/>
-      <c r="O56" s="4"/>
+      <c r="M56" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="N56" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="O56" s="4" t="s">
+        <v>542</v>
+      </c>
       <c r="P56" s="4" t="s">
         <v>57</v>
       </c>
@@ -6623,9 +6954,15 @@
       <c r="L57" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M57" s="4"/>
-      <c r="N57" s="4"/>
-      <c r="O57" s="4"/>
+      <c r="M57" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="N57" s="4" t="s">
+        <v>543</v>
+      </c>
+      <c r="O57" s="4" t="s">
+        <v>544</v>
+      </c>
       <c r="P57" s="4" t="s">
         <v>57</v>
       </c>
@@ -6688,9 +7025,15 @@
       <c r="L58" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M58" s="4"/>
-      <c r="N58" s="4"/>
-      <c r="O58" s="4"/>
+      <c r="M58" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="N58" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="O58" s="4" t="s">
+        <v>546</v>
+      </c>
       <c r="P58" s="4" t="s">
         <v>57</v>
       </c>
@@ -6753,9 +7096,15 @@
       <c r="L59" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="M59" s="4"/>
-      <c r="N59" s="4"/>
-      <c r="O59" s="4"/>
+      <c r="M59" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="N59" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="O59" s="4" t="s">
+        <v>548</v>
+      </c>
       <c r="P59" s="4" t="s">
         <v>57</v>
       </c>
@@ -6818,9 +7167,15 @@
       <c r="L60" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="M60" s="6"/>
-      <c r="N60" s="6"/>
-      <c r="O60" s="6"/>
+      <c r="M60" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="N60" s="6" t="s">
+        <v>549</v>
+      </c>
+      <c r="O60" s="6" t="s">
+        <v>508</v>
+      </c>
       <c r="P60" s="6" t="s">
         <v>57</v>
       </c>
@@ -7328,129 +7683,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE6F4BC9-6BA0-49D2-B9EC-3326267B383F}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="27.125" defaultRowHeight="14.25"/>
-  <cols>
-    <col min="1" max="1" width="14.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="25.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="67.125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="15">
-      <c r="A1" s="40" t="s">
-        <v>447</v>
-      </c>
-      <c r="B1" s="40" t="s">
-        <v>448</v>
-      </c>
-      <c r="C1" s="40" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="57">
-      <c r="A2" s="42" t="s">
-        <v>449</v>
-      </c>
-      <c r="B2" s="42" t="s">
-        <v>471</v>
-      </c>
-      <c r="C2" s="41" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="42.75">
-      <c r="A3" s="42" t="s">
-        <v>450</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>456</v>
-      </c>
-      <c r="C3" s="41" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="42.75">
-      <c r="A4" s="42" t="s">
-        <v>450</v>
-      </c>
-      <c r="B4" s="42" t="s">
-        <v>473</v>
-      </c>
-      <c r="C4" s="41" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="42.75">
-      <c r="A5" s="42" t="s">
-        <v>450</v>
-      </c>
-      <c r="B5" s="42" t="s">
-        <v>470</v>
-      </c>
-      <c r="C5" s="41" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="30">
-      <c r="A6" s="42" t="s">
-        <v>451</v>
-      </c>
-      <c r="B6" s="42" t="s">
-        <v>452</v>
-      </c>
-      <c r="C6" s="41" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="30">
-      <c r="A7" s="42" t="s">
-        <v>451</v>
-      </c>
-      <c r="B7" s="42" t="s">
-        <v>466</v>
-      </c>
-      <c r="C7" s="41" t="s">
-        <v>498</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="30">
-      <c r="A8" s="42" t="s">
-        <v>451</v>
-      </c>
-      <c r="B8" s="42" t="s">
-        <v>459</v>
-      </c>
-      <c r="C8" s="41" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="42.75">
-      <c r="A9" s="42" t="s">
-        <v>451</v>
-      </c>
-      <c r="B9" s="42" t="s">
-        <v>455</v>
-      </c>
-      <c r="C9" s="41" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="42.75">
-      <c r="A10" s="42" t="s">
-        <v>451</v>
-      </c>
-      <c r="B10" s="42" t="s">
-        <v>472</v>
-      </c>
-      <c r="C10" s="41" t="s">
-        <v>501</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
+++ b/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="472" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5783A1C2-7965-49AB-ABD3-D35792B2B3D4}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="1245" yWindow="2100" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>

--- a/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
+++ b/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d752cb73b61fc091/Desktop/linuxlabs/projectredstone/docs/project-management/02_Business_Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="472" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5783A1C2-7965-49AB-ABD3-D35792B2B3D4}"/>
+  <xr:revisionPtr revIDLastSave="642" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72A7FA09-7FC3-42C1-8F8F-356E6C972604}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1245" yWindow="2100" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="RTM" sheetId="2" r:id="rId2"/>
     <sheet name="Legend &amp; Reference" sheetId="3" r:id="rId3"/>
     <sheet name="Architecture Domains" sheetId="4" r:id="rId4"/>
+    <sheet name="Capabilities" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1464" uniqueCount="550">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="635">
   <si>
     <t>Northwind Outdoor Ltd. | RTM Summary</t>
   </si>
@@ -1703,6 +1704,272 @@
   </si>
   <si>
     <t>AD-03 Identity &amp; Access, AD-09 Observability, AD-08 Security</t>
+  </si>
+  <si>
+    <t>Capability ID</t>
+  </si>
+  <si>
+    <t>Business Purpose</t>
+  </si>
+  <si>
+    <t>CAP-001</t>
+  </si>
+  <si>
+    <t>Identity &amp; Access Management</t>
+  </si>
+  <si>
+    <t>Provides centralised management of user identities, roles and access throughout the user lifecycle.</t>
+  </si>
+  <si>
+    <t>CAP-002</t>
+  </si>
+  <si>
+    <t>Automation &amp; Scheduled Operations</t>
+  </si>
+  <si>
+    <t>Reduces repetitive manual administration and improves consistency by enabling repeatable and scheduled operational tasks.</t>
+  </si>
+  <si>
+    <t>CAP-003</t>
+  </si>
+  <si>
+    <t>File &amp; Data Services</t>
+  </si>
+  <si>
+    <t>Enables authorised users to store, organise, locate and share business files using a consistent structure.</t>
+  </si>
+  <si>
+    <t>CAP-004</t>
+  </si>
+  <si>
+    <t>Storage Provisioning/Management</t>
+  </si>
+  <si>
+    <t>Provides appropriately sized, accessible and manageable persistent storage to support business data, applications and infrastructure services.</t>
+  </si>
+  <si>
+    <t>CAP-005</t>
+  </si>
+  <si>
+    <t>Logging &amp; Audit</t>
+  </si>
+  <si>
+    <t>Clear audit trail of system changes and activity captured from a range of devices and services.</t>
+  </si>
+  <si>
+    <t>CAP-006</t>
+  </si>
+  <si>
+    <t>Monitoring &amp; Alerting</t>
+  </si>
+  <si>
+    <t>Provides visibility of service availability, health, resource utilisation and abnormal conditions, with timely alerting to enable proactive operational response.</t>
+  </si>
+  <si>
+    <t>CAP-007</t>
+  </si>
+  <si>
+    <t>Backup &amp; Recovery</t>
+  </si>
+  <si>
+    <t>In cases of outages, errors etc. business needs recent backups and proven process to restore from backups efficiently.</t>
+  </si>
+  <si>
+    <t>CAP-008</t>
+  </si>
+  <si>
+    <t>Remote Access</t>
+  </si>
+  <si>
+    <t>Authorised users can perform their jobs from outside the office environment</t>
+  </si>
+  <si>
+    <t>CAP-009</t>
+  </si>
+  <si>
+    <t>Network Connectivity &amp; Core Network Services</t>
+  </si>
+  <si>
+    <t>Business needs system to system and user to system communications, service discovery and name resolutions, network config, prevent unauthorised access</t>
+  </si>
+  <si>
+    <t>CAP-010</t>
+  </si>
+  <si>
+    <t>Application Hosting</t>
+  </si>
+  <si>
+    <t>Northwind requires infrastructure capable of running and supporting business applications.</t>
+  </si>
+  <si>
+    <t>CAP-011</t>
+  </si>
+  <si>
+    <t>Service Integration / Interoperability</t>
+  </si>
+  <si>
+    <t>New infrastructure should be capable of interoperating with existing business services</t>
+  </si>
+  <si>
+    <t>CAP-012</t>
+  </si>
+  <si>
+    <t>Reporting</t>
+  </si>
+  <si>
+    <t>Business wants to generate statistics/KPIs regarding the current systems and services to influence decisions re growth, investment, changes etc.</t>
+  </si>
+  <si>
+    <t>CAP-013</t>
+  </si>
+  <si>
+    <t>Software &amp; Patch Management</t>
+  </si>
+  <si>
+    <t>Admins must be able to control the software lifecycle, run and test updates, revert if errors encountered</t>
+  </si>
+  <si>
+    <t>CAP-014</t>
+  </si>
+  <si>
+    <t>Time Synchronisation Services</t>
+  </si>
+  <si>
+    <t>Maintains a consistent time reference across infrastructure and services to support reliable authentication, scheduling, monitoring, logging and investigation.</t>
+  </si>
+  <si>
+    <t>CAP-015</t>
+  </si>
+  <si>
+    <t>Compute Provisioning / Compute Hosting</t>
+  </si>
+  <si>
+    <t>Provides the processing resources and execution environments required to run Northwind infrastructure and business workloads.</t>
+  </si>
+  <si>
+    <t>CAP-016</t>
+  </si>
+  <si>
+    <t>Systems Administration &amp; Management</t>
+  </si>
+  <si>
+    <t>Provides authorised administrators with secure mechanisms to configure, operate, maintain and troubleshoot infrastructure services.</t>
+  </si>
+  <si>
+    <t>CAP-017</t>
+  </si>
+  <si>
+    <t>Security</t>
+  </si>
+  <si>
+    <t>Business needs designated security tools to protect systems, services and business information from unauthorised access, misuse and compromise.</t>
+  </si>
+  <si>
+    <t>CAP-018</t>
+  </si>
+  <si>
+    <t>Asset &amp; Configuration Management</t>
+  </si>
+  <si>
+    <t>Provides an authoritative record of infrastructure and technology assets, their ownership, status and lifecycle to support effective administration and planning.</t>
+  </si>
+  <si>
+    <t>CAP-019</t>
+  </si>
+  <si>
+    <t>[CONDITIONAL] Governance / Approval Workflow Support</t>
+  </si>
+  <si>
+    <t>Some requests may need business approval not only technical access / ability</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>CAP (Primary)</t>
+  </si>
+  <si>
+    <t>CAP (Secondary)</t>
+  </si>
+  <si>
+    <t>CAP-017
+CAP-005</t>
+  </si>
+  <si>
+    <t>CAP-005
+CAP-006</t>
+  </si>
+  <si>
+    <t>CAP-008
+CAP-017</t>
+  </si>
+  <si>
+    <t>CAP-017
+CAP-001</t>
+  </si>
+  <si>
+    <t>CAP-006
+CAP-005</t>
+  </si>
+  <si>
+    <t>CAP-007
+CAP-001</t>
+  </si>
+  <si>
+    <t>CAP-002
+CAP-013</t>
+  </si>
+  <si>
+    <t>CAP-005
+CAP-012</t>
+  </si>
+  <si>
+    <t>DD-012 — Availability &amp; Resilience Strategy</t>
+  </si>
+  <si>
+    <t>DD-002 — Identity &amp; Access Management Architecture</t>
+  </si>
+  <si>
+    <t>DD-003 — File &amp; Data Services Architecture</t>
+  </si>
+  <si>
+    <t>HLD (Primary)</t>
+  </si>
+  <si>
+    <t>HLD (Secondary)</t>
+  </si>
+  <si>
+    <t>DD-004 — Storage Architecture</t>
+  </si>
+  <si>
+    <t>DD-009 Network Security &amp; Segmentation</t>
+  </si>
+  <si>
+    <t>DD-002 Identity &amp; Access Management
+DD-007 Logging &amp; Audit</t>
+  </si>
+  <si>
+    <t>DD-007 — Logging &amp; Audit Architecture</t>
+  </si>
+  <si>
+    <t>DD-006 — Monitoring &amp; Alerting Architecture</t>
+  </si>
+  <si>
+    <t>DD-006 Monitoring &amp; Alerting</t>
+  </si>
+  <si>
+    <t>DD-005 — Backup &amp; Recovery Architecture</t>
+  </si>
+  <si>
+    <t>DD-001 — Compute / Platform Architecture
+DD-010 — Application Hosting Architecture</t>
+  </si>
+  <si>
+    <t>DD-008 — Remote Administration Architecture</t>
+  </si>
+  <si>
+    <t>DD-002 — Identity &amp; Access Management Architecture
+DD-009 — Network Security &amp; Segmentation</t>
   </si>
 </sst>
 </file>
@@ -2132,7 +2399,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2275,11 +2542,52 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFDCE6F1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFDCE6F1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFDCE6F1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFDCE6F1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -2298,11 +2606,106 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFDCE6F1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFDCE6F1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFDCE6F1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFDCE6F1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFDCE6F1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFDCE6F1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFDCE6F1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFDCE6F1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFDCE6F1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFDCE6F1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFDCE6F1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFDCE6F1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -2628,8 +3031,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="RTMTable" displayName="RTMTable" ref="B4:W60" totalsRowShown="0">
-  <tableColumns count="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="RTMTable" displayName="RTMTable" ref="B4:Y60" totalsRowShown="0">
+  <tableColumns count="24">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Requirement ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Requirement / Title"/>
@@ -2637,16 +3040,18 @@
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Business Owner"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="DF"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="BD"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="CAP"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="CAP (Primary)"/>
+    <tableColumn id="23" xr3:uid="{C116EC89-8261-41A9-893A-12DFD9AC01D5}" name="CAP (Secondary)" dataDxfId="5"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="BRD"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="SOW"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Sprint"/>
-    <tableColumn id="20" xr3:uid="{D1E0B300-86BD-45A9-B3EB-8951F17E8029}" name="Primary AD" dataDxfId="5"/>
-    <tableColumn id="22" xr3:uid="{701B3B8E-55FF-4520-83AD-295760593E66}" name="Key ADs" dataDxfId="4"/>
-    <tableColumn id="21" xr3:uid="{1638868F-A11C-40F1-8FB2-2AB197E42B79}" name="Secondary Ads" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="HLD"/>
+    <tableColumn id="20" xr3:uid="{D1E0B300-86BD-45A9-B3EB-8951F17E8029}" name="Primary AD" dataDxfId="8"/>
+    <tableColumn id="22" xr3:uid="{701B3B8E-55FF-4520-83AD-295760593E66}" name="Key ADs" dataDxfId="7"/>
+    <tableColumn id="21" xr3:uid="{1638868F-A11C-40F1-8FB2-2AB197E42B79}" name="Secondary Ads" dataDxfId="6"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="HLD (Primary)"/>
+    <tableColumn id="24" xr3:uid="{599BD185-8391-4930-BB9A-B52E39596ACD}" name="HLD (Secondary)" dataDxfId="4"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="LLD"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="ADR"/>
+    <tableColumn id="25" xr3:uid="{28378BB4-B208-482C-96C2-5A1994DECC42}" name="SOW" dataDxfId="3"/>
+    <tableColumn id="26" xr3:uid="{BAEC8EC4-D90B-4FBA-979D-21CDBE3C330A}" name="Sprint" dataDxfId="0"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Test / UAT"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Acceptance Criteria"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Status"/>
@@ -3062,7 +3467,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="32">
-        <f>COUNTIF(RTM!$U$5:$U$60,A16)</f>
+        <f>COUNTIF(RTM!$W$5:$W$60,A16)</f>
         <v>56</v>
       </c>
     </row>
@@ -3078,7 +3483,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:W60"/>
+  <dimension ref="A1:Y60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.625" bestFit="1" customWidth="1"/>
@@ -3089,20 +3494,24 @@
     <col min="6" max="6" width="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="3.875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.25" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="16" max="19" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="42" customWidth="1"/>
-    <col min="21" max="21" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="25" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="54" customWidth="1"/>
+    <col min="9" max="9" width="9.25" customWidth="1"/>
+    <col min="10" max="10" width="13.125" customWidth="1"/>
+    <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="17" max="18" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="11.5" customWidth="1"/>
+    <col min="21" max="21" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="42" customWidth="1"/>
+    <col min="23" max="23" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="25" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="27.95" customHeight="1">
+    <row r="1" spans="1:25" ht="27.95" customHeight="1">
       <c r="B1" s="43" t="s">
         <v>32</v>
       </c>
@@ -3127,8 +3536,10 @@
       <c r="U1" s="43"/>
       <c r="V1" s="43"/>
       <c r="W1" s="43"/>
-    </row>
-    <row r="2" spans="1:23" ht="21" customHeight="1">
+      <c r="X1" s="43"/>
+      <c r="Y1" s="43"/>
+    </row>
+    <row r="2" spans="1:25" ht="21" customHeight="1">
       <c r="B2" s="44" t="s">
         <v>33</v>
       </c>
@@ -3153,8 +3564,10 @@
       <c r="U2" s="44"/>
       <c r="V2" s="44"/>
       <c r="W2" s="44"/>
-    </row>
-    <row r="4" spans="1:23" ht="33" customHeight="1">
+      <c r="X2" s="44"/>
+      <c r="Y2" s="44"/>
+    </row>
+    <row r="4" spans="1:25" ht="33" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>387</v>
       </c>
@@ -3180,28 +3593,28 @@
         <v>40</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>41</v>
+        <v>610</v>
       </c>
       <c r="J4" s="1" t="s">
+        <v>611</v>
+      </c>
+      <c r="K4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="K4" s="1" t="s">
-        <v>43</v>
-      </c>
       <c r="L4" s="1" t="s">
-        <v>44</v>
+        <v>440</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>441</v>
+        <v>623</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>45</v>
+        <v>624</v>
       </c>
       <c r="Q4" s="1" t="s">
         <v>46</v>
@@ -3210,22 +3623,28 @@
         <v>47</v>
       </c>
       <c r="S4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="U4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:23" ht="51.95" customHeight="1">
+    <row r="5" spans="1:25" ht="51.95" customHeight="1">
       <c r="A5" s="39" t="s">
         <v>57</v>
       </c>
@@ -3251,52 +3670,50 @@
         <v>28</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J5" s="2" t="s">
+        <v>609</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="L5" s="2" t="s">
-        <v>57</v>
+        <v>436</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>57</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="P5" s="2"/>
       <c r="Q5" s="2" t="s">
         <v>57</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="S5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="T5" s="2" t="s">
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="V5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="U5" s="2" t="s">
+      <c r="W5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="V5" s="2" t="s">
+      <c r="X5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="W5" s="3" t="s">
+      <c r="Y5" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:23" ht="51.95" customHeight="1">
+    <row r="6" spans="1:25" ht="51.95" customHeight="1">
       <c r="A6" s="39" t="s">
         <v>57</v>
       </c>
@@ -3322,52 +3739,50 @@
         <v>25</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J6" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4" t="s">
         <v>332</v>
       </c>
-      <c r="K6" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="M6" s="4" t="s">
         <v>400</v>
       </c>
+      <c r="M6" s="2" t="s">
+        <v>445</v>
+      </c>
       <c r="N6" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="O6" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="P6" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="O6" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="P6" s="4"/>
       <c r="Q6" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T6" s="4" t="s">
+      <c r="S6" s="4"/>
+      <c r="T6" s="4"/>
+      <c r="U6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="U6" s="4" t="s">
+      <c r="W6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V6" s="4" t="s">
+      <c r="X6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W6" s="5" t="s">
+      <c r="Y6" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:23" ht="51.95" customHeight="1">
+    <row r="7" spans="1:25" ht="51.95" customHeight="1">
       <c r="A7" s="39" t="s">
         <v>57</v>
       </c>
@@ -3393,52 +3808,50 @@
         <v>25</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J7" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="K7" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L7" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>428</v>
+        <v>447</v>
       </c>
       <c r="N7" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="O7" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="P7" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="P7" s="4"/>
       <c r="Q7" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T7" s="4" t="s">
+      <c r="S7" s="4"/>
+      <c r="T7" s="4"/>
+      <c r="U7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V7" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="U7" s="4" t="s">
+      <c r="W7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V7" s="4" t="s">
+      <c r="X7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W7" s="5" t="s">
+      <c r="Y7" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:23" ht="51.95" customHeight="1">
+    <row r="8" spans="1:25" ht="51.95" customHeight="1">
       <c r="A8" s="39" t="s">
         <v>57</v>
       </c>
@@ -3464,52 +3877,52 @@
         <v>25</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>56</v>
+        <v>555</v>
       </c>
       <c r="J8" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="K8" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="K8" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L8" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>428</v>
+        <v>449</v>
       </c>
       <c r="N8" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="O8" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="P8" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="P8" s="4"/>
       <c r="Q8" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S8" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T8" s="4" t="s">
+      <c r="S8" s="4"/>
+      <c r="T8" s="4"/>
+      <c r="U8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="U8" s="4" t="s">
+      <c r="W8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V8" s="4" t="s">
+      <c r="X8" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W8" s="5" t="s">
+      <c r="Y8" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:23" ht="51.95" customHeight="1">
+    <row r="9" spans="1:25" ht="51.95" customHeight="1">
       <c r="A9" s="39" t="s">
         <v>57</v>
       </c>
@@ -3535,52 +3948,50 @@
         <v>28</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J9" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="K9" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L9" s="4" t="s">
-        <v>57</v>
+        <v>400</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>400</v>
+        <v>450</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>621</v>
+      </c>
+      <c r="P9" s="4"/>
       <c r="Q9" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S9" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T9" s="4" t="s">
+      <c r="S9" s="4"/>
+      <c r="T9" s="4"/>
+      <c r="U9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V9" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="U9" s="4" t="s">
+      <c r="W9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V9" s="4" t="s">
+      <c r="X9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W9" s="5" t="s">
+      <c r="Y9" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="51.95" customHeight="1">
+    <row r="10" spans="1:25" ht="51.95" customHeight="1">
       <c r="A10" s="39" t="s">
         <v>57</v>
       </c>
@@ -3606,28 +4017,28 @@
         <v>25</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>56</v>
+        <v>558</v>
       </c>
       <c r="J10" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="K10" s="4" t="s">
         <v>336</v>
       </c>
-      <c r="K10" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L10" s="4" t="s">
-        <v>57</v>
+        <v>408</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>408</v>
+        <v>452</v>
       </c>
       <c r="N10" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>453</v>
+        <v>622</v>
       </c>
       <c r="P10" s="4" t="s">
-        <v>57</v>
+        <v>625</v>
       </c>
       <c r="Q10" s="4" t="s">
         <v>57</v>
@@ -3635,23 +4046,25 @@
       <c r="R10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S10" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T10" s="4" t="s">
+      <c r="S10" s="4"/>
+      <c r="T10" s="4"/>
+      <c r="U10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V10" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="U10" s="4" t="s">
+      <c r="W10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V10" s="4" t="s">
+      <c r="X10" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W10" s="5" t="s">
+      <c r="Y10" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:23" ht="51.95" customHeight="1">
+    <row r="11" spans="1:25" ht="51.95" customHeight="1">
       <c r="A11" s="39" t="s">
         <v>57</v>
       </c>
@@ -3677,28 +4090,26 @@
         <v>25</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J11" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="K11" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L11" s="4" t="s">
-        <v>57</v>
+        <v>408</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>408</v>
+        <v>454</v>
       </c>
       <c r="N11" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>455</v>
+        <v>622</v>
       </c>
       <c r="P11" s="4" t="s">
-        <v>57</v>
+        <v>625</v>
       </c>
       <c r="Q11" s="4" t="s">
         <v>57</v>
@@ -3706,23 +4117,25 @@
       <c r="R11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T11" s="4" t="s">
+      <c r="S11" s="4"/>
+      <c r="T11" s="4"/>
+      <c r="U11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V11" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="U11" s="4" t="s">
+      <c r="W11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V11" s="4" t="s">
+      <c r="X11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W11" s="5" t="s">
+      <c r="Y11" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:23" ht="51.95" customHeight="1">
+    <row r="12" spans="1:25" ht="51.95" customHeight="1">
       <c r="A12" s="39" t="s">
         <v>57</v>
       </c>
@@ -3748,28 +4161,28 @@
         <v>28</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>56</v>
+        <v>558</v>
       </c>
       <c r="J12" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="K12" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="K12" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L12" s="4" t="s">
-        <v>57</v>
+        <v>420</v>
       </c>
       <c r="M12" s="4" t="s">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="N12" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>455</v>
+        <v>622</v>
       </c>
       <c r="P12" s="4" t="s">
-        <v>57</v>
+        <v>626</v>
       </c>
       <c r="Q12" s="4" t="s">
         <v>57</v>
@@ -3777,23 +4190,25 @@
       <c r="R12" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S12" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T12" s="4" t="s">
+      <c r="S12" s="4"/>
+      <c r="T12" s="4"/>
+      <c r="U12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V12" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="U12" s="4" t="s">
+      <c r="W12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V12" s="4" t="s">
+      <c r="X12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W12" s="5" t="s">
+      <c r="Y12" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:23" ht="51.95" customHeight="1">
+    <row r="13" spans="1:25" ht="51.95" customHeight="1">
       <c r="A13" s="39" t="s">
         <v>57</v>
       </c>
@@ -3819,28 +4234,28 @@
         <v>28</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>56</v>
+        <v>552</v>
       </c>
       <c r="J13" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="K13" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="K13" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L13" s="4" t="s">
-        <v>57</v>
+        <v>420</v>
       </c>
       <c r="M13" s="4" t="s">
-        <v>420</v>
+        <v>457</v>
       </c>
       <c r="N13" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O13" s="4" t="s">
-        <v>458</v>
+        <v>622</v>
       </c>
       <c r="P13" s="4" t="s">
-        <v>57</v>
+        <v>627</v>
       </c>
       <c r="Q13" s="4" t="s">
         <v>57</v>
@@ -3848,23 +4263,25 @@
       <c r="R13" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S13" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T13" s="4" t="s">
+      <c r="S13" s="4"/>
+      <c r="T13" s="4"/>
+      <c r="U13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V13" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="U13" s="4" t="s">
+      <c r="W13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V13" s="4" t="s">
+      <c r="X13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W13" s="5" t="s">
+      <c r="Y13" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:23" ht="51.95" customHeight="1">
+    <row r="14" spans="1:25" ht="51.95" customHeight="1">
       <c r="A14" s="39" t="s">
         <v>57</v>
       </c>
@@ -3890,52 +4307,50 @@
         <v>28</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J14" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4" t="s">
         <v>340</v>
       </c>
-      <c r="K14" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L14" s="4" t="s">
-        <v>57</v>
+        <v>424</v>
       </c>
       <c r="M14" s="4" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="N14" s="4" t="s">
-        <v>416</v>
+        <v>432</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="P14" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>628</v>
+      </c>
+      <c r="P14" s="4"/>
       <c r="Q14" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R14" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T14" s="4" t="s">
+      <c r="S14" s="4"/>
+      <c r="T14" s="4"/>
+      <c r="U14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V14" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="U14" s="4" t="s">
+      <c r="W14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V14" s="4" t="s">
+      <c r="X14" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W14" s="5" t="s">
+      <c r="Y14" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:23" ht="51.95" customHeight="1">
+    <row r="15" spans="1:25" ht="51.95" customHeight="1">
       <c r="A15" s="39" t="s">
         <v>57</v>
       </c>
@@ -3961,28 +4376,28 @@
         <v>28</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>56</v>
+        <v>567</v>
       </c>
       <c r="J15" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="K15" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="K15" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L15" s="4" t="s">
-        <v>57</v>
+        <v>424</v>
       </c>
       <c r="M15" s="4" t="s">
-        <v>424</v>
+        <v>459</v>
       </c>
       <c r="N15" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>460</v>
+        <v>629</v>
       </c>
       <c r="P15" s="4" t="s">
-        <v>57</v>
+        <v>628</v>
       </c>
       <c r="Q15" s="4" t="s">
         <v>57</v>
@@ -3990,23 +4405,25 @@
       <c r="R15" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S15" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T15" s="4" t="s">
+      <c r="S15" s="4"/>
+      <c r="T15" s="4"/>
+      <c r="U15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V15" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="U15" s="4" t="s">
+      <c r="W15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V15" s="4" t="s">
+      <c r="X15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W15" s="5" t="s">
+      <c r="Y15" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:23" ht="51.95" customHeight="1">
+    <row r="16" spans="1:25" ht="51.95" customHeight="1">
       <c r="A16" s="39" t="s">
         <v>57</v>
       </c>
@@ -4032,28 +4449,28 @@
         <v>28</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>56</v>
+        <v>600</v>
       </c>
       <c r="J16" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="K16" s="4" t="s">
         <v>342</v>
       </c>
-      <c r="K16" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L16" s="4" t="s">
-        <v>57</v>
+        <v>420</v>
       </c>
       <c r="M16" s="4" t="s">
-        <v>420</v>
+        <v>461</v>
       </c>
       <c r="N16" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>462</v>
+        <v>628</v>
       </c>
       <c r="P16" s="4" t="s">
-        <v>57</v>
+        <v>630</v>
       </c>
       <c r="Q16" s="4" t="s">
         <v>57</v>
@@ -4061,23 +4478,25 @@
       <c r="R16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S16" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T16" s="4" t="s">
+      <c r="S16" s="4"/>
+      <c r="T16" s="4"/>
+      <c r="U16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V16" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="U16" s="4" t="s">
+      <c r="W16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V16" s="4" t="s">
+      <c r="X16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W16" s="5" t="s">
+      <c r="Y16" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="51.95" customHeight="1">
+    <row r="17" spans="1:25" ht="51.95" customHeight="1">
       <c r="A17" s="39" t="s">
         <v>57</v>
       </c>
@@ -4103,28 +4522,28 @@
         <v>28</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>56</v>
+        <v>570</v>
       </c>
       <c r="J17" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="K17" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="K17" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L17" s="4" t="s">
-        <v>57</v>
+        <v>416</v>
       </c>
       <c r="M17" s="4" t="s">
-        <v>416</v>
+        <v>463</v>
       </c>
       <c r="N17" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>464</v>
+        <v>631</v>
       </c>
       <c r="P17" s="4" t="s">
-        <v>57</v>
+        <v>620</v>
       </c>
       <c r="Q17" s="4" t="s">
         <v>57</v>
@@ -4132,23 +4551,25 @@
       <c r="R17" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S17" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T17" s="4" t="s">
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V17" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="U17" s="4" t="s">
+      <c r="W17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V17" s="4" t="s">
+      <c r="X17" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W17" s="5" t="s">
+      <c r="Y17" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="51.95" customHeight="1">
+    <row r="18" spans="1:25" ht="51.95" customHeight="1">
       <c r="A18" s="39" t="s">
         <v>57</v>
       </c>
@@ -4174,28 +4595,28 @@
         <v>28</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>56</v>
+        <v>570</v>
       </c>
       <c r="J18" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="K18" s="4" t="s">
         <v>344</v>
       </c>
-      <c r="K18" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L18" s="4" t="s">
-        <v>57</v>
+        <v>416</v>
       </c>
       <c r="M18" s="4" t="s">
-        <v>416</v>
+        <v>465</v>
       </c>
       <c r="N18" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>466</v>
+        <v>631</v>
       </c>
       <c r="P18" s="4" t="s">
-        <v>57</v>
+        <v>620</v>
       </c>
       <c r="Q18" s="4" t="s">
         <v>57</v>
@@ -4203,23 +4624,25 @@
       <c r="R18" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T18" s="4" t="s">
+      <c r="S18" s="4"/>
+      <c r="T18" s="4"/>
+      <c r="U18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V18" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="U18" s="4" t="s">
+      <c r="W18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V18" s="4" t="s">
+      <c r="X18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W18" s="5" t="s">
+      <c r="Y18" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:23" ht="51.95" customHeight="1">
+    <row r="19" spans="1:25" ht="51.95" customHeight="1">
       <c r="A19" s="39" t="s">
         <v>57</v>
       </c>
@@ -4245,28 +4668,28 @@
         <v>28</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>56</v>
+        <v>570</v>
       </c>
       <c r="J19" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="K19" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="K19" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L19" s="4" t="s">
-        <v>57</v>
+        <v>436</v>
       </c>
       <c r="M19" s="4" t="s">
-        <v>436</v>
+        <v>467</v>
       </c>
       <c r="N19" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>468</v>
+        <v>620</v>
       </c>
       <c r="P19" s="4" t="s">
-        <v>57</v>
+        <v>631</v>
       </c>
       <c r="Q19" s="4" t="s">
         <v>57</v>
@@ -4274,23 +4697,25 @@
       <c r="R19" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T19" s="4" t="s">
+      <c r="S19" s="4"/>
+      <c r="T19" s="4"/>
+      <c r="U19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V19" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="U19" s="4" t="s">
+      <c r="W19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V19" s="4" t="s">
+      <c r="X19" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W19" s="5" t="s">
+      <c r="Y19" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="51.95" customHeight="1">
+    <row r="20" spans="1:25" ht="51.95" customHeight="1">
       <c r="A20" s="39" t="s">
         <v>57</v>
       </c>
@@ -4316,28 +4741,26 @@
         <v>28</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J20" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4" t="s">
         <v>346</v>
       </c>
-      <c r="K20" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L20" s="4" t="s">
-        <v>57</v>
+        <v>436</v>
       </c>
       <c r="M20" s="4" t="s">
-        <v>436</v>
+        <v>469</v>
       </c>
       <c r="N20" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>470</v>
+        <v>620</v>
       </c>
       <c r="P20" s="4" t="s">
-        <v>57</v>
+        <v>632</v>
       </c>
       <c r="Q20" s="4" t="s">
         <v>57</v>
@@ -4345,23 +4768,25 @@
       <c r="R20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S20" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T20" s="4" t="s">
+      <c r="S20" s="4"/>
+      <c r="T20" s="4"/>
+      <c r="U20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V20" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="U20" s="4" t="s">
+      <c r="W20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V20" s="4" t="s">
+      <c r="X20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W20" s="5" t="s">
+      <c r="Y20" s="5" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:23" ht="51.95" customHeight="1">
+    <row r="21" spans="1:25" ht="51.95" customHeight="1">
       <c r="A21" s="39" t="s">
         <v>57</v>
       </c>
@@ -4387,28 +4812,28 @@
         <v>25</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>56</v>
+        <v>597</v>
       </c>
       <c r="J21" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="K21" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="K21" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L21" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M21" s="4" t="s">
-        <v>428</v>
+        <v>472</v>
       </c>
       <c r="N21" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>473</v>
+        <v>633</v>
       </c>
       <c r="P21" s="4" t="s">
-        <v>57</v>
+        <v>634</v>
       </c>
       <c r="Q21" s="4" t="s">
         <v>57</v>
@@ -4416,23 +4841,25 @@
       <c r="R21" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S21" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T21" s="4" t="s">
+      <c r="S21" s="4"/>
+      <c r="T21" s="4"/>
+      <c r="U21" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V21" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="U21" s="4" t="s">
+      <c r="W21" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V21" s="4" t="s">
+      <c r="X21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W21" s="5" t="s">
+      <c r="Y21" s="5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="51.95" customHeight="1">
+    <row r="22" spans="1:25" ht="51.95" customHeight="1">
       <c r="A22" s="39" t="s">
         <v>57</v>
       </c>
@@ -4458,52 +4885,52 @@
         <v>28</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>56</v>
+        <v>573</v>
       </c>
       <c r="J22" s="4" t="s">
+        <v>615</v>
+      </c>
+      <c r="K22" s="4" t="s">
         <v>348</v>
       </c>
-      <c r="K22" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L22" s="4" t="s">
-        <v>57</v>
+        <v>392</v>
       </c>
       <c r="M22" s="4" t="s">
-        <v>392</v>
+        <v>474</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="P22" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P22" s="4"/>
       <c r="Q22" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R22" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S22" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T22" s="4" t="s">
+      <c r="S22" s="4"/>
+      <c r="T22" s="4"/>
+      <c r="U22" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V22" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="U22" s="4" t="s">
+      <c r="W22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V22" s="4" t="s">
+      <c r="X22" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W22" s="5" t="s">
+      <c r="Y22" s="5" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:23" ht="51.95" customHeight="1">
+    <row r="23" spans="1:25" ht="51.95" customHeight="1">
       <c r="A23" s="39" t="s">
         <v>57</v>
       </c>
@@ -4529,52 +4956,52 @@
         <v>28</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>56</v>
+        <v>600</v>
       </c>
       <c r="J23" s="4" t="s">
+        <v>576</v>
+      </c>
+      <c r="K23" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="K23" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L23" s="4" t="s">
-        <v>57</v>
+        <v>420</v>
       </c>
       <c r="M23" s="4" t="s">
-        <v>420</v>
+        <v>476</v>
       </c>
       <c r="N23" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="P23" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P23" s="4"/>
       <c r="Q23" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R23" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S23" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T23" s="4" t="s">
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V23" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="U23" s="4" t="s">
+      <c r="W23" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V23" s="4" t="s">
+      <c r="X23" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W23" s="5" t="s">
+      <c r="Y23" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="51.95" customHeight="1">
+    <row r="24" spans="1:25" ht="51.95" customHeight="1">
       <c r="A24" s="39" t="s">
         <v>57</v>
       </c>
@@ -4600,52 +5027,52 @@
         <v>28</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>56</v>
+        <v>576</v>
       </c>
       <c r="J24" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="K24" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="K24" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L24" s="4" t="s">
-        <v>57</v>
+        <v>392</v>
       </c>
       <c r="M24" s="4" t="s">
-        <v>392</v>
+        <v>478</v>
       </c>
       <c r="N24" s="4" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="P24" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P24" s="4"/>
       <c r="Q24" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R24" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T24" s="4" t="s">
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V24" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="U24" s="4" t="s">
+      <c r="W24" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V24" s="4" t="s">
+      <c r="X24" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W24" s="5" t="s">
+      <c r="Y24" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="25" spans="1:23" ht="51.95" customHeight="1">
+    <row r="25" spans="1:25" ht="51.95" customHeight="1">
       <c r="A25" s="39" t="s">
         <v>57</v>
       </c>
@@ -4671,52 +5098,50 @@
         <v>25</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J25" s="4" t="s">
+        <v>582</v>
+      </c>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="K25" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L25" s="4" t="s">
-        <v>57</v>
+        <v>432</v>
       </c>
       <c r="M25" s="4" t="s">
-        <v>432</v>
+        <v>480</v>
       </c>
       <c r="N25" s="4" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="P25" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P25" s="4"/>
       <c r="Q25" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R25" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S25" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T25" s="4" t="s">
+      <c r="S25" s="4"/>
+      <c r="T25" s="4"/>
+      <c r="U25" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V25" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="U25" s="4" t="s">
+      <c r="W25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V25" s="4" t="s">
+      <c r="X25" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W25" s="5" t="s">
+      <c r="Y25" s="5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="51.95" customHeight="1">
+    <row r="26" spans="1:25" ht="51.95" customHeight="1">
       <c r="A26" s="39" t="s">
         <v>57</v>
       </c>
@@ -4742,52 +5167,52 @@
         <v>30</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>56</v>
+        <v>579</v>
       </c>
       <c r="J26" s="4" t="s">
+        <v>594</v>
+      </c>
+      <c r="K26" s="4" t="s">
         <v>352</v>
       </c>
-      <c r="K26" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L26" s="4" t="s">
-        <v>57</v>
+        <v>396</v>
       </c>
       <c r="M26" s="4" t="s">
-        <v>396</v>
+        <v>482</v>
       </c>
       <c r="N26" s="4" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="P26" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P26" s="4"/>
       <c r="Q26" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R26" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T26" s="4" t="s">
+      <c r="S26" s="4"/>
+      <c r="T26" s="4"/>
+      <c r="U26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V26" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="U26" s="4" t="s">
+      <c r="W26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V26" s="4" t="s">
+      <c r="X26" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W26" s="5" t="s">
+      <c r="Y26" s="5" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="51.95" customHeight="1">
+    <row r="27" spans="1:25" ht="51.95" customHeight="1">
       <c r="A27" s="39" t="s">
         <v>57</v>
       </c>
@@ -4813,52 +5238,50 @@
         <v>30</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J27" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="K27" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L27" s="4" t="s">
-        <v>57</v>
+        <v>396</v>
       </c>
       <c r="M27" s="4" t="s">
-        <v>396</v>
+        <v>484</v>
       </c>
       <c r="N27" s="4" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>485</v>
-      </c>
-      <c r="P27" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P27" s="4"/>
       <c r="Q27" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R27" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S27" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T27" s="4" t="s">
+      <c r="S27" s="4"/>
+      <c r="T27" s="4"/>
+      <c r="U27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V27" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="U27" s="4" t="s">
+      <c r="W27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V27" s="4" t="s">
+      <c r="X27" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W27" s="5" t="s">
+      <c r="Y27" s="5" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="51.95" customHeight="1">
+    <row r="28" spans="1:25" ht="51.95" customHeight="1">
       <c r="A28" s="39" t="s">
         <v>57</v>
       </c>
@@ -4884,52 +5307,52 @@
         <v>25</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>56</v>
+        <v>597</v>
       </c>
       <c r="J28" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="K28" s="4" t="s">
         <v>354</v>
       </c>
-      <c r="K28" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L28" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M28" s="4" t="s">
-        <v>428</v>
+        <v>486</v>
       </c>
       <c r="N28" s="4" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>487</v>
-      </c>
-      <c r="P28" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P28" s="4"/>
       <c r="Q28" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R28" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T28" s="4" t="s">
+      <c r="S28" s="4"/>
+      <c r="T28" s="4"/>
+      <c r="U28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V28" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="U28" s="4" t="s">
+      <c r="W28" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V28" s="4" t="s">
+      <c r="X28" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W28" s="5" t="s">
+      <c r="Y28" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="29" spans="1:23" ht="51.95" customHeight="1">
+    <row r="29" spans="1:25" ht="51.95" customHeight="1">
       <c r="A29" s="39" t="s">
         <v>57</v>
       </c>
@@ -4955,52 +5378,50 @@
         <v>25</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J29" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="K29" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L29" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M29" s="4" t="s">
-        <v>428</v>
+        <v>488</v>
       </c>
       <c r="N29" s="4" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>489</v>
-      </c>
-      <c r="P29" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P29" s="4"/>
       <c r="Q29" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R29" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T29" s="4" t="s">
+      <c r="S29" s="4"/>
+      <c r="T29" s="4"/>
+      <c r="U29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V29" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="U29" s="4" t="s">
+      <c r="W29" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V29" s="4" t="s">
+      <c r="X29" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W29" s="5" t="s">
+      <c r="Y29" s="5" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="30" spans="1:23" ht="51.95" customHeight="1">
+    <row r="30" spans="1:25" ht="51.95" customHeight="1">
       <c r="A30" s="39" t="s">
         <v>57</v>
       </c>
@@ -5026,52 +5447,52 @@
         <v>25</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>56</v>
+        <v>585</v>
       </c>
       <c r="J30" s="4" t="s">
+        <v>616</v>
+      </c>
+      <c r="K30" s="4" t="s">
         <v>356</v>
       </c>
-      <c r="K30" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L30" s="4" t="s">
-        <v>57</v>
+        <v>424</v>
       </c>
       <c r="M30" s="4" t="s">
-        <v>424</v>
+        <v>490</v>
       </c>
       <c r="N30" s="4" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>491</v>
-      </c>
-      <c r="P30" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P30" s="4"/>
       <c r="Q30" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R30" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S30" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T30" s="4" t="s">
+      <c r="S30" s="4"/>
+      <c r="T30" s="4"/>
+      <c r="U30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V30" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="U30" s="4" t="s">
+      <c r="W30" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V30" s="4" t="s">
+      <c r="X30" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W30" s="5" t="s">
+      <c r="Y30" s="5" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="51.95" customHeight="1">
+    <row r="31" spans="1:25" ht="51.95" customHeight="1">
       <c r="A31" s="39" t="s">
         <v>57</v>
       </c>
@@ -5097,52 +5518,50 @@
         <v>25</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J31" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="J31" s="4"/>
+      <c r="K31" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="K31" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L31" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M31" s="4" t="s">
-        <v>428</v>
+        <v>492</v>
       </c>
       <c r="N31" s="4" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="P31" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P31" s="4"/>
       <c r="Q31" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R31" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S31" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T31" s="4" t="s">
+      <c r="S31" s="4"/>
+      <c r="T31" s="4"/>
+      <c r="U31" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V31" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="U31" s="4" t="s">
+      <c r="W31" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V31" s="4" t="s">
+      <c r="X31" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W31" s="5" t="s">
+      <c r="Y31" s="5" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="32" spans="1:23" ht="51.95" customHeight="1">
+    <row r="32" spans="1:25" ht="51.95" customHeight="1">
       <c r="A32" s="39" t="s">
         <v>57</v>
       </c>
@@ -5168,52 +5587,50 @@
         <v>25</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J32" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="J32" s="4"/>
+      <c r="K32" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="K32" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L32" s="4" t="s">
-        <v>57</v>
+        <v>408</v>
       </c>
       <c r="M32" s="4" t="s">
-        <v>408</v>
+        <v>494</v>
       </c>
       <c r="N32" s="4" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="P32" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P32" s="4"/>
       <c r="Q32" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R32" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S32" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T32" s="4" t="s">
+      <c r="S32" s="4"/>
+      <c r="T32" s="4"/>
+      <c r="U32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V32" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="U32" s="4" t="s">
+      <c r="W32" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V32" s="4" t="s">
+      <c r="X32" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W32" s="5" t="s">
+      <c r="Y32" s="5" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="33" spans="1:23" ht="51.95" customHeight="1">
+    <row r="33" spans="1:25" ht="51.95" customHeight="1">
       <c r="A33" s="39" t="s">
         <v>57</v>
       </c>
@@ -5239,52 +5656,50 @@
         <v>25</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J33" s="4" t="s">
+        <v>603</v>
+      </c>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="K33" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L33" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M33" s="4" t="s">
-        <v>428</v>
+        <v>496</v>
       </c>
       <c r="N33" s="4" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>497</v>
-      </c>
-      <c r="P33" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P33" s="4"/>
       <c r="Q33" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R33" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S33" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T33" s="4" t="s">
+      <c r="S33" s="4"/>
+      <c r="T33" s="4"/>
+      <c r="U33" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V33" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="U33" s="4" t="s">
+      <c r="W33" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V33" s="4" t="s">
+      <c r="X33" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W33" s="5" t="s">
+      <c r="Y33" s="5" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="34" spans="1:23" ht="51.95" customHeight="1">
+    <row r="34" spans="1:25" ht="51.95" customHeight="1">
       <c r="A34" s="39" t="s">
         <v>57</v>
       </c>
@@ -5310,52 +5725,52 @@
         <v>25</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>56</v>
+        <v>588</v>
       </c>
       <c r="J34" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="K34" s="4" t="s">
         <v>360</v>
       </c>
-      <c r="K34" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L34" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M34" s="4" t="s">
-        <v>428</v>
+        <v>498</v>
       </c>
       <c r="N34" s="4" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="P34" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P34" s="4"/>
       <c r="Q34" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R34" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S34" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T34" s="4" t="s">
+      <c r="S34" s="4"/>
+      <c r="T34" s="4"/>
+      <c r="U34" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V34" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="U34" s="4" t="s">
+      <c r="W34" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V34" s="4" t="s">
+      <c r="X34" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W34" s="5" t="s">
+      <c r="Y34" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="35" spans="1:23" ht="51.95" customHeight="1">
+    <row r="35" spans="1:25" ht="51.95" customHeight="1">
       <c r="A35" s="39" t="s">
         <v>57</v>
       </c>
@@ -5381,52 +5796,50 @@
         <v>25</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J35" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="J35" s="4"/>
+      <c r="K35" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="K35" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L35" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M35" s="4" t="s">
-        <v>428</v>
+        <v>500</v>
       </c>
       <c r="N35" s="4" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>501</v>
-      </c>
-      <c r="P35" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P35" s="4"/>
       <c r="Q35" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R35" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S35" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T35" s="4" t="s">
+      <c r="S35" s="4"/>
+      <c r="T35" s="4"/>
+      <c r="U35" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V35" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="U35" s="4" t="s">
+      <c r="W35" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V35" s="4" t="s">
+      <c r="X35" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W35" s="5" t="s">
+      <c r="Y35" s="5" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="36" spans="1:23" ht="51.95" customHeight="1">
+    <row r="36" spans="1:25" ht="51.95" customHeight="1">
       <c r="A36" s="39" t="s">
         <v>57</v>
       </c>
@@ -5452,52 +5865,52 @@
         <v>25</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>56</v>
+        <v>555</v>
       </c>
       <c r="J36" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="K36" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="K36" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L36" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M36" s="4" t="s">
-        <v>428</v>
+        <v>502</v>
       </c>
       <c r="N36" s="4" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="P36" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P36" s="4"/>
       <c r="Q36" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R36" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S36" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T36" s="4" t="s">
+      <c r="S36" s="4"/>
+      <c r="T36" s="4"/>
+      <c r="U36" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V36" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="U36" s="4" t="s">
+      <c r="W36" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V36" s="4" t="s">
+      <c r="X36" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W36" s="5" t="s">
+      <c r="Y36" s="5" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="37" spans="1:23" ht="51.95" customHeight="1">
+    <row r="37" spans="1:25" ht="51.95" customHeight="1">
       <c r="A37" s="39" t="s">
         <v>57</v>
       </c>
@@ -5523,52 +5936,52 @@
         <v>25</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>56</v>
+        <v>555</v>
       </c>
       <c r="J37" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="K37" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="K37" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L37" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M37" s="4" t="s">
-        <v>428</v>
+        <v>496</v>
       </c>
       <c r="N37" s="4" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>504</v>
-      </c>
-      <c r="P37" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P37" s="4"/>
       <c r="Q37" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R37" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S37" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T37" s="4" t="s">
+      <c r="S37" s="4"/>
+      <c r="T37" s="4"/>
+      <c r="U37" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V37" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="U37" s="4" t="s">
+      <c r="W37" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V37" s="4" t="s">
+      <c r="X37" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W37" s="5" t="s">
+      <c r="Y37" s="5" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="38" spans="1:23" ht="51.95" customHeight="1">
+    <row r="38" spans="1:25" ht="51.95" customHeight="1">
       <c r="A38" s="39" t="s">
         <v>57</v>
       </c>
@@ -5594,52 +6007,52 @@
         <v>30</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>56</v>
+        <v>585</v>
       </c>
       <c r="J38" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="K38" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="K38" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L38" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M38" s="4" t="s">
-        <v>428</v>
+        <v>505</v>
       </c>
       <c r="N38" s="4" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="P38" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P38" s="4"/>
       <c r="Q38" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R38" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S38" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T38" s="4" t="s">
+      <c r="S38" s="4"/>
+      <c r="T38" s="4"/>
+      <c r="U38" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V38" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="U38" s="4" t="s">
+      <c r="W38" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V38" s="4" t="s">
+      <c r="X38" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W38" s="5" t="s">
+      <c r="Y38" s="5" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="1:23" ht="51.95" customHeight="1">
+    <row r="39" spans="1:25" ht="51.95" customHeight="1">
       <c r="A39" s="39" t="s">
         <v>57</v>
       </c>
@@ -5665,52 +6078,50 @@
         <v>28</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J39" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="J39" s="4"/>
+      <c r="K39" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="K39" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L39" s="4" t="s">
-        <v>57</v>
+        <v>404</v>
       </c>
       <c r="M39" s="4" t="s">
-        <v>404</v>
+        <v>507</v>
       </c>
       <c r="N39" s="4" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>508</v>
-      </c>
-      <c r="P39" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P39" s="4"/>
       <c r="Q39" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R39" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S39" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T39" s="4" t="s">
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
+      <c r="U39" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V39" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="U39" s="4" t="s">
+      <c r="W39" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V39" s="4" t="s">
+      <c r="X39" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W39" s="5" t="s">
+      <c r="Y39" s="5" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="40" spans="1:23" ht="51.95" customHeight="1">
+    <row r="40" spans="1:25" ht="51.95" customHeight="1">
       <c r="A40" s="39" t="s">
         <v>57</v>
       </c>
@@ -5736,52 +6147,52 @@
         <v>28</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>56</v>
+        <v>600</v>
       </c>
       <c r="J40" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="K40" s="4" t="s">
         <v>366</v>
       </c>
-      <c r="K40" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L40" s="4" t="s">
-        <v>57</v>
+        <v>420</v>
       </c>
       <c r="M40" s="4" t="s">
-        <v>420</v>
+        <v>509</v>
       </c>
       <c r="N40" s="4" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="P40" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P40" s="4"/>
       <c r="Q40" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R40" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S40" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T40" s="4" t="s">
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
+      <c r="U40" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V40" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="U40" s="4" t="s">
+      <c r="W40" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V40" s="4" t="s">
+      <c r="X40" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W40" s="5" t="s">
+      <c r="Y40" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="41" spans="1:23" ht="51.95" customHeight="1">
+    <row r="41" spans="1:25" ht="51.95" customHeight="1">
       <c r="A41" s="39" t="s">
         <v>57</v>
       </c>
@@ -5807,52 +6218,52 @@
         <v>25</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>56</v>
+        <v>576</v>
       </c>
       <c r="J41" s="4" t="s">
+        <v>552</v>
+      </c>
+      <c r="K41" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="K41" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L41" s="4" t="s">
-        <v>57</v>
+        <v>392</v>
       </c>
       <c r="M41" s="4" t="s">
-        <v>392</v>
+        <v>511</v>
       </c>
       <c r="N41" s="4" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="P41" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P41" s="4"/>
       <c r="Q41" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R41" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S41" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T41" s="4" t="s">
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
+      <c r="U41" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V41" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="U41" s="4" t="s">
+      <c r="W41" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V41" s="4" t="s">
+      <c r="X41" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W41" s="5" t="s">
+      <c r="Y41" s="5" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="42" spans="1:23" ht="51.95" customHeight="1">
+    <row r="42" spans="1:25" ht="51.95" customHeight="1">
       <c r="A42" s="39" t="s">
         <v>57</v>
       </c>
@@ -5878,52 +6289,52 @@
         <v>28</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>56</v>
+        <v>597</v>
       </c>
       <c r="J42" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="K42" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="K42" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L42" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M42" s="4" t="s">
-        <v>428</v>
+        <v>513</v>
       </c>
       <c r="N42" s="4" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>514</v>
-      </c>
-      <c r="P42" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P42" s="4"/>
       <c r="Q42" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R42" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S42" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T42" s="4" t="s">
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="U42" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V42" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="U42" s="4" t="s">
+      <c r="W42" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V42" s="4" t="s">
+      <c r="X42" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W42" s="5" t="s">
+      <c r="Y42" s="5" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="43" spans="1:23" ht="51.95" customHeight="1">
+    <row r="43" spans="1:25" ht="51.95" customHeight="1">
       <c r="A43" s="39" t="s">
         <v>57</v>
       </c>
@@ -5949,52 +6360,50 @@
         <v>28</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J43" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="J43" s="4"/>
+      <c r="K43" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="K43" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L43" s="4" t="s">
-        <v>57</v>
+        <v>436</v>
       </c>
       <c r="M43" s="4" t="s">
-        <v>436</v>
+        <v>515</v>
       </c>
       <c r="N43" s="4" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="P43" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P43" s="4"/>
       <c r="Q43" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R43" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S43" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T43" s="4" t="s">
+      <c r="S43" s="4"/>
+      <c r="T43" s="4"/>
+      <c r="U43" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V43" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="U43" s="4" t="s">
+      <c r="W43" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V43" s="4" t="s">
+      <c r="X43" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W43" s="5" t="s">
+      <c r="Y43" s="5" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="44" spans="1:23" ht="51.95" customHeight="1">
+    <row r="44" spans="1:25" ht="51.95" customHeight="1">
       <c r="A44" s="39" t="s">
         <v>57</v>
       </c>
@@ -6020,52 +6429,50 @@
         <v>28</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J44" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="K44" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L44" s="4" t="s">
-        <v>57</v>
+        <v>436</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>436</v>
+        <v>517</v>
       </c>
       <c r="N44" s="4" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>518</v>
-      </c>
-      <c r="P44" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P44" s="4"/>
       <c r="Q44" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R44" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S44" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T44" s="4" t="s">
+      <c r="S44" s="4"/>
+      <c r="T44" s="4"/>
+      <c r="U44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V44" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="U44" s="4" t="s">
+      <c r="W44" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V44" s="4" t="s">
+      <c r="X44" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W44" s="5" t="s">
+      <c r="Y44" s="5" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="45" spans="1:23" ht="51.95" customHeight="1">
+    <row r="45" spans="1:25" ht="51.95" customHeight="1">
       <c r="A45" s="39" t="s">
         <v>57</v>
       </c>
@@ -6091,52 +6498,52 @@
         <v>30</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>56</v>
+        <v>609</v>
       </c>
       <c r="J45" s="4" t="s">
+        <v>567</v>
+      </c>
+      <c r="K45" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="K45" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L45" s="4" t="s">
-        <v>57</v>
+        <v>396</v>
       </c>
       <c r="M45" s="4" t="s">
-        <v>396</v>
+        <v>519</v>
       </c>
       <c r="N45" s="4" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>520</v>
-      </c>
-      <c r="P45" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P45" s="4"/>
       <c r="Q45" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R45" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S45" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T45" s="4" t="s">
+      <c r="S45" s="4"/>
+      <c r="T45" s="4"/>
+      <c r="U45" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V45" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="U45" s="4" t="s">
+      <c r="W45" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V45" s="4" t="s">
+      <c r="X45" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W45" s="5" t="s">
+      <c r="Y45" s="5" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="46" spans="1:23" ht="51.95" customHeight="1">
+    <row r="46" spans="1:25" ht="51.95" customHeight="1">
       <c r="A46" s="39" t="s">
         <v>57</v>
       </c>
@@ -6162,52 +6569,50 @@
         <v>30</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J46" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="K46" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L46" s="4" t="s">
-        <v>57</v>
+        <v>396</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>396</v>
+        <v>521</v>
       </c>
       <c r="N46" s="4" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>522</v>
-      </c>
-      <c r="P46" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P46" s="4"/>
       <c r="Q46" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R46" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S46" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T46" s="4" t="s">
+      <c r="S46" s="4"/>
+      <c r="T46" s="4"/>
+      <c r="U46" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V46" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="U46" s="4" t="s">
+      <c r="W46" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V46" s="4" t="s">
+      <c r="X46" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W46" s="5" t="s">
+      <c r="Y46" s="5" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="47" spans="1:23" ht="51.95" customHeight="1">
+    <row r="47" spans="1:25" ht="51.95" customHeight="1">
       <c r="A47" s="39" t="s">
         <v>57</v>
       </c>
@@ -6233,52 +6638,50 @@
         <v>28</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J47" s="4" t="s">
+        <v>600</v>
+      </c>
+      <c r="J47" s="4"/>
+      <c r="K47" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="K47" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L47" s="4" t="s">
-        <v>57</v>
+        <v>420</v>
       </c>
       <c r="M47" s="4" t="s">
-        <v>420</v>
+        <v>523</v>
       </c>
       <c r="N47" s="4" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>524</v>
-      </c>
-      <c r="P47" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P47" s="4"/>
       <c r="Q47" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R47" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S47" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T47" s="4" t="s">
+      <c r="S47" s="4"/>
+      <c r="T47" s="4"/>
+      <c r="U47" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V47" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="U47" s="4" t="s">
+      <c r="W47" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V47" s="4" t="s">
+      <c r="X47" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W47" s="5" t="s">
+      <c r="Y47" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="48" spans="1:23" ht="51.95" customHeight="1">
+    <row r="48" spans="1:25" ht="51.95" customHeight="1">
       <c r="A48" s="39" t="s">
         <v>57</v>
       </c>
@@ -6304,52 +6707,50 @@
         <v>28</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J48" s="4" t="s">
+        <v>564</v>
+      </c>
+      <c r="J48" s="4"/>
+      <c r="K48" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="K48" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L48" s="4" t="s">
-        <v>57</v>
+        <v>424</v>
       </c>
       <c r="M48" s="4" t="s">
-        <v>424</v>
+        <v>525</v>
       </c>
       <c r="N48" s="4" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="P48" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P48" s="4"/>
       <c r="Q48" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R48" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S48" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T48" s="4" t="s">
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
+      <c r="U48" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V48" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="U48" s="4" t="s">
+      <c r="W48" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V48" s="4" t="s">
+      <c r="X48" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W48" s="5" t="s">
+      <c r="Y48" s="5" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="49" spans="1:23" ht="51.95" customHeight="1">
+    <row r="49" spans="1:25" ht="51.95" customHeight="1">
       <c r="A49" s="39" t="s">
         <v>57</v>
       </c>
@@ -6375,52 +6776,52 @@
         <v>28</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>56</v>
+        <v>600</v>
       </c>
       <c r="J49" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="K49" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="K49" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L49" s="4" t="s">
-        <v>57</v>
+        <v>420</v>
       </c>
       <c r="M49" s="4" t="s">
-        <v>420</v>
+        <v>527</v>
       </c>
       <c r="N49" s="4" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="P49" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P49" s="4"/>
       <c r="Q49" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R49" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S49" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T49" s="4" t="s">
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
+      <c r="U49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V49" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="U49" s="4" t="s">
+      <c r="W49" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V49" s="4" t="s">
+      <c r="X49" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W49" s="5" t="s">
+      <c r="Y49" s="5" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="50" spans="1:23" ht="51.95" customHeight="1">
+    <row r="50" spans="1:25" ht="51.95" customHeight="1">
       <c r="A50" s="39" t="s">
         <v>57</v>
       </c>
@@ -6446,52 +6847,52 @@
         <v>25</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>56</v>
+        <v>597</v>
       </c>
       <c r="J50" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="K50" s="4" t="s">
         <v>376</v>
       </c>
-      <c r="K50" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L50" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M50" s="4" t="s">
-        <v>428</v>
+        <v>529</v>
       </c>
       <c r="N50" s="4" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>530</v>
-      </c>
-      <c r="P50" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P50" s="4"/>
       <c r="Q50" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R50" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S50" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T50" s="4" t="s">
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
+      <c r="U50" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V50" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="U50" s="4" t="s">
+      <c r="W50" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V50" s="4" t="s">
+      <c r="X50" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W50" s="5" t="s">
+      <c r="Y50" s="5" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="51" spans="1:23" ht="51.95" customHeight="1">
+    <row r="51" spans="1:25" ht="51.95" customHeight="1">
       <c r="A51" s="39" t="s">
         <v>57</v>
       </c>
@@ -6517,52 +6918,50 @@
         <v>28</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J51" s="4" t="s">
+        <v>570</v>
+      </c>
+      <c r="J51" s="4"/>
+      <c r="K51" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="K51" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L51" s="4" t="s">
-        <v>57</v>
+        <v>416</v>
       </c>
       <c r="M51" s="4" t="s">
-        <v>416</v>
+        <v>531</v>
       </c>
       <c r="N51" s="4" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="P51" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P51" s="4"/>
       <c r="Q51" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R51" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S51" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T51" s="4" t="s">
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
+      <c r="U51" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V51" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="U51" s="4" t="s">
+      <c r="W51" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V51" s="4" t="s">
+      <c r="X51" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W51" s="5" t="s">
+      <c r="Y51" s="5" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="1:23" ht="51.95" customHeight="1">
+    <row r="52" spans="1:25" ht="51.95" customHeight="1">
       <c r="A52" s="39" t="s">
         <v>57</v>
       </c>
@@ -6588,52 +6987,50 @@
         <v>25</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J52" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="J52" s="4"/>
+      <c r="K52" s="4" t="s">
         <v>378</v>
       </c>
-      <c r="K52" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L52" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M52" s="4" t="s">
-        <v>428</v>
+        <v>533</v>
       </c>
       <c r="N52" s="4" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>534</v>
-      </c>
-      <c r="P52" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P52" s="4"/>
       <c r="Q52" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R52" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S52" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T52" s="4" t="s">
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
+      <c r="U52" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V52" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="U52" s="4" t="s">
+      <c r="W52" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V52" s="4" t="s">
+      <c r="X52" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W52" s="5" t="s">
+      <c r="Y52" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="53" spans="1:23" ht="51.95" customHeight="1">
+    <row r="53" spans="1:25" ht="51.95" customHeight="1">
       <c r="A53" s="39" t="s">
         <v>57</v>
       </c>
@@ -6659,52 +7056,52 @@
         <v>25</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>56</v>
+        <v>597</v>
       </c>
       <c r="J53" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="K53" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="K53" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L53" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>428</v>
+        <v>535</v>
       </c>
       <c r="N53" s="4" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>536</v>
-      </c>
-      <c r="P53" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P53" s="4"/>
       <c r="Q53" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R53" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S53" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T53" s="4" t="s">
+      <c r="S53" s="4"/>
+      <c r="T53" s="4"/>
+      <c r="U53" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V53" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="U53" s="4" t="s">
+      <c r="W53" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V53" s="4" t="s">
+      <c r="X53" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W53" s="5" t="s">
+      <c r="Y53" s="5" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="54" spans="1:23" ht="51.95" customHeight="1">
+    <row r="54" spans="1:25" ht="51.95" customHeight="1">
       <c r="A54" s="39" t="s">
         <v>57</v>
       </c>
@@ -6730,52 +7127,52 @@
         <v>25</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>56</v>
+        <v>582</v>
       </c>
       <c r="J54" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="K54" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="K54" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L54" s="4" t="s">
-        <v>57</v>
+        <v>432</v>
       </c>
       <c r="M54" s="4" t="s">
-        <v>432</v>
+        <v>537</v>
       </c>
       <c r="N54" s="4" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="P54" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P54" s="4"/>
       <c r="Q54" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R54" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S54" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T54" s="4" t="s">
+      <c r="S54" s="4"/>
+      <c r="T54" s="4"/>
+      <c r="U54" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V54" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="U54" s="4" t="s">
+      <c r="W54" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V54" s="4" t="s">
+      <c r="X54" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W54" s="5" t="s">
+      <c r="Y54" s="5" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="55" spans="1:23" ht="51.95" customHeight="1">
+    <row r="55" spans="1:25" ht="51.95" customHeight="1">
       <c r="A55" s="39" t="s">
         <v>57</v>
       </c>
@@ -6801,52 +7198,50 @@
         <v>28</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J55" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="J55" s="4"/>
+      <c r="K55" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="K55" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L55" s="4" t="s">
-        <v>57</v>
+        <v>420</v>
       </c>
       <c r="M55" s="4" t="s">
-        <v>420</v>
+        <v>539</v>
       </c>
       <c r="N55" s="4" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="P55" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P55" s="4"/>
       <c r="Q55" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R55" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S55" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T55" s="4" t="s">
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V55" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="U55" s="4" t="s">
+      <c r="W55" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V55" s="4" t="s">
+      <c r="X55" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W55" s="5" t="s">
+      <c r="Y55" s="5" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="56" spans="1:23" ht="51.95" customHeight="1">
+    <row r="56" spans="1:25" ht="51.95" customHeight="1">
       <c r="A56" s="39" t="s">
         <v>57</v>
       </c>
@@ -6872,52 +7267,52 @@
         <v>28</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>56</v>
+        <v>567</v>
       </c>
       <c r="J56" s="4" t="s">
+        <v>619</v>
+      </c>
+      <c r="K56" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="K56" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L56" s="4" t="s">
-        <v>57</v>
+        <v>424</v>
       </c>
       <c r="M56" s="4" t="s">
-        <v>424</v>
+        <v>541</v>
       </c>
       <c r="N56" s="4" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>542</v>
-      </c>
-      <c r="P56" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P56" s="4"/>
       <c r="Q56" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R56" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S56" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T56" s="4" t="s">
+      <c r="S56" s="4"/>
+      <c r="T56" s="4"/>
+      <c r="U56" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V56" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="U56" s="4" t="s">
+      <c r="W56" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V56" s="4" t="s">
+      <c r="X56" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W56" s="5" t="s">
+      <c r="Y56" s="5" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="57" spans="1:23" ht="51.95" customHeight="1">
+    <row r="57" spans="1:25" ht="51.95" customHeight="1">
       <c r="A57" s="39" t="s">
         <v>57</v>
       </c>
@@ -6943,52 +7338,50 @@
         <v>30</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="J57" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="J57" s="4"/>
+      <c r="K57" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="K57" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L57" s="4" t="s">
-        <v>57</v>
+        <v>396</v>
       </c>
       <c r="M57" s="4" t="s">
-        <v>396</v>
+        <v>543</v>
       </c>
       <c r="N57" s="4" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>544</v>
-      </c>
-      <c r="P57" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P57" s="4"/>
       <c r="Q57" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R57" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S57" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T57" s="4" t="s">
+      <c r="S57" s="4"/>
+      <c r="T57" s="4"/>
+      <c r="U57" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V57" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="U57" s="4" t="s">
+      <c r="W57" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V57" s="4" t="s">
+      <c r="X57" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W57" s="5" t="s">
+      <c r="Y57" s="5" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="58" spans="1:23" ht="51.95" customHeight="1">
+    <row r="58" spans="1:25" ht="51.95" customHeight="1">
       <c r="A58" s="39" t="s">
         <v>57</v>
       </c>
@@ -7014,52 +7407,52 @@
         <v>25</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>56</v>
+        <v>597</v>
       </c>
       <c r="J58" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="K58" s="4" t="s">
         <v>384</v>
       </c>
-      <c r="K58" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L58" s="4" t="s">
-        <v>57</v>
+        <v>428</v>
       </c>
       <c r="M58" s="4" t="s">
-        <v>428</v>
+        <v>545</v>
       </c>
       <c r="N58" s="4" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>546</v>
-      </c>
-      <c r="P58" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P58" s="4"/>
       <c r="Q58" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R58" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S58" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T58" s="4" t="s">
+      <c r="S58" s="4"/>
+      <c r="T58" s="4"/>
+      <c r="U58" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V58" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="U58" s="4" t="s">
+      <c r="W58" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V58" s="4" t="s">
+      <c r="X58" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W58" s="5" t="s">
+      <c r="Y58" s="5" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="59" spans="1:23" ht="51.95" customHeight="1">
+    <row r="59" spans="1:25" ht="51.95" customHeight="1">
       <c r="A59" s="39" t="s">
         <v>57</v>
       </c>
@@ -7085,52 +7478,52 @@
         <v>28</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>56</v>
+        <v>570</v>
       </c>
       <c r="J59" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="K59" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="K59" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="L59" s="4" t="s">
-        <v>57</v>
+        <v>436</v>
       </c>
       <c r="M59" s="4" t="s">
-        <v>436</v>
+        <v>547</v>
       </c>
       <c r="N59" s="4" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>548</v>
-      </c>
-      <c r="P59" s="4" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P59" s="4"/>
       <c r="Q59" s="4" t="s">
         <v>57</v>
       </c>
       <c r="R59" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="S59" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="T59" s="4" t="s">
+      <c r="S59" s="4"/>
+      <c r="T59" s="4"/>
+      <c r="U59" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="V59" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="U59" s="4" t="s">
+      <c r="W59" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="V59" s="4" t="s">
+      <c r="X59" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="W59" s="5" t="s">
+      <c r="Y59" s="5" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="60" spans="1:23" ht="51.95" customHeight="1">
+    <row r="60" spans="1:25" ht="51.95" customHeight="1">
       <c r="A60" s="39" t="s">
         <v>57</v>
       </c>
@@ -7156,68 +7549,61 @@
         <v>28</v>
       </c>
       <c r="I60" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J60" s="6" t="s">
+        <v>591</v>
+      </c>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="K60" s="6" t="s">
-        <v>57</v>
-      </c>
       <c r="L60" s="6" t="s">
-        <v>57</v>
+        <v>404</v>
       </c>
       <c r="M60" s="6" t="s">
-        <v>404</v>
+        <v>549</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>549</v>
+        <v>508</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>508</v>
-      </c>
-      <c r="P60" s="6" t="s">
-        <v>57</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="P60" s="6"/>
       <c r="Q60" s="6" t="s">
         <v>57</v>
       </c>
       <c r="R60" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="S60" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="T60" s="6" t="s">
+      <c r="S60" s="6"/>
+      <c r="T60" s="6"/>
+      <c r="U60" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="V60" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="U60" s="6" t="s">
+      <c r="W60" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="V60" s="6" t="s">
+      <c r="X60" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="W60" s="7" t="s">
+      <c r="Y60" s="7" t="s">
         <v>283</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:W1"/>
-    <mergeCell ref="B2:W2"/>
+    <mergeCell ref="B1:Y1"/>
+    <mergeCell ref="B2:Y2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:A60">
+  <conditionalFormatting sqref="A5:Y60">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>$E5="Must"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:W60">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>$E5="Must"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="U5:U60">
-    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="Pending"/>
+  <conditionalFormatting sqref="W5:W60">
+    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Pending"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" sqref="B5:B60" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -7683,4 +8069,300 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C15C412-025F-4E3C-9071-5C08A9EB58CA}">
+  <dimension ref="A1:D20"/>
+  <sheetFormatPr defaultColWidth="66.875" defaultRowHeight="14.25"/>
+  <cols>
+    <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.625" style="48" customWidth="1"/>
+    <col min="3" max="3" width="84.25" style="48" customWidth="1"/>
+    <col min="4" max="4" width="33.625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="15">
+      <c r="A1" s="49" t="s">
+        <v>550</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>296</v>
+      </c>
+      <c r="C1" s="50" t="s">
+        <v>551</v>
+      </c>
+      <c r="D1" s="49" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B2" s="48" t="s">
+        <v>553</v>
+      </c>
+      <c r="C2" s="48" t="s">
+        <v>554</v>
+      </c>
+      <c r="D2" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="28.5">
+      <c r="A3" t="s">
+        <v>555</v>
+      </c>
+      <c r="B3" s="48" t="s">
+        <v>556</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>557</v>
+      </c>
+      <c r="D3" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
+        <v>558</v>
+      </c>
+      <c r="B4" s="48" t="s">
+        <v>559</v>
+      </c>
+      <c r="C4" s="48" t="s">
+        <v>560</v>
+      </c>
+      <c r="D4" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="28.5">
+      <c r="A5" t="s">
+        <v>561</v>
+      </c>
+      <c r="B5" s="48" t="s">
+        <v>562</v>
+      </c>
+      <c r="C5" s="48" t="s">
+        <v>563</v>
+      </c>
+      <c r="D5" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>564</v>
+      </c>
+      <c r="B6" s="48" t="s">
+        <v>565</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>566</v>
+      </c>
+      <c r="D6" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="28.5">
+      <c r="A7" t="s">
+        <v>567</v>
+      </c>
+      <c r="B7" s="48" t="s">
+        <v>568</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>569</v>
+      </c>
+      <c r="D7" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>570</v>
+      </c>
+      <c r="B8" s="48" t="s">
+        <v>571</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>572</v>
+      </c>
+      <c r="D8" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
+        <v>573</v>
+      </c>
+      <c r="B9" s="48" t="s">
+        <v>574</v>
+      </c>
+      <c r="C9" s="48" t="s">
+        <v>575</v>
+      </c>
+      <c r="D9" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="28.5">
+      <c r="A10" t="s">
+        <v>576</v>
+      </c>
+      <c r="B10" s="48" t="s">
+        <v>577</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>578</v>
+      </c>
+      <c r="D10" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>579</v>
+      </c>
+      <c r="B11" s="48" t="s">
+        <v>580</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>581</v>
+      </c>
+      <c r="D11" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>582</v>
+      </c>
+      <c r="B12" s="48" t="s">
+        <v>583</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>584</v>
+      </c>
+      <c r="D12" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="28.5">
+      <c r="A13" t="s">
+        <v>585</v>
+      </c>
+      <c r="B13" s="48" t="s">
+        <v>586</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>587</v>
+      </c>
+      <c r="D13" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>588</v>
+      </c>
+      <c r="B14" s="48" t="s">
+        <v>589</v>
+      </c>
+      <c r="C14" s="48" t="s">
+        <v>590</v>
+      </c>
+      <c r="D14" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="28.5">
+      <c r="A15" t="s">
+        <v>591</v>
+      </c>
+      <c r="B15" s="48" t="s">
+        <v>592</v>
+      </c>
+      <c r="C15" s="48" t="s">
+        <v>593</v>
+      </c>
+      <c r="D15" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="28.5">
+      <c r="A16" t="s">
+        <v>594</v>
+      </c>
+      <c r="B16" s="48" t="s">
+        <v>595</v>
+      </c>
+      <c r="C16" s="48" t="s">
+        <v>596</v>
+      </c>
+      <c r="D16" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="28.5">
+      <c r="A17" t="s">
+        <v>597</v>
+      </c>
+      <c r="B17" s="48" t="s">
+        <v>598</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>599</v>
+      </c>
+      <c r="D17" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="28.5">
+      <c r="A18" t="s">
+        <v>600</v>
+      </c>
+      <c r="B18" s="48" t="s">
+        <v>601</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>602</v>
+      </c>
+      <c r="D18" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="28.5">
+      <c r="A19" t="s">
+        <v>603</v>
+      </c>
+      <c r="B19" s="48" t="s">
+        <v>604</v>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>605</v>
+      </c>
+      <c r="D19" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="28.5">
+      <c r="A20" t="s">
+        <v>606</v>
+      </c>
+      <c r="B20" s="48" t="s">
+        <v>607</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>608</v>
+      </c>
+      <c r="D20" t="s">
+        <v>429</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
+++ b/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d752cb73b61fc091/Desktop/linuxlabs/projectredstone/docs/project-management/02_Business_Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="642" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72A7FA09-7FC3-42C1-8F8F-356E6C972604}"/>
+  <xr:revisionPtr revIDLastSave="740" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D54EF7AD-19F9-4EF6-9BB7-D46AC06A5B15}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1476" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="663">
   <si>
     <t>Northwind Outdoor Ltd. | RTM Summary</t>
   </si>
@@ -1970,6 +1970,96 @@
   <si>
     <t>DD-002 — Identity &amp; Access Management Architecture
 DD-009 — Network Security &amp; Segmentation</t>
+  </si>
+  <si>
+    <t>DD-011 — Service Integration / Interoperability Architecture</t>
+  </si>
+  <si>
+    <t>DD-010 — Application Hosting Architecture</t>
+  </si>
+  <si>
+    <t>DD-001 — Compute / Platform Architecture</t>
+  </si>
+  <si>
+    <t>DD-001 — Compute / Platform Architecture
+DD-012 — Availability &amp; Resilience Strategy</t>
+  </si>
+  <si>
+    <t>DD-001 — Compute &amp; Platform Architecture</t>
+  </si>
+  <si>
+    <t>DD-004 — Storage Architecture
+DD-009 — Network Security &amp; Segmentation
+DD-012 — Availability &amp; Resilience Strategy</t>
+  </si>
+  <si>
+    <t>DD-011 — Automation &amp; Scheduled Operations Architecture</t>
+  </si>
+  <si>
+    <t>DD-010 — Application Hosting Architecture
+DD-012 — Availability &amp; Resilience Strategy</t>
+  </si>
+  <si>
+    <t>DD-006 — Monitoring &amp; Alerting</t>
+  </si>
+  <si>
+    <t>DD-007 — Logging &amp; Audit</t>
+  </si>
+  <si>
+    <t>No dedicated</t>
+  </si>
+  <si>
+    <t>DD-009 — Network Security &amp; Segmentation</t>
+  </si>
+  <si>
+    <t>DD-010 — Patch &amp; Software Lifecycle Management Architecture</t>
+  </si>
+  <si>
+    <t>DD-009 — Network Security &amp; Segmentation Architecture</t>
+  </si>
+  <si>
+    <t>DD-002 — Identity &amp; Access Management Architecture
+DD-008 — Remote Administration Architecture</t>
+  </si>
+  <si>
+    <t>DD-007 — Logging &amp; Audit
+DD-010 — Application Hosting Architecture</t>
+  </si>
+  <si>
+    <t>DD-005 — Backup &amp; Recovery Architecture; DD-006 — Monitoring &amp; Alerting Architecture</t>
+  </si>
+  <si>
+    <t>DD-001 — Compute / Virtualisation</t>
+  </si>
+  <si>
+    <t>DD-001 — Compute / Virtualisation; DD-004 — Storage Architecture</t>
+  </si>
+  <si>
+    <t>DD-004 — Storage Architecture; DD-012 — Availability &amp; Resilience Strategy</t>
+  </si>
+  <si>
+    <t>DD-002 — Identity &amp; Access Management Architecture; DD-008 — Remote &amp; Administrative Access Architecture</t>
+  </si>
+  <si>
+    <t>DD-002 — Identity &amp; Access Management Architecture; DD-005 — Backup &amp; Recovery Architecture</t>
+  </si>
+  <si>
+    <t>DD-010 — Patch &amp; Software Lifecycle Management Architecture; DD-001 — Compute / Virtualisation</t>
+  </si>
+  <si>
+    <t>DD-010 — Patch &amp; Software Lifecycle Management Architecture; DD-012 — Availability &amp; Resilience Strategy</t>
+  </si>
+  <si>
+    <t>DD-001 — Compute / Virtualisation; DD-008 — Remote &amp; Administrative Access Architecture</t>
+  </si>
+  <si>
+    <t>DD-007 — Logging &amp; Audit Architecture; DD-010 — Patch &amp; Software Lifecycle Management Architecture</t>
+  </si>
+  <si>
+    <t>DD-001 — Compute / Virtualisation; DD-010 — Patch &amp; Software Lifecycle Management Architecture</t>
+  </si>
+  <si>
+    <t>DD-005 — Backup &amp; Recovery Architecture; DD-010 — Patch &amp; Software Lifecycle Management Architecture</t>
   </si>
 </sst>
 </file>
@@ -2527,6 +2617,13 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2542,18 +2639,49 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="12">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -2587,23 +2715,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -3041,17 +3152,17 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="DF"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="BD"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="CAP (Primary)"/>
-    <tableColumn id="23" xr3:uid="{C116EC89-8261-41A9-893A-12DFD9AC01D5}" name="CAP (Secondary)" dataDxfId="5"/>
+    <tableColumn id="23" xr3:uid="{C116EC89-8261-41A9-893A-12DFD9AC01D5}" name="CAP (Secondary)" dataDxfId="11"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="BRD"/>
-    <tableColumn id="20" xr3:uid="{D1E0B300-86BD-45A9-B3EB-8951F17E8029}" name="Primary AD" dataDxfId="8"/>
-    <tableColumn id="22" xr3:uid="{701B3B8E-55FF-4520-83AD-295760593E66}" name="Key ADs" dataDxfId="7"/>
-    <tableColumn id="21" xr3:uid="{1638868F-A11C-40F1-8FB2-2AB197E42B79}" name="Secondary Ads" dataDxfId="6"/>
+    <tableColumn id="20" xr3:uid="{D1E0B300-86BD-45A9-B3EB-8951F17E8029}" name="Primary AD" dataDxfId="10"/>
+    <tableColumn id="22" xr3:uid="{701B3B8E-55FF-4520-83AD-295760593E66}" name="Key ADs" dataDxfId="9"/>
+    <tableColumn id="21" xr3:uid="{1638868F-A11C-40F1-8FB2-2AB197E42B79}" name="Secondary Ads" dataDxfId="8"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="HLD (Primary)"/>
-    <tableColumn id="24" xr3:uid="{599BD185-8391-4930-BB9A-B52E39596ACD}" name="HLD (Secondary)" dataDxfId="4"/>
+    <tableColumn id="24" xr3:uid="{599BD185-8391-4930-BB9A-B52E39596ACD}" name="HLD (Secondary)" dataDxfId="7"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="LLD"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="ADR"/>
-    <tableColumn id="25" xr3:uid="{28378BB4-B208-482C-96C2-5A1994DECC42}" name="SOW" dataDxfId="3"/>
-    <tableColumn id="26" xr3:uid="{BAEC8EC4-D90B-4FBA-979D-21CDBE3C330A}" name="Sprint" dataDxfId="0"/>
+    <tableColumn id="25" xr3:uid="{28378BB4-B208-482C-96C2-5A1994DECC42}" name="SOW" dataDxfId="6"/>
+    <tableColumn id="26" xr3:uid="{BAEC8EC4-D90B-4FBA-979D-21CDBE3C330A}" name="Sprint" dataDxfId="5"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Test / UAT"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Acceptance Criteria"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Status"/>
@@ -3272,32 +3383,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.95" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="46" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
     </row>
     <row r="2" spans="1:10" ht="21" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="47" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
     </row>
     <row r="4" spans="1:10" ht="15">
       <c r="A4" s="21" t="s">
@@ -3501,7 +3612,7 @@
     <col min="13" max="13" width="19.875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="15.625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16" customWidth="1"/>
+    <col min="16" max="16" width="26.375" customWidth="1"/>
     <col min="17" max="18" width="11.5" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="11.5" customWidth="1"/>
     <col min="21" max="21" width="11.5" bestFit="1" customWidth="1"/>
@@ -3512,60 +3623,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="27.95" customHeight="1">
-      <c r="B1" s="43" t="s">
+      <c r="B1" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
-      <c r="S1" s="43"/>
-      <c r="T1" s="43"/>
-      <c r="U1" s="43"/>
-      <c r="V1" s="43"/>
-      <c r="W1" s="43"/>
-      <c r="X1" s="43"/>
-      <c r="Y1" s="43"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+      <c r="I1" s="46"/>
+      <c r="J1" s="46"/>
+      <c r="K1" s="46"/>
+      <c r="L1" s="46"/>
+      <c r="M1" s="46"/>
+      <c r="N1" s="46"/>
+      <c r="O1" s="46"/>
+      <c r="P1" s="46"/>
+      <c r="Q1" s="46"/>
+      <c r="R1" s="46"/>
+      <c r="S1" s="46"/>
+      <c r="T1" s="46"/>
+      <c r="U1" s="46"/>
+      <c r="V1" s="46"/>
+      <c r="W1" s="46"/>
+      <c r="X1" s="46"/>
+      <c r="Y1" s="46"/>
     </row>
     <row r="2" spans="1:25" ht="21" customHeight="1">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="47" t="s">
         <v>33</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-      <c r="M2" s="44"/>
-      <c r="N2" s="44"/>
-      <c r="O2" s="44"/>
-      <c r="P2" s="44"/>
-      <c r="Q2" s="44"/>
-      <c r="R2" s="44"/>
-      <c r="S2" s="44"/>
-      <c r="T2" s="44"/>
-      <c r="U2" s="44"/>
-      <c r="V2" s="44"/>
-      <c r="W2" s="44"/>
-      <c r="X2" s="44"/>
-      <c r="Y2" s="44"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="47"/>
+      <c r="X2" s="47"/>
+      <c r="Y2" s="47"/>
     </row>
     <row r="4" spans="1:25" ht="33" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -4903,9 +5014,11 @@
         <v>475</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P22" s="4"/>
+        <v>633</v>
+      </c>
+      <c r="P22" s="4" t="s">
+        <v>634</v>
+      </c>
       <c r="Q22" s="4" t="s">
         <v>57</v>
       </c>
@@ -4974,9 +5087,11 @@
         <v>477</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P23" s="4"/>
+        <v>626</v>
+      </c>
+      <c r="P23" s="4" t="s">
+        <v>621</v>
+      </c>
       <c r="Q23" s="4" t="s">
         <v>57</v>
       </c>
@@ -5045,9 +5160,11 @@
         <v>479</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P24" s="4"/>
+        <v>626</v>
+      </c>
+      <c r="P24" s="4" t="s">
+        <v>637</v>
+      </c>
       <c r="Q24" s="4" t="s">
         <v>57</v>
       </c>
@@ -5114,7 +5231,7 @@
         <v>481</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>57</v>
+        <v>635</v>
       </c>
       <c r="P25" s="4"/>
       <c r="Q25" s="4" t="s">
@@ -5185,9 +5302,11 @@
         <v>483</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P26" s="4"/>
+        <v>636</v>
+      </c>
+      <c r="P26" s="4" t="s">
+        <v>638</v>
+      </c>
       <c r="Q26" s="4" t="s">
         <v>57</v>
       </c>
@@ -5254,9 +5373,11 @@
         <v>485</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P27" s="4"/>
+        <v>639</v>
+      </c>
+      <c r="P27" s="4" t="s">
+        <v>640</v>
+      </c>
       <c r="Q27" s="4" t="s">
         <v>57</v>
       </c>
@@ -5325,9 +5446,11 @@
         <v>487</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P28" s="4"/>
+        <v>637</v>
+      </c>
+      <c r="P28" s="4" t="s">
+        <v>641</v>
+      </c>
       <c r="Q28" s="4" t="s">
         <v>57</v>
       </c>
@@ -5394,9 +5517,11 @@
         <v>489</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P29" s="4"/>
+        <v>641</v>
+      </c>
+      <c r="P29" s="4" t="s">
+        <v>642</v>
+      </c>
       <c r="Q29" s="4" t="s">
         <v>57</v>
       </c>
@@ -5465,9 +5590,11 @@
         <v>491</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P30" s="4"/>
+        <v>643</v>
+      </c>
+      <c r="P30" s="4" t="s">
+        <v>644</v>
+      </c>
       <c r="Q30" s="4" t="s">
         <v>57</v>
       </c>
@@ -5534,7 +5661,7 @@
         <v>493</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>57</v>
+        <v>645</v>
       </c>
       <c r="P31" s="4"/>
       <c r="Q31" s="4" t="s">
@@ -5603,9 +5730,11 @@
         <v>495</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P32" s="4"/>
+        <v>645</v>
+      </c>
+      <c r="P32" s="4" t="s">
+        <v>646</v>
+      </c>
       <c r="Q32" s="4" t="s">
         <v>57</v>
       </c>
@@ -5672,9 +5801,11 @@
         <v>497</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P33" s="4"/>
+        <v>645</v>
+      </c>
+      <c r="P33" s="4" t="s">
+        <v>637</v>
+      </c>
       <c r="Q33" s="4" t="s">
         <v>57</v>
       </c>
@@ -5743,9 +5874,11 @@
         <v>499</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P34" s="4"/>
+        <v>647</v>
+      </c>
+      <c r="P34" s="4" t="s">
+        <v>641</v>
+      </c>
       <c r="Q34" s="4" t="s">
         <v>57</v>
       </c>
@@ -5812,7 +5945,7 @@
         <v>501</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>57</v>
+        <v>647</v>
       </c>
       <c r="P35" s="4"/>
       <c r="Q35" s="4" t="s">
@@ -5883,7 +6016,7 @@
         <v>503</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>57</v>
+        <v>641</v>
       </c>
       <c r="P36" s="4"/>
       <c r="Q36" s="4" t="s">
@@ -5954,9 +6087,11 @@
         <v>504</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P37" s="4"/>
+        <v>641</v>
+      </c>
+      <c r="P37" s="4" t="s">
+        <v>647</v>
+      </c>
       <c r="Q37" s="4" t="s">
         <v>57</v>
       </c>
@@ -6025,9 +6160,11 @@
         <v>506</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P38" s="4"/>
+        <v>629</v>
+      </c>
+      <c r="P38" s="4" t="s">
+        <v>625</v>
+      </c>
       <c r="Q38" s="4" t="s">
         <v>57</v>
       </c>
@@ -6094,7 +6231,7 @@
         <v>508</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>57</v>
+        <v>628</v>
       </c>
       <c r="P39" s="4"/>
       <c r="Q39" s="4" t="s">
@@ -6165,9 +6302,11 @@
         <v>510</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P40" s="4"/>
+        <v>648</v>
+      </c>
+      <c r="P40" s="4" t="s">
+        <v>649</v>
+      </c>
       <c r="Q40" s="4" t="s">
         <v>57</v>
       </c>
@@ -6236,9 +6375,11 @@
         <v>512</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P41" s="4"/>
+        <v>648</v>
+      </c>
+      <c r="P41" s="4" t="s">
+        <v>621</v>
+      </c>
       <c r="Q41" s="4" t="s">
         <v>57</v>
       </c>
@@ -6307,9 +6448,11 @@
         <v>514</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P42" s="4"/>
+        <v>629</v>
+      </c>
+      <c r="P42" s="4" t="s">
+        <v>650</v>
+      </c>
       <c r="Q42" s="4" t="s">
         <v>57</v>
       </c>
@@ -6376,9 +6519,11 @@
         <v>516</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P43" s="4"/>
+        <v>620</v>
+      </c>
+      <c r="P43" s="4" t="s">
+        <v>651</v>
+      </c>
       <c r="Q43" s="4" t="s">
         <v>57</v>
       </c>
@@ -6445,9 +6590,11 @@
         <v>518</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P44" s="4"/>
+        <v>620</v>
+      </c>
+      <c r="P44" s="4" t="s">
+        <v>629</v>
+      </c>
       <c r="Q44" s="4" t="s">
         <v>57</v>
       </c>
@@ -6516,9 +6663,11 @@
         <v>520</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P45" s="4"/>
+        <v>629</v>
+      </c>
+      <c r="P45" s="4" t="s">
+        <v>653</v>
+      </c>
       <c r="Q45" s="4" t="s">
         <v>57</v>
       </c>
@@ -6585,9 +6734,11 @@
         <v>522</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P46" s="4"/>
+        <v>652</v>
+      </c>
+      <c r="P46" s="4" t="s">
+        <v>654</v>
+      </c>
       <c r="Q46" s="4" t="s">
         <v>57</v>
       </c>
@@ -6654,9 +6805,11 @@
         <v>524</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P47" s="4"/>
+        <v>648</v>
+      </c>
+      <c r="P47" s="4" t="s">
+        <v>655</v>
+      </c>
       <c r="Q47" s="4" t="s">
         <v>57</v>
       </c>
@@ -6723,9 +6876,11 @@
         <v>526</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P48" s="4"/>
+        <v>628</v>
+      </c>
+      <c r="P48" s="4" t="s">
+        <v>621</v>
+      </c>
       <c r="Q48" s="4" t="s">
         <v>57</v>
       </c>
@@ -6794,9 +6949,11 @@
         <v>528</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P49" s="4"/>
+        <v>648</v>
+      </c>
+      <c r="P49" s="4" t="s">
+        <v>656</v>
+      </c>
       <c r="Q49" s="4" t="s">
         <v>57</v>
       </c>
@@ -6865,9 +7022,11 @@
         <v>530</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P50" s="4"/>
+        <v>641</v>
+      </c>
+      <c r="P50" s="4" t="s">
+        <v>657</v>
+      </c>
       <c r="Q50" s="4" t="s">
         <v>57</v>
       </c>
@@ -6934,9 +7093,11 @@
         <v>532</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P51" s="4"/>
+        <v>620</v>
+      </c>
+      <c r="P51" s="4" t="s">
+        <v>631</v>
+      </c>
       <c r="Q51" s="4" t="s">
         <v>57</v>
       </c>
@@ -7003,9 +7164,11 @@
         <v>534</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P52" s="4"/>
+        <v>641</v>
+      </c>
+      <c r="P52" s="4" t="s">
+        <v>658</v>
+      </c>
       <c r="Q52" s="4" t="s">
         <v>57</v>
       </c>
@@ -7074,9 +7237,11 @@
         <v>536</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P53" s="4"/>
+        <v>641</v>
+      </c>
+      <c r="P53" s="4" t="s">
+        <v>652</v>
+      </c>
       <c r="Q53" s="4" t="s">
         <v>57</v>
       </c>
@@ -7145,9 +7310,11 @@
         <v>538</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P54" s="4"/>
+        <v>622</v>
+      </c>
+      <c r="P54" s="4" t="s">
+        <v>659</v>
+      </c>
       <c r="Q54" s="4" t="s">
         <v>57</v>
       </c>
@@ -7214,9 +7381,11 @@
         <v>540</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P55" s="4"/>
+        <v>648</v>
+      </c>
+      <c r="P55" s="4" t="s">
+        <v>660</v>
+      </c>
       <c r="Q55" s="4" t="s">
         <v>57</v>
       </c>
@@ -7285,9 +7454,11 @@
         <v>542</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P56" s="4"/>
+        <v>629</v>
+      </c>
+      <c r="P56" s="4" t="s">
+        <v>628</v>
+      </c>
       <c r="Q56" s="4" t="s">
         <v>57</v>
       </c>
@@ -7354,9 +7525,11 @@
         <v>544</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P57" s="4"/>
+        <v>652</v>
+      </c>
+      <c r="P57" s="4" t="s">
+        <v>654</v>
+      </c>
       <c r="Q57" s="4" t="s">
         <v>57</v>
       </c>
@@ -7425,9 +7598,11 @@
         <v>546</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P58" s="4"/>
+        <v>641</v>
+      </c>
+      <c r="P58" s="4" t="s">
+        <v>661</v>
+      </c>
       <c r="Q58" s="4" t="s">
         <v>57</v>
       </c>
@@ -7496,9 +7671,11 @@
         <v>548</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="P59" s="4"/>
+        <v>620</v>
+      </c>
+      <c r="P59" s="4" t="s">
+        <v>662</v>
+      </c>
       <c r="Q59" s="4" t="s">
         <v>57</v>
       </c>
@@ -7565,7 +7742,7 @@
         <v>508</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>57</v>
+        <v>628</v>
       </c>
       <c r="P60" s="6"/>
       <c r="Q60" s="6" t="s">
@@ -7597,13 +7774,28 @@
     <mergeCell ref="B1:Y1"/>
     <mergeCell ref="B2:Y2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:Y60">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="A5:Y27 A29:O29 Q28:Y29 A28:N28 A30:Y33 A34:O34 Q34:Y34 A35:Y60">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>$E5="Must"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="W5:W60">
-    <cfRule type="containsText" dxfId="1" priority="4" operator="containsText" text="Pending"/>
+    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="Pending"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P29">
+    <cfRule type="expression" dxfId="2" priority="8">
+      <formula>$E28="Must"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="O28:P28">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$E28="Must"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="P34">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$E34="Must"</formula>
+    </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" sqref="B5:B60" xr:uid="{00000000-0002-0000-0100-000000000000}">
@@ -7629,20 +7821,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27.95" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="46" t="s">
         <v>284</v>
       </c>
-      <c r="B1" s="43"/>
-      <c r="C1" s="43"/>
-      <c r="D1" s="43"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
     </row>
     <row r="2" spans="1:4" ht="21" customHeight="1">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="47" t="s">
         <v>285</v>
       </c>
-      <c r="B2" s="44"/>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
     </row>
     <row r="4" spans="1:4" ht="15">
       <c r="A4" s="11" t="s">
@@ -7855,12 +8047,12 @@
       </c>
     </row>
     <row r="20" spans="1:4" ht="42" customHeight="1">
-      <c r="A20" s="45" t="s">
+      <c r="A20" s="48" t="s">
         <v>330</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="47"/>
+      <c r="B20" s="49"/>
+      <c r="C20" s="49"/>
+      <c r="D20" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -8077,22 +8269,22 @@
   <sheetFormatPr defaultColWidth="66.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="33.625" style="48" customWidth="1"/>
-    <col min="3" max="3" width="84.25" style="48" customWidth="1"/>
+    <col min="2" max="2" width="33.625" style="43" customWidth="1"/>
+    <col min="3" max="3" width="84.25" style="43" customWidth="1"/>
     <col min="4" max="4" width="33.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="15">
-      <c r="A1" s="49" t="s">
+      <c r="A1" s="44" t="s">
         <v>550</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="B1" s="45" t="s">
         <v>296</v>
       </c>
-      <c r="C1" s="50" t="s">
+      <c r="C1" s="45" t="s">
         <v>551</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="44" t="s">
         <v>389</v>
       </c>
     </row>
@@ -8100,10 +8292,10 @@
       <c r="A2" t="s">
         <v>552</v>
       </c>
-      <c r="B2" s="48" t="s">
+      <c r="B2" s="43" t="s">
         <v>553</v>
       </c>
-      <c r="C2" s="48" t="s">
+      <c r="C2" s="43" t="s">
         <v>554</v>
       </c>
       <c r="D2" t="s">
@@ -8114,24 +8306,24 @@
       <c r="A3" t="s">
         <v>555</v>
       </c>
-      <c r="B3" s="48" t="s">
+      <c r="B3" s="43" t="s">
         <v>556</v>
       </c>
-      <c r="C3" s="48" t="s">
+      <c r="C3" s="43" t="s">
         <v>557</v>
       </c>
       <c r="D3" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" ht="28.5">
       <c r="A4" t="s">
         <v>558</v>
       </c>
-      <c r="B4" s="48" t="s">
+      <c r="B4" s="43" t="s">
         <v>559</v>
       </c>
-      <c r="C4" s="48" t="s">
+      <c r="C4" s="43" t="s">
         <v>560</v>
       </c>
       <c r="D4" t="s">
@@ -8142,10 +8334,10 @@
       <c r="A5" t="s">
         <v>561</v>
       </c>
-      <c r="B5" s="48" t="s">
+      <c r="B5" s="43" t="s">
         <v>562</v>
       </c>
-      <c r="C5" s="48" t="s">
+      <c r="C5" s="43" t="s">
         <v>563</v>
       </c>
       <c r="D5" t="s">
@@ -8156,10 +8348,10 @@
       <c r="A6" t="s">
         <v>564</v>
       </c>
-      <c r="B6" s="48" t="s">
+      <c r="B6" s="43" t="s">
         <v>565</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="43" t="s">
         <v>566</v>
       </c>
       <c r="D6" t="s">
@@ -8170,24 +8362,24 @@
       <c r="A7" t="s">
         <v>567</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="43" t="s">
         <v>568</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="43" t="s">
         <v>569</v>
       </c>
       <c r="D7" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" ht="28.5">
       <c r="A8" t="s">
         <v>570</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="B8" s="43" t="s">
         <v>571</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="43" t="s">
         <v>572</v>
       </c>
       <c r="D8" t="s">
@@ -8198,10 +8390,10 @@
       <c r="A9" t="s">
         <v>573</v>
       </c>
-      <c r="B9" s="48" t="s">
+      <c r="B9" s="43" t="s">
         <v>574</v>
       </c>
-      <c r="C9" s="48" t="s">
+      <c r="C9" s="43" t="s">
         <v>575</v>
       </c>
       <c r="D9" t="s">
@@ -8212,10 +8404,10 @@
       <c r="A10" t="s">
         <v>576</v>
       </c>
-      <c r="B10" s="48" t="s">
+      <c r="B10" s="43" t="s">
         <v>577</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="43" t="s">
         <v>578</v>
       </c>
       <c r="D10" t="s">
@@ -8226,10 +8418,10 @@
       <c r="A11" t="s">
         <v>579</v>
       </c>
-      <c r="B11" s="48" t="s">
+      <c r="B11" s="43" t="s">
         <v>580</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="43" t="s">
         <v>581</v>
       </c>
       <c r="D11" t="s">
@@ -8240,10 +8432,10 @@
       <c r="A12" t="s">
         <v>582</v>
       </c>
-      <c r="B12" s="48" t="s">
+      <c r="B12" s="43" t="s">
         <v>583</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="43" t="s">
         <v>584</v>
       </c>
       <c r="D12" t="s">
@@ -8254,24 +8446,24 @@
       <c r="A13" t="s">
         <v>585</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="43" t="s">
         <v>586</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="43" t="s">
         <v>587</v>
       </c>
       <c r="D13" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" ht="28.5">
       <c r="A14" t="s">
         <v>588</v>
       </c>
-      <c r="B14" s="48" t="s">
+      <c r="B14" s="43" t="s">
         <v>589</v>
       </c>
-      <c r="C14" s="48" t="s">
+      <c r="C14" s="43" t="s">
         <v>590</v>
       </c>
       <c r="D14" t="s">
@@ -8282,10 +8474,10 @@
       <c r="A15" t="s">
         <v>591</v>
       </c>
-      <c r="B15" s="48" t="s">
+      <c r="B15" s="43" t="s">
         <v>592</v>
       </c>
-      <c r="C15" s="48" t="s">
+      <c r="C15" s="43" t="s">
         <v>593</v>
       </c>
       <c r="D15" t="s">
@@ -8296,10 +8488,10 @@
       <c r="A16" t="s">
         <v>594</v>
       </c>
-      <c r="B16" s="48" t="s">
+      <c r="B16" s="43" t="s">
         <v>595</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="43" t="s">
         <v>596</v>
       </c>
       <c r="D16" t="s">
@@ -8310,10 +8502,10 @@
       <c r="A17" t="s">
         <v>597</v>
       </c>
-      <c r="B17" s="48" t="s">
+      <c r="B17" s="43" t="s">
         <v>598</v>
       </c>
-      <c r="C17" s="48" t="s">
+      <c r="C17" s="43" t="s">
         <v>599</v>
       </c>
       <c r="D17" t="s">
@@ -8324,10 +8516,10 @@
       <c r="A18" t="s">
         <v>600</v>
       </c>
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="43" t="s">
         <v>601</v>
       </c>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="43" t="s">
         <v>602</v>
       </c>
       <c r="D18" t="s">
@@ -8338,10 +8530,10 @@
       <c r="A19" t="s">
         <v>603</v>
       </c>
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="43" t="s">
         <v>604</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="43" t="s">
         <v>605</v>
       </c>
       <c r="D19" t="s">
@@ -8352,10 +8544,10 @@
       <c r="A20" t="s">
         <v>606</v>
       </c>
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="43" t="s">
         <v>607</v>
       </c>
-      <c r="C20" s="48" t="s">
+      <c r="C20" s="43" t="s">
         <v>608</v>
       </c>
       <c r="D20" t="s">

--- a/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
+++ b/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d752cb73b61fc091/Desktop/linuxlabs/projectredstone/docs/project-management/02_Business_Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="740" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D54EF7AD-19F9-4EF6-9BB7-D46AC06A5B15}"/>
+  <xr:revisionPtr revIDLastSave="784" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30CC72D7-AC51-4E30-8460-6C0F686F2BF5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="663">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1511" uniqueCount="667">
   <si>
     <t>Northwind Outdoor Ltd. | RTM Summary</t>
   </si>
@@ -2060,6 +2060,18 @@
   </si>
   <si>
     <t>DD-005 — Backup &amp; Recovery Architecture; DD-010 — Patch &amp; Software Lifecycle Management Architecture</t>
+  </si>
+  <si>
+    <t>LLD-01</t>
+  </si>
+  <si>
+    <t>LLD (Primary)</t>
+  </si>
+  <si>
+    <t>LLD (Secondary)</t>
+  </si>
+  <si>
+    <t>LLD-08</t>
   </si>
 </sst>
 </file>
@@ -2643,7 +2655,24 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="13">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF2CC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2667,20 +2696,37 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF9C0006"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFCE4D6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FFFFF2CC"/>
-        </patternFill>
-      </fill>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color rgb="FFDCE6F1"/>
+        </left>
+        <right style="thin">
+          <color rgb="FFDCE6F1"/>
+        </right>
+        <top style="thin">
+          <color rgb="FFDCE6F1"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FFDCE6F1"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -3142,8 +3188,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="RTMTable" displayName="RTMTable" ref="B4:Y60" totalsRowShown="0">
-  <tableColumns count="24">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="RTMTable" displayName="RTMTable" ref="B4:Z60" totalsRowShown="0">
+  <autoFilter ref="B4:Z60" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
+  <tableColumns count="25">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Requirement ID"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Type"/>
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Requirement / Title"/>
@@ -3152,17 +3199,18 @@
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="DF"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="BD"/>
     <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="CAP (Primary)"/>
-    <tableColumn id="23" xr3:uid="{C116EC89-8261-41A9-893A-12DFD9AC01D5}" name="CAP (Secondary)" dataDxfId="11"/>
+    <tableColumn id="23" xr3:uid="{C116EC89-8261-41A9-893A-12DFD9AC01D5}" name="CAP (Secondary)" dataDxfId="12"/>
     <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="BRD"/>
-    <tableColumn id="20" xr3:uid="{D1E0B300-86BD-45A9-B3EB-8951F17E8029}" name="Primary AD" dataDxfId="10"/>
-    <tableColumn id="22" xr3:uid="{701B3B8E-55FF-4520-83AD-295760593E66}" name="Key ADs" dataDxfId="9"/>
-    <tableColumn id="21" xr3:uid="{1638868F-A11C-40F1-8FB2-2AB197E42B79}" name="Secondary Ads" dataDxfId="8"/>
+    <tableColumn id="20" xr3:uid="{D1E0B300-86BD-45A9-B3EB-8951F17E8029}" name="Primary AD" dataDxfId="11"/>
+    <tableColumn id="22" xr3:uid="{701B3B8E-55FF-4520-83AD-295760593E66}" name="Key ADs" dataDxfId="10"/>
+    <tableColumn id="21" xr3:uid="{1638868F-A11C-40F1-8FB2-2AB197E42B79}" name="Secondary Ads" dataDxfId="9"/>
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="HLD (Primary)"/>
-    <tableColumn id="24" xr3:uid="{599BD185-8391-4930-BB9A-B52E39596ACD}" name="HLD (Secondary)" dataDxfId="7"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="LLD"/>
+    <tableColumn id="24" xr3:uid="{599BD185-8391-4930-BB9A-B52E39596ACD}" name="HLD (Secondary)" dataDxfId="8"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="LLD (Primary)"/>
+    <tableColumn id="10" xr3:uid="{D9149C79-EC24-41C1-B36D-CD2D9225FFA3}" name="LLD (Secondary)" dataDxfId="5"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="ADR"/>
-    <tableColumn id="25" xr3:uid="{28378BB4-B208-482C-96C2-5A1994DECC42}" name="SOW" dataDxfId="6"/>
-    <tableColumn id="26" xr3:uid="{BAEC8EC4-D90B-4FBA-979D-21CDBE3C330A}" name="Sprint" dataDxfId="5"/>
+    <tableColumn id="25" xr3:uid="{28378BB4-B208-482C-96C2-5A1994DECC42}" name="SOW" dataDxfId="7"/>
+    <tableColumn id="26" xr3:uid="{BAEC8EC4-D90B-4FBA-979D-21CDBE3C330A}" name="Sprint" dataDxfId="6"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Test / UAT"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Acceptance Criteria"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Status"/>
@@ -3578,7 +3626,7 @@
         <v>16</v>
       </c>
       <c r="B16" s="32">
-        <f>COUNTIF(RTM!$W$5:$W$60,A16)</f>
+        <f>COUNTIF(RTM!$X$5:$X$60,A16)</f>
         <v>56</v>
       </c>
     </row>
@@ -3594,7 +3642,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:Y60"/>
+  <dimension ref="A1:Z60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="14.625" bestFit="1" customWidth="1"/>
@@ -3613,16 +3661,18 @@
     <col min="14" max="14" width="15.625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="26.375" customWidth="1"/>
-    <col min="17" max="18" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="11.5" customWidth="1"/>
-    <col min="21" max="21" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="42" customWidth="1"/>
-    <col min="23" max="23" width="19.625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="25" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="54" customWidth="1"/>
+    <col min="17" max="17" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.5" customWidth="1"/>
+    <col min="19" max="19" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="11.5" customWidth="1"/>
+    <col min="22" max="22" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="42" customWidth="1"/>
+    <col min="24" max="24" width="19.625" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="25" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="54" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="27.95" customHeight="1">
+    <row r="1" spans="1:26" ht="27.95" customHeight="1">
       <c r="B1" s="46" t="s">
         <v>32</v>
       </c>
@@ -3649,8 +3699,9 @@
       <c r="W1" s="46"/>
       <c r="X1" s="46"/>
       <c r="Y1" s="46"/>
-    </row>
-    <row r="2" spans="1:25" ht="21" customHeight="1">
+      <c r="Z1" s="46"/>
+    </row>
+    <row r="2" spans="1:26" ht="21" customHeight="1">
       <c r="B2" s="47" t="s">
         <v>33</v>
       </c>
@@ -3677,8 +3728,9 @@
       <c r="W2" s="47"/>
       <c r="X2" s="47"/>
       <c r="Y2" s="47"/>
-    </row>
-    <row r="4" spans="1:25" ht="33" customHeight="1">
+      <c r="Z2" s="47"/>
+    </row>
+    <row r="4" spans="1:26" ht="33" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>387</v>
       </c>
@@ -3728,34 +3780,37 @@
         <v>624</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>46</v>
+        <v>664</v>
       </c>
       <c r="R4" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="S4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="S4" s="1" t="s">
+      <c r="T4" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="T4" s="1" t="s">
+      <c r="U4" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="U4" s="1" t="s">
+      <c r="V4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="V4" s="1" t="s">
+      <c r="W4" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="W4" s="1" t="s">
+      <c r="X4" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="X4" s="1" t="s">
+      <c r="Y4" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="Y4" s="1" t="s">
+      <c r="Z4" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="51.95" customHeight="1">
+    <row r="5" spans="1:26" ht="51.95" customHeight="1">
       <c r="A5" s="39" t="s">
         <v>57</v>
       </c>
@@ -3803,28 +3858,29 @@
       <c r="Q5" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="R5" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="S5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2" t="s">
+        <v>57</v>
+      </c>
       <c r="T5" s="2"/>
-      <c r="U5" s="2" t="s">
-        <v>57</v>
-      </c>
+      <c r="U5" s="2"/>
       <c r="V5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="W5" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="W5" s="2" t="s">
+      <c r="X5" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="X5" s="2" t="s">
+      <c r="Y5" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Y5" s="3" t="s">
+      <c r="Z5" s="3" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:25" ht="51.95" customHeight="1">
+    <row r="6" spans="1:26" ht="51.95" customHeight="1">
       <c r="A6" s="39" t="s">
         <v>57</v>
       </c>
@@ -3872,28 +3928,29 @@
       <c r="Q6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R6" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S6" s="4"/>
+      <c r="R6" s="4"/>
+      <c r="S6" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T6" s="4"/>
-      <c r="U6" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U6" s="4"/>
       <c r="V6" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W6" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="W6" s="4" t="s">
+      <c r="X6" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X6" s="4" t="s">
+      <c r="Y6" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y6" s="5" t="s">
+      <c r="Z6" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="7" spans="1:25" ht="51.95" customHeight="1">
+    <row r="7" spans="1:26" ht="51.95" customHeight="1">
       <c r="A7" s="39" t="s">
         <v>57</v>
       </c>
@@ -3941,28 +3998,29 @@
       <c r="Q7" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R7" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S7" s="4"/>
+      <c r="R7" s="4"/>
+      <c r="S7" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T7" s="4"/>
-      <c r="U7" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U7" s="4"/>
       <c r="V7" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W7" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="W7" s="4" t="s">
+      <c r="X7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X7" s="4" t="s">
+      <c r="Y7" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y7" s="5" t="s">
+      <c r="Z7" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:25" ht="51.95" customHeight="1">
+    <row r="8" spans="1:26" ht="51.95" customHeight="1">
       <c r="A8" s="39" t="s">
         <v>57</v>
       </c>
@@ -4012,28 +4070,29 @@
       <c r="Q8" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R8" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S8" s="4"/>
+      <c r="R8" s="4"/>
+      <c r="S8" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T8" s="4"/>
-      <c r="U8" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U8" s="4"/>
       <c r="V8" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W8" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="W8" s="4" t="s">
+      <c r="X8" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X8" s="4" t="s">
+      <c r="Y8" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y8" s="5" t="s">
+      <c r="Z8" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="9" spans="1:25" ht="51.95" customHeight="1">
+    <row r="9" spans="1:26" ht="51.95" customHeight="1">
       <c r="A9" s="39" t="s">
         <v>57</v>
       </c>
@@ -4081,28 +4140,29 @@
       <c r="Q9" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R9" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S9" s="4"/>
+      <c r="R9" s="4"/>
+      <c r="S9" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T9" s="4"/>
-      <c r="U9" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U9" s="4"/>
       <c r="V9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W9" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="W9" s="4" t="s">
+      <c r="X9" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X9" s="4" t="s">
+      <c r="Y9" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y9" s="5" t="s">
+      <c r="Z9" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="51.95" customHeight="1">
+    <row r="10" spans="1:26" ht="51.95" customHeight="1">
       <c r="A10" s="39" t="s">
         <v>57</v>
       </c>
@@ -4154,28 +4214,29 @@
       <c r="Q10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R10" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S10" s="4"/>
+      <c r="R10" s="4"/>
+      <c r="S10" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T10" s="4"/>
-      <c r="U10" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U10" s="4"/>
       <c r="V10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W10" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="W10" s="4" t="s">
+      <c r="X10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X10" s="4" t="s">
+      <c r="Y10" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y10" s="5" t="s">
+      <c r="Z10" s="5" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="51.95" customHeight="1">
+    <row r="11" spans="1:26" ht="51.95" customHeight="1">
       <c r="A11" s="39" t="s">
         <v>57</v>
       </c>
@@ -4225,28 +4286,29 @@
       <c r="Q11" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R11" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S11" s="4"/>
+      <c r="R11" s="4"/>
+      <c r="S11" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T11" s="4"/>
-      <c r="U11" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U11" s="4"/>
       <c r="V11" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W11" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="W11" s="4" t="s">
+      <c r="X11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X11" s="4" t="s">
+      <c r="Y11" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y11" s="5" t="s">
+      <c r="Z11" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="12" spans="1:25" ht="51.95" customHeight="1">
+    <row r="12" spans="1:26" ht="51.95" customHeight="1">
       <c r="A12" s="39" t="s">
         <v>57</v>
       </c>
@@ -4298,28 +4360,29 @@
       <c r="Q12" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R12" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S12" s="4"/>
+      <c r="R12" s="4"/>
+      <c r="S12" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T12" s="4"/>
-      <c r="U12" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U12" s="4"/>
       <c r="V12" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W12" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="W12" s="4" t="s">
+      <c r="X12" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X12" s="4" t="s">
+      <c r="Y12" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y12" s="5" t="s">
+      <c r="Z12" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:25" ht="51.95" customHeight="1">
+    <row r="13" spans="1:26" ht="51.95" customHeight="1">
       <c r="A13" s="39" t="s">
         <v>57</v>
       </c>
@@ -4371,28 +4434,29 @@
       <c r="Q13" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R13" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S13" s="4"/>
+      <c r="R13" s="4"/>
+      <c r="S13" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T13" s="4"/>
-      <c r="U13" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U13" s="4"/>
       <c r="V13" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W13" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="W13" s="4" t="s">
+      <c r="X13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X13" s="4" t="s">
+      <c r="Y13" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y13" s="5" t="s">
+      <c r="Z13" s="5" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="14" spans="1:25" ht="51.95" customHeight="1">
+    <row r="14" spans="1:26" ht="51.95" customHeight="1">
       <c r="A14" s="39" t="s">
         <v>57</v>
       </c>
@@ -4438,30 +4502,33 @@
       </c>
       <c r="P14" s="4"/>
       <c r="Q14" s="4" t="s">
-        <v>57</v>
+        <v>666</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S14" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="S14" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T14" s="4"/>
-      <c r="U14" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U14" s="4"/>
       <c r="V14" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W14" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="W14" s="4" t="s">
+      <c r="X14" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X14" s="4" t="s">
+      <c r="Y14" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y14" s="5" t="s">
+      <c r="Z14" s="5" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="1:25" ht="51.95" customHeight="1">
+    <row r="15" spans="1:26" ht="51.95" customHeight="1">
       <c r="A15" s="39" t="s">
         <v>57</v>
       </c>
@@ -4510,31 +4577,32 @@
       <c r="P15" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="Q15" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="Q15" s="4"/>
       <c r="R15" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S15" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="S15" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T15" s="4"/>
-      <c r="U15" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U15" s="4"/>
       <c r="V15" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W15" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="W15" s="4" t="s">
+      <c r="X15" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X15" s="4" t="s">
+      <c r="Y15" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y15" s="5" t="s">
+      <c r="Z15" s="5" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:25" ht="51.95" customHeight="1">
+    <row r="16" spans="1:26" ht="51.95" customHeight="1">
       <c r="A16" s="39" t="s">
         <v>57</v>
       </c>
@@ -4586,28 +4654,29 @@
       <c r="Q16" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R16" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S16" s="4"/>
+      <c r="R16" s="4"/>
+      <c r="S16" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T16" s="4"/>
-      <c r="U16" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U16" s="4"/>
       <c r="V16" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W16" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="W16" s="4" t="s">
+      <c r="X16" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X16" s="4" t="s">
+      <c r="Y16" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y16" s="5" t="s">
+      <c r="Z16" s="5" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="17" spans="1:25" ht="51.95" customHeight="1">
+    <row r="17" spans="1:26" ht="51.95" customHeight="1">
       <c r="A17" s="39" t="s">
         <v>57</v>
       </c>
@@ -4656,31 +4725,32 @@
       <c r="P17" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="Q17" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="Q17" s="4"/>
       <c r="R17" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S17" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T17" s="4"/>
-      <c r="U17" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U17" s="4"/>
       <c r="V17" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W17" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="W17" s="4" t="s">
+      <c r="X17" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X17" s="4" t="s">
+      <c r="Y17" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y17" s="5" t="s">
+      <c r="Z17" s="5" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="18" spans="1:25" ht="51.95" customHeight="1">
+    <row r="18" spans="1:26" ht="51.95" customHeight="1">
       <c r="A18" s="39" t="s">
         <v>57</v>
       </c>
@@ -4729,31 +4799,32 @@
       <c r="P18" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="Q18" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="Q18" s="4"/>
       <c r="R18" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S18" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="S18" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T18" s="4"/>
-      <c r="U18" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U18" s="4"/>
       <c r="V18" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W18" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="W18" s="4" t="s">
+      <c r="X18" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X18" s="4" t="s">
+      <c r="Y18" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y18" s="5" t="s">
+      <c r="Z18" s="5" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="51.95" customHeight="1">
+    <row r="19" spans="1:26" ht="51.95" customHeight="1">
       <c r="A19" s="39" t="s">
         <v>57</v>
       </c>
@@ -4802,31 +4873,32 @@
       <c r="P19" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="Q19" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="Q19" s="4"/>
       <c r="R19" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S19" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="S19" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T19" s="4"/>
-      <c r="U19" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U19" s="4"/>
       <c r="V19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W19" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="W19" s="4" t="s">
+      <c r="X19" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X19" s="4" t="s">
+      <c r="Y19" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y19" s="5" t="s">
+      <c r="Z19" s="5" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="20" spans="1:25" ht="51.95" customHeight="1">
+    <row r="20" spans="1:26" ht="51.95" customHeight="1">
       <c r="A20" s="39" t="s">
         <v>57</v>
       </c>
@@ -4876,28 +4948,29 @@
       <c r="Q20" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R20" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S20" s="4"/>
+      <c r="R20" s="4"/>
+      <c r="S20" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T20" s="4"/>
-      <c r="U20" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U20" s="4"/>
       <c r="V20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W20" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="W20" s="4" t="s">
+      <c r="X20" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X20" s="4" t="s">
+      <c r="Y20" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y20" s="5" t="s">
+      <c r="Z20" s="5" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="21" spans="1:25" ht="51.95" customHeight="1">
+    <row r="21" spans="1:26" ht="51.95" customHeight="1">
       <c r="A21" s="39" t="s">
         <v>57</v>
       </c>
@@ -4947,30 +5020,31 @@
         <v>634</v>
       </c>
       <c r="Q21" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="R21" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S21" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="R21" s="4"/>
+      <c r="S21" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T21" s="4"/>
-      <c r="U21" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U21" s="4"/>
       <c r="V21" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W21" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="W21" s="4" t="s">
+      <c r="X21" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X21" s="4" t="s">
+      <c r="Y21" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y21" s="5" t="s">
+      <c r="Z21" s="5" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="51.95" customHeight="1">
+    <row r="22" spans="1:26" ht="51.95" customHeight="1">
       <c r="A22" s="39" t="s">
         <v>57</v>
       </c>
@@ -5022,28 +5096,29 @@
       <c r="Q22" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R22" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S22" s="4"/>
+      <c r="R22" s="4"/>
+      <c r="S22" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T22" s="4"/>
-      <c r="U22" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U22" s="4"/>
       <c r="V22" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W22" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="W22" s="4" t="s">
+      <c r="X22" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X22" s="4" t="s">
+      <c r="Y22" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y22" s="5" t="s">
+      <c r="Z22" s="5" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="51.95" customHeight="1">
+    <row r="23" spans="1:26" ht="51.95" customHeight="1">
       <c r="A23" s="39" t="s">
         <v>57</v>
       </c>
@@ -5093,30 +5168,31 @@
         <v>621</v>
       </c>
       <c r="Q23" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="R23" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S23" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T23" s="4"/>
-      <c r="U23" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U23" s="4"/>
       <c r="V23" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W23" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="W23" s="4" t="s">
+      <c r="X23" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X23" s="4" t="s">
+      <c r="Y23" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y23" s="5" t="s">
+      <c r="Z23" s="5" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="51.95" customHeight="1">
+    <row r="24" spans="1:26" ht="51.95" customHeight="1">
       <c r="A24" s="39" t="s">
         <v>57</v>
       </c>
@@ -5166,30 +5242,31 @@
         <v>637</v>
       </c>
       <c r="Q24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="R24" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S24" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T24" s="4"/>
-      <c r="U24" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U24" s="4"/>
       <c r="V24" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W24" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="W24" s="4" t="s">
+      <c r="X24" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X24" s="4" t="s">
+      <c r="Y24" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y24" s="5" t="s">
+      <c r="Z24" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="25" spans="1:25" ht="51.95" customHeight="1">
+    <row r="25" spans="1:26" ht="51.95" customHeight="1">
       <c r="A25" s="39" t="s">
         <v>57</v>
       </c>
@@ -5237,28 +5314,29 @@
       <c r="Q25" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R25" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T25" s="4"/>
-      <c r="U25" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U25" s="4"/>
       <c r="V25" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W25" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="W25" s="4" t="s">
+      <c r="X25" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X25" s="4" t="s">
+      <c r="Y25" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y25" s="5" t="s">
+      <c r="Z25" s="5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="51.95" customHeight="1">
+    <row r="26" spans="1:26" ht="51.95" customHeight="1">
       <c r="A26" s="39" t="s">
         <v>57</v>
       </c>
@@ -5310,28 +5388,29 @@
       <c r="Q26" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T26" s="4"/>
-      <c r="U26" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U26" s="4"/>
       <c r="V26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W26" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="W26" s="4" t="s">
+      <c r="X26" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X26" s="4" t="s">
+      <c r="Y26" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y26" s="5" t="s">
+      <c r="Z26" s="5" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="51.95" customHeight="1">
+    <row r="27" spans="1:26" ht="51.95" customHeight="1">
       <c r="A27" s="39" t="s">
         <v>57</v>
       </c>
@@ -5379,30 +5458,31 @@
         <v>640</v>
       </c>
       <c r="Q27" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="R27" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S27" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="R27" s="4"/>
+      <c r="S27" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T27" s="4"/>
-      <c r="U27" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U27" s="4"/>
       <c r="V27" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W27" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="W27" s="4" t="s">
+      <c r="X27" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X27" s="4" t="s">
+      <c r="Y27" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y27" s="5" t="s">
+      <c r="Z27" s="5" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="51.95" customHeight="1">
+    <row r="28" spans="1:26" ht="51.95" customHeight="1">
       <c r="A28" s="39" t="s">
         <v>57</v>
       </c>
@@ -5452,30 +5532,31 @@
         <v>641</v>
       </c>
       <c r="Q28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="R28" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S28" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="R28" s="4"/>
+      <c r="S28" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T28" s="4"/>
-      <c r="U28" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U28" s="4"/>
       <c r="V28" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W28" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="W28" s="4" t="s">
+      <c r="X28" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X28" s="4" t="s">
+      <c r="Y28" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y28" s="5" t="s">
+      <c r="Z28" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="29" spans="1:25" ht="51.95" customHeight="1">
+    <row r="29" spans="1:26" ht="51.95" customHeight="1">
       <c r="A29" s="39" t="s">
         <v>57</v>
       </c>
@@ -5525,28 +5606,29 @@
       <c r="Q29" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R29" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S29" s="4"/>
+      <c r="R29" s="4"/>
+      <c r="S29" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T29" s="4"/>
-      <c r="U29" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U29" s="4"/>
       <c r="V29" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W29" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="W29" s="4" t="s">
+      <c r="X29" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X29" s="4" t="s">
+      <c r="Y29" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y29" s="5" t="s">
+      <c r="Z29" s="5" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="30" spans="1:25" ht="51.95" customHeight="1">
+    <row r="30" spans="1:26" ht="51.95" customHeight="1">
       <c r="A30" s="39" t="s">
         <v>57</v>
       </c>
@@ -5598,28 +5680,29 @@
       <c r="Q30" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R30" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T30" s="4"/>
-      <c r="U30" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U30" s="4"/>
       <c r="V30" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W30" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="W30" s="4" t="s">
+      <c r="X30" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X30" s="4" t="s">
+      <c r="Y30" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y30" s="5" t="s">
+      <c r="Z30" s="5" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="51.95" customHeight="1">
+    <row r="31" spans="1:26" ht="51.95" customHeight="1">
       <c r="A31" s="39" t="s">
         <v>57</v>
       </c>
@@ -5667,28 +5750,29 @@
       <c r="Q31" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R31" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S31" s="4"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T31" s="4"/>
-      <c r="U31" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U31" s="4"/>
       <c r="V31" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W31" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="W31" s="4" t="s">
+      <c r="X31" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X31" s="4" t="s">
+      <c r="Y31" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y31" s="5" t="s">
+      <c r="Z31" s="5" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="32" spans="1:25" ht="51.95" customHeight="1">
+    <row r="32" spans="1:26" ht="51.95" customHeight="1">
       <c r="A32" s="39" t="s">
         <v>57</v>
       </c>
@@ -5738,28 +5822,29 @@
       <c r="Q32" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R32" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S32" s="4"/>
+      <c r="R32" s="4"/>
+      <c r="S32" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T32" s="4"/>
-      <c r="U32" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U32" s="4"/>
       <c r="V32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W32" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="W32" s="4" t="s">
+      <c r="X32" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X32" s="4" t="s">
+      <c r="Y32" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y32" s="5" t="s">
+      <c r="Z32" s="5" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="33" spans="1:25" ht="51.95" customHeight="1">
+    <row r="33" spans="1:26" ht="51.95" customHeight="1">
       <c r="A33" s="39" t="s">
         <v>57</v>
       </c>
@@ -5809,28 +5894,29 @@
       <c r="Q33" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R33" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T33" s="4"/>
-      <c r="U33" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U33" s="4"/>
       <c r="V33" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W33" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="W33" s="4" t="s">
+      <c r="X33" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X33" s="4" t="s">
+      <c r="Y33" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y33" s="5" t="s">
+      <c r="Z33" s="5" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="34" spans="1:25" ht="51.95" customHeight="1">
+    <row r="34" spans="1:26" ht="51.95" customHeight="1">
       <c r="A34" s="39" t="s">
         <v>57</v>
       </c>
@@ -5882,28 +5968,29 @@
       <c r="Q34" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R34" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S34" s="4"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T34" s="4"/>
-      <c r="U34" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U34" s="4"/>
       <c r="V34" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W34" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="W34" s="4" t="s">
+      <c r="X34" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X34" s="4" t="s">
+      <c r="Y34" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y34" s="5" t="s">
+      <c r="Z34" s="5" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="35" spans="1:25" ht="51.95" customHeight="1">
+    <row r="35" spans="1:26" ht="51.95" customHeight="1">
       <c r="A35" s="39" t="s">
         <v>57</v>
       </c>
@@ -5951,28 +6038,29 @@
       <c r="Q35" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R35" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S35" s="4"/>
+      <c r="R35" s="4"/>
+      <c r="S35" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T35" s="4"/>
-      <c r="U35" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U35" s="4"/>
       <c r="V35" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W35" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="W35" s="4" t="s">
+      <c r="X35" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X35" s="4" t="s">
+      <c r="Y35" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y35" s="5" t="s">
+      <c r="Z35" s="5" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="36" spans="1:25" ht="51.95" customHeight="1">
+    <row r="36" spans="1:26" ht="51.95" customHeight="1">
       <c r="A36" s="39" t="s">
         <v>57</v>
       </c>
@@ -6022,28 +6110,29 @@
       <c r="Q36" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R36" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S36" s="4"/>
+      <c r="R36" s="4"/>
+      <c r="S36" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T36" s="4"/>
-      <c r="U36" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U36" s="4"/>
       <c r="V36" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W36" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="W36" s="4" t="s">
+      <c r="X36" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X36" s="4" t="s">
+      <c r="Y36" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y36" s="5" t="s">
+      <c r="Z36" s="5" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="37" spans="1:25" ht="51.95" customHeight="1">
+    <row r="37" spans="1:26" ht="51.95" customHeight="1">
       <c r="A37" s="39" t="s">
         <v>57</v>
       </c>
@@ -6095,28 +6184,29 @@
       <c r="Q37" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R37" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S37" s="4"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T37" s="4"/>
-      <c r="U37" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U37" s="4"/>
       <c r="V37" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W37" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="W37" s="4" t="s">
+      <c r="X37" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X37" s="4" t="s">
+      <c r="Y37" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y37" s="5" t="s">
+      <c r="Z37" s="5" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="38" spans="1:25" ht="51.95" customHeight="1">
+    <row r="38" spans="1:26" ht="51.95" customHeight="1">
       <c r="A38" s="39" t="s">
         <v>57</v>
       </c>
@@ -6165,31 +6255,32 @@
       <c r="P38" s="4" t="s">
         <v>625</v>
       </c>
-      <c r="Q38" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="Q38" s="4"/>
       <c r="R38" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S38" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="S38" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T38" s="4"/>
-      <c r="U38" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U38" s="4"/>
       <c r="V38" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W38" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="W38" s="4" t="s">
+      <c r="X38" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X38" s="4" t="s">
+      <c r="Y38" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y38" s="5" t="s">
+      <c r="Z38" s="5" t="s">
         <v>195</v>
       </c>
     </row>
-    <row r="39" spans="1:25" ht="51.95" customHeight="1">
+    <row r="39" spans="1:26" ht="51.95" customHeight="1">
       <c r="A39" s="39" t="s">
         <v>57</v>
       </c>
@@ -6234,31 +6325,32 @@
         <v>628</v>
       </c>
       <c r="P39" s="4"/>
-      <c r="Q39" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="Q39" s="4"/>
       <c r="R39" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S39" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="S39" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T39" s="4"/>
-      <c r="U39" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U39" s="4"/>
       <c r="V39" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W39" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="W39" s="4" t="s">
+      <c r="X39" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X39" s="4" t="s">
+      <c r="Y39" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y39" s="5" t="s">
+      <c r="Z39" s="5" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="40" spans="1:25" ht="51.95" customHeight="1">
+    <row r="40" spans="1:26" ht="51.95" customHeight="1">
       <c r="A40" s="39" t="s">
         <v>57</v>
       </c>
@@ -6310,28 +6402,29 @@
       <c r="Q40" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R40" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T40" s="4"/>
-      <c r="U40" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U40" s="4"/>
       <c r="V40" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W40" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="W40" s="4" t="s">
+      <c r="X40" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X40" s="4" t="s">
+      <c r="Y40" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y40" s="5" t="s">
+      <c r="Z40" s="5" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="41" spans="1:25" ht="51.95" customHeight="1">
+    <row r="41" spans="1:26" ht="51.95" customHeight="1">
       <c r="A41" s="39" t="s">
         <v>57</v>
       </c>
@@ -6381,30 +6474,31 @@
         <v>621</v>
       </c>
       <c r="Q41" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="R41" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S41" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T41" s="4"/>
-      <c r="U41" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U41" s="4"/>
       <c r="V41" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W41" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="W41" s="4" t="s">
+      <c r="X41" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X41" s="4" t="s">
+      <c r="Y41" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y41" s="5" t="s">
+      <c r="Z41" s="5" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="42" spans="1:25" ht="51.95" customHeight="1">
+    <row r="42" spans="1:26" ht="51.95" customHeight="1">
       <c r="A42" s="39" t="s">
         <v>57</v>
       </c>
@@ -6456,28 +6550,29 @@
       <c r="Q42" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R42" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T42" s="4"/>
-      <c r="U42" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U42" s="4"/>
       <c r="V42" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W42" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="W42" s="4" t="s">
+      <c r="X42" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X42" s="4" t="s">
+      <c r="Y42" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y42" s="5" t="s">
+      <c r="Z42" s="5" t="s">
         <v>211</v>
       </c>
     </row>
-    <row r="43" spans="1:25" ht="51.95" customHeight="1">
+    <row r="43" spans="1:26" ht="51.95" customHeight="1">
       <c r="A43" s="39" t="s">
         <v>57</v>
       </c>
@@ -6527,28 +6622,29 @@
       <c r="Q43" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R43" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T43" s="4"/>
-      <c r="U43" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U43" s="4"/>
       <c r="V43" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W43" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="W43" s="4" t="s">
+      <c r="X43" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X43" s="4" t="s">
+      <c r="Y43" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y43" s="5" t="s">
+      <c r="Z43" s="5" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="44" spans="1:25" ht="51.95" customHeight="1">
+    <row r="44" spans="1:26" ht="51.95" customHeight="1">
       <c r="A44" s="39" t="s">
         <v>57</v>
       </c>
@@ -6596,30 +6692,31 @@
         <v>629</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="R44" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S44" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="R44" s="4"/>
+      <c r="S44" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T44" s="4"/>
-      <c r="U44" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U44" s="4"/>
       <c r="V44" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W44" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="W44" s="4" t="s">
+      <c r="X44" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X44" s="4" t="s">
+      <c r="Y44" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y44" s="5" t="s">
+      <c r="Z44" s="5" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="45" spans="1:25" ht="51.95" customHeight="1">
+    <row r="45" spans="1:26" ht="51.95" customHeight="1">
       <c r="A45" s="39" t="s">
         <v>57</v>
       </c>
@@ -6669,30 +6766,31 @@
         <v>653</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="R45" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S45" s="4"/>
+        <v>663</v>
+      </c>
+      <c r="R45" s="4"/>
+      <c r="S45" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T45" s="4"/>
-      <c r="U45" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U45" s="4"/>
       <c r="V45" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W45" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="W45" s="4" t="s">
+      <c r="X45" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X45" s="4" t="s">
+      <c r="Y45" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y45" s="5" t="s">
+      <c r="Z45" s="5" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="46" spans="1:25" ht="51.95" customHeight="1">
+    <row r="46" spans="1:26" ht="51.95" customHeight="1">
       <c r="A46" s="39" t="s">
         <v>57</v>
       </c>
@@ -6742,28 +6840,29 @@
       <c r="Q46" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R46" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S46" s="4"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T46" s="4"/>
-      <c r="U46" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U46" s="4"/>
       <c r="V46" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W46" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="W46" s="4" t="s">
+      <c r="X46" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X46" s="4" t="s">
+      <c r="Y46" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y46" s="5" t="s">
+      <c r="Z46" s="5" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="47" spans="1:25" ht="51.95" customHeight="1">
+    <row r="47" spans="1:26" ht="51.95" customHeight="1">
       <c r="A47" s="39" t="s">
         <v>57</v>
       </c>
@@ -6813,28 +6912,29 @@
       <c r="Q47" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R47" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S47" s="4"/>
+      <c r="R47" s="4"/>
+      <c r="S47" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T47" s="4"/>
-      <c r="U47" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U47" s="4"/>
       <c r="V47" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W47" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="W47" s="4" t="s">
+      <c r="X47" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X47" s="4" t="s">
+      <c r="Y47" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y47" s="5" t="s">
+      <c r="Z47" s="5" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="48" spans="1:25" ht="51.95" customHeight="1">
+    <row r="48" spans="1:26" ht="51.95" customHeight="1">
       <c r="A48" s="39" t="s">
         <v>57</v>
       </c>
@@ -6884,28 +6984,29 @@
       <c r="Q48" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R48" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T48" s="4"/>
-      <c r="U48" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U48" s="4"/>
       <c r="V48" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W48" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="W48" s="4" t="s">
+      <c r="X48" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X48" s="4" t="s">
+      <c r="Y48" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y48" s="5" t="s">
+      <c r="Z48" s="5" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="49" spans="1:25" ht="51.95" customHeight="1">
+    <row r="49" spans="1:26" ht="51.95" customHeight="1">
       <c r="A49" s="39" t="s">
         <v>57</v>
       </c>
@@ -6957,28 +7058,29 @@
       <c r="Q49" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R49" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T49" s="4"/>
-      <c r="U49" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U49" s="4"/>
       <c r="V49" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W49" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="W49" s="4" t="s">
+      <c r="X49" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X49" s="4" t="s">
+      <c r="Y49" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y49" s="5" t="s">
+      <c r="Z49" s="5" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="51.95" customHeight="1">
+    <row r="50" spans="1:26" ht="51.95" customHeight="1">
       <c r="A50" s="39" t="s">
         <v>57</v>
       </c>
@@ -7030,28 +7132,29 @@
       <c r="Q50" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R50" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S50" s="4"/>
+      <c r="R50" s="4"/>
+      <c r="S50" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T50" s="4"/>
-      <c r="U50" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U50" s="4"/>
       <c r="V50" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W50" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="W50" s="4" t="s">
+      <c r="X50" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X50" s="4" t="s">
+      <c r="Y50" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y50" s="5" t="s">
+      <c r="Z50" s="5" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="51.95" customHeight="1">
+    <row r="51" spans="1:26" ht="51.95" customHeight="1">
       <c r="A51" s="39" t="s">
         <v>57</v>
       </c>
@@ -7101,28 +7204,29 @@
       <c r="Q51" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R51" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T51" s="4"/>
-      <c r="U51" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U51" s="4"/>
       <c r="V51" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W51" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="W51" s="4" t="s">
+      <c r="X51" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X51" s="4" t="s">
+      <c r="Y51" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y51" s="5" t="s">
+      <c r="Z51" s="5" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="51.95" customHeight="1">
+    <row r="52" spans="1:26" ht="51.95" customHeight="1">
       <c r="A52" s="39" t="s">
         <v>57</v>
       </c>
@@ -7172,28 +7276,29 @@
       <c r="Q52" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R52" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T52" s="4"/>
-      <c r="U52" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U52" s="4"/>
       <c r="V52" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W52" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="W52" s="4" t="s">
+      <c r="X52" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X52" s="4" t="s">
+      <c r="Y52" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y52" s="5" t="s">
+      <c r="Z52" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="51.95" customHeight="1">
+    <row r="53" spans="1:26" ht="51.95" customHeight="1">
       <c r="A53" s="39" t="s">
         <v>57</v>
       </c>
@@ -7245,28 +7350,29 @@
       <c r="Q53" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R53" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T53" s="4"/>
-      <c r="U53" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U53" s="4"/>
       <c r="V53" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W53" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="W53" s="4" t="s">
+      <c r="X53" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X53" s="4" t="s">
+      <c r="Y53" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y53" s="5" t="s">
+      <c r="Z53" s="5" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="54" spans="1:25" ht="51.95" customHeight="1">
+    <row r="54" spans="1:26" ht="51.95" customHeight="1">
       <c r="A54" s="39" t="s">
         <v>57</v>
       </c>
@@ -7318,28 +7424,29 @@
       <c r="Q54" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R54" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S54" s="4"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T54" s="4"/>
-      <c r="U54" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U54" s="4"/>
       <c r="V54" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W54" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="W54" s="4" t="s">
+      <c r="X54" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X54" s="4" t="s">
+      <c r="Y54" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y54" s="5" t="s">
+      <c r="Z54" s="5" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="51.95" customHeight="1">
+    <row r="55" spans="1:26" ht="51.95" customHeight="1">
       <c r="A55" s="39" t="s">
         <v>57</v>
       </c>
@@ -7389,28 +7496,29 @@
       <c r="Q55" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R55" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T55" s="4"/>
-      <c r="U55" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U55" s="4"/>
       <c r="V55" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W55" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="W55" s="4" t="s">
+      <c r="X55" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X55" s="4" t="s">
+      <c r="Y55" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y55" s="5" t="s">
+      <c r="Z55" s="5" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="51.95" customHeight="1">
+    <row r="56" spans="1:26" ht="51.95" customHeight="1">
       <c r="A56" s="39" t="s">
         <v>57</v>
       </c>
@@ -7462,28 +7570,29 @@
       <c r="Q56" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R56" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S56" s="4"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T56" s="4"/>
-      <c r="U56" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U56" s="4"/>
       <c r="V56" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W56" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="W56" s="4" t="s">
+      <c r="X56" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X56" s="4" t="s">
+      <c r="Y56" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y56" s="5" t="s">
+      <c r="Z56" s="5" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="51.95" customHeight="1">
+    <row r="57" spans="1:26" ht="51.95" customHeight="1">
       <c r="A57" s="39" t="s">
         <v>57</v>
       </c>
@@ -7533,28 +7642,29 @@
       <c r="Q57" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R57" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T57" s="4"/>
-      <c r="U57" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U57" s="4"/>
       <c r="V57" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W57" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="W57" s="4" t="s">
+      <c r="X57" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X57" s="4" t="s">
+      <c r="Y57" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y57" s="5" t="s">
+      <c r="Z57" s="5" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="58" spans="1:25" ht="51.95" customHeight="1">
+    <row r="58" spans="1:26" ht="51.95" customHeight="1">
       <c r="A58" s="39" t="s">
         <v>57</v>
       </c>
@@ -7606,28 +7716,29 @@
       <c r="Q58" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R58" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T58" s="4"/>
-      <c r="U58" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U58" s="4"/>
       <c r="V58" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W58" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="W58" s="4" t="s">
+      <c r="X58" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X58" s="4" t="s">
+      <c r="Y58" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y58" s="5" t="s">
+      <c r="Z58" s="5" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="59" spans="1:25" ht="51.95" customHeight="1">
+    <row r="59" spans="1:26" ht="51.95" customHeight="1">
       <c r="A59" s="39" t="s">
         <v>57</v>
       </c>
@@ -7679,28 +7790,29 @@
       <c r="Q59" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="R59" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="S59" s="4"/>
+      <c r="R59" s="4"/>
+      <c r="S59" s="4" t="s">
+        <v>57</v>
+      </c>
       <c r="T59" s="4"/>
-      <c r="U59" s="4" t="s">
-        <v>57</v>
-      </c>
+      <c r="U59" s="4"/>
       <c r="V59" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="W59" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="W59" s="4" t="s">
+      <c r="X59" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="X59" s="4" t="s">
+      <c r="Y59" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="Y59" s="5" t="s">
+      <c r="Z59" s="5" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="60" spans="1:25" ht="51.95" customHeight="1">
+    <row r="60" spans="1:26" ht="51.95" customHeight="1">
       <c r="A60" s="39" t="s">
         <v>57</v>
       </c>
@@ -7748,54 +7860,55 @@
       <c r="Q60" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="R60" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="S60" s="6"/>
+      <c r="R60" s="6"/>
+      <c r="S60" s="6" t="s">
+        <v>57</v>
+      </c>
       <c r="T60" s="6"/>
-      <c r="U60" s="6" t="s">
-        <v>57</v>
-      </c>
+      <c r="U60" s="6"/>
       <c r="V60" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="W60" s="6" t="s">
         <v>282</v>
       </c>
-      <c r="W60" s="6" t="s">
+      <c r="X60" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="X60" s="6" t="s">
+      <c r="Y60" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="Y60" s="7" t="s">
+      <c r="Z60" s="7" t="s">
         <v>283</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:Y1"/>
-    <mergeCell ref="B2:Y2"/>
+    <mergeCell ref="B1:Z1"/>
+    <mergeCell ref="B2:Z2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A5:Y27 A29:O29 Q28:Y29 A28:N28 A30:Y33 A34:O34 Q34:Y34 A35:Y60">
+  <conditionalFormatting sqref="A28:N28 Q28:Z29 A29:O29 A30:Z33 A34:O34 Q34:Z34 A5:Z27 A35:Z60">
     <cfRule type="expression" dxfId="4" priority="3">
       <formula>$E5="Must"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="W5:W60">
-    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="Pending"/>
+  <conditionalFormatting sqref="O28:P28">
+    <cfRule type="expression" dxfId="3" priority="2">
+      <formula>$E28="Must"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="P29">
     <cfRule type="expression" dxfId="2" priority="8">
       <formula>$E28="Must"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O28:P28">
-    <cfRule type="expression" dxfId="1" priority="2">
-      <formula>$E28="Must"</formula>
+  <conditionalFormatting sqref="P34">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>$E34="Must"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P34">
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>$E34="Must"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="X5:X60">
+    <cfRule type="containsText" dxfId="0" priority="6" operator="containsText" text="Pending"/>
   </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation type="list" sqref="B5:B60" xr:uid="{00000000-0002-0000-0100-000000000000}">

--- a/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
+++ b/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d752cb73b61fc091/Desktop/linuxlabs/projectredstone/docs/project-management/02_Business_Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="784" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{30CC72D7-AC51-4E30-8460-6C0F686F2BF5}"/>
+  <xr:revisionPtr revIDLastSave="785" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19A492DE-21E7-4B61-BCAA-22328CBB8AEE}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3207,10 +3207,10 @@
     <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="HLD (Primary)"/>
     <tableColumn id="24" xr3:uid="{599BD185-8391-4930-BB9A-B52E39596ACD}" name="HLD (Secondary)" dataDxfId="8"/>
     <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="LLD (Primary)"/>
-    <tableColumn id="10" xr3:uid="{D9149C79-EC24-41C1-B36D-CD2D9225FFA3}" name="LLD (Secondary)" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{D9149C79-EC24-41C1-B36D-CD2D9225FFA3}" name="LLD (Secondary)" dataDxfId="7"/>
     <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="ADR"/>
-    <tableColumn id="25" xr3:uid="{28378BB4-B208-482C-96C2-5A1994DECC42}" name="SOW" dataDxfId="7"/>
-    <tableColumn id="26" xr3:uid="{BAEC8EC4-D90B-4FBA-979D-21CDBE3C330A}" name="Sprint" dataDxfId="6"/>
+    <tableColumn id="25" xr3:uid="{28378BB4-B208-482C-96C2-5A1994DECC42}" name="SOW" dataDxfId="6"/>
+    <tableColumn id="26" xr3:uid="{BAEC8EC4-D90B-4FBA-979D-21CDBE3C330A}" name="Sprint" dataDxfId="5"/>
     <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Test / UAT"/>
     <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Acceptance Criteria"/>
     <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Status"/>
@@ -3645,7 +3645,7 @@
   <dimension ref="A1:Z60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.625" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="13.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="48" customWidth="1"/>
@@ -7887,7 +7887,7 @@
     <mergeCell ref="B1:Z1"/>
     <mergeCell ref="B2:Z2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A28:N28 Q28:Z29 A29:O29 A30:Z33 A34:O34 Q34:Z34 A5:Z27 A35:Z60">
+  <conditionalFormatting sqref="A5:Z27 A28:N28 Q28:Z29 A29:O29 A30:Z33 A34:O34 Q34:Z34 A35:Z60">
     <cfRule type="expression" dxfId="4" priority="3">
       <formula>$E5="Must"</formula>
     </cfRule>

--- a/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
+++ b/docs/project-management/02_Business_Requirements/Northwind-Outdoor-RTM-v1.0.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d752cb73b61fc091/Desktop/linuxlabs/projectredstone/docs/project-management/02_Business_Requirements/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="785" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{19A492DE-21E7-4B61-BCAA-22328CBB8AEE}"/>
+  <xr:revisionPtr revIDLastSave="789" documentId="8_{170D4D7C-E242-4887-90C6-7A678B36976C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C381DF28-FFE1-4755-8D2F-0EF22ED441F8}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
